--- a/data_panen_dummy.xlsx
+++ b/data_panen_dummy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vansa\Documents\Kulyeah\Epidem\db_tajumase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C9140E-768A-4B4A-89D5-8D3136725319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2A0BF8-B514-44CF-8656-48A21AED0331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="54">
   <si>
     <t>Program</t>
   </si>
@@ -178,6 +178,21 @@
   </si>
   <si>
     <t>Komoditas</t>
+  </si>
+  <si>
+    <t>Produk_Olahan</t>
+  </si>
+  <si>
+    <t>Sabun</t>
+  </si>
+  <si>
+    <t>Data_Produksi_Olahan</t>
+  </si>
+  <si>
+    <t>Data_Penjualan_Olahan</t>
+  </si>
+  <si>
+    <t>Sampo</t>
   </si>
 </sst>
 </file>
@@ -517,17 +532,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L481"/>
+  <dimension ref="A1:O481"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" customWidth="1"/>
     <col min="10" max="10" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" customWidth="1"/>
+    <col min="14" max="14" width="23.6640625" customWidth="1"/>
+    <col min="15" max="15" width="20.77734375" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,8 +584,17 @@
       <c r="L1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -595,18 +624,27 @@
       </c>
       <c r="J2">
         <f ca="1">RANDBETWEEN(100,400)</f>
-        <v>255</v>
+        <v>358</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:L17" ca="1" si="0">RANDBETWEEN(100,400)</f>
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>308</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+      <c r="M2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2">
+        <v>21</v>
+      </c>
+      <c r="O2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -636,18 +674,27 @@
       </c>
       <c r="J3">
         <f t="shared" ref="J3:L66" ca="1" si="1">RANDBETWEEN(100,400)</f>
-        <v>171</v>
+        <v>272</v>
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
-        <v>362</v>
+        <v>257</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+      <c r="M3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3">
+        <v>42</v>
+      </c>
+      <c r="O3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -677,18 +724,18 @@
       </c>
       <c r="J4">
         <f t="shared" ca="1" si="1"/>
-        <v>268</v>
+        <v>189</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>243</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="0"/>
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -718,18 +765,18 @@
       </c>
       <c r="J5">
         <f t="shared" ca="1" si="1"/>
-        <v>183</v>
+        <v>337</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="0"/>
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="0"/>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -759,18 +806,18 @@
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
-        <v>107</v>
+        <v>245</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="0"/>
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="0"/>
-        <v>260</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -800,18 +847,18 @@
       </c>
       <c r="J7">
         <f t="shared" ca="1" si="1"/>
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="0"/>
-        <v>327</v>
+        <v>196</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="0"/>
-        <v>140</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -841,18 +888,18 @@
       </c>
       <c r="J8">
         <f t="shared" ca="1" si="1"/>
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="0"/>
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -882,18 +929,18 @@
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="1"/>
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="0"/>
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="0"/>
-        <v>187</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -923,18 +970,18 @@
       </c>
       <c r="J10">
         <f t="shared" ca="1" si="1"/>
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="0"/>
-        <v>369</v>
+        <v>312</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="0"/>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -964,18 +1011,18 @@
       </c>
       <c r="J11">
         <f t="shared" ca="1" si="1"/>
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="0"/>
-        <v>347</v>
+        <v>179</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="0"/>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1005,18 +1052,18 @@
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="1"/>
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="0"/>
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="0"/>
-        <v>238</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1046,18 +1093,18 @@
       </c>
       <c r="J13">
         <f t="shared" ca="1" si="1"/>
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="0"/>
-        <v>327</v>
+        <v>220</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="0"/>
-        <v>351</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -1087,18 +1134,18 @@
       </c>
       <c r="J14">
         <f t="shared" ca="1" si="1"/>
-        <v>375</v>
+        <v>162</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="0"/>
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="0"/>
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1128,18 +1175,18 @@
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="1"/>
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="0"/>
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="0"/>
-        <v>231</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -1169,15 +1216,15 @@
       </c>
       <c r="J16">
         <f t="shared" ca="1" si="1"/>
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="0"/>
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="0"/>
-        <v>207</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1210,15 +1257,15 @@
       </c>
       <c r="J17">
         <f t="shared" ca="1" si="1"/>
-        <v>263</v>
+        <v>342</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="0"/>
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="0"/>
-        <v>320</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1251,15 +1298,15 @@
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="1"/>
-        <v>387</v>
+        <v>258</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="1"/>
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="1"/>
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1292,15 +1339,15 @@
       </c>
       <c r="J19">
         <f t="shared" ca="1" si="1"/>
-        <v>168</v>
+        <v>356</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="1"/>
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="1"/>
-        <v>368</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1333,15 +1380,15 @@
       </c>
       <c r="J20">
         <f t="shared" ca="1" si="1"/>
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="1"/>
-        <v>368</v>
+        <v>179</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="1"/>
-        <v>208</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1374,15 +1421,15 @@
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="1"/>
-        <v>151</v>
+        <v>270</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="1"/>
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="1"/>
-        <v>140</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1415,15 +1462,15 @@
       </c>
       <c r="J22">
         <f t="shared" ca="1" si="1"/>
-        <v>146</v>
+        <v>229</v>
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="1"/>
-        <v>319</v>
+        <v>384</v>
       </c>
       <c r="L22">
         <f t="shared" ca="1" si="1"/>
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1456,15 +1503,15 @@
       </c>
       <c r="J23">
         <f t="shared" ca="1" si="1"/>
-        <v>147</v>
+        <v>315</v>
       </c>
       <c r="K23">
         <f t="shared" ca="1" si="1"/>
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="L23">
         <f t="shared" ca="1" si="1"/>
-        <v>194</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1497,15 +1544,15 @@
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="1"/>
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="1"/>
-        <v>263</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1538,15 +1585,15 @@
       </c>
       <c r="J25">
         <f t="shared" ca="1" si="1"/>
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="1"/>
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="1"/>
-        <v>376</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -1579,15 +1626,15 @@
       </c>
       <c r="J26">
         <f t="shared" ca="1" si="1"/>
-        <v>121</v>
+        <v>199</v>
       </c>
       <c r="K26">
         <f t="shared" ca="1" si="1"/>
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="1"/>
-        <v>252</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -1620,15 +1667,15 @@
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="1"/>
-        <v>242</v>
+        <v>359</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="1"/>
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="1"/>
-        <v>333</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -1661,15 +1708,15 @@
       </c>
       <c r="J28">
         <f t="shared" ca="1" si="1"/>
-        <v>145</v>
+        <v>335</v>
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="1"/>
-        <v>297</v>
+        <v>391</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -1702,15 +1749,15 @@
       </c>
       <c r="J29">
         <f t="shared" ca="1" si="1"/>
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="K29">
         <f t="shared" ca="1" si="1"/>
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="L29">
         <f t="shared" ca="1" si="1"/>
-        <v>156</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -1743,15 +1790,15 @@
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="1"/>
-        <v>245</v>
+        <v>398</v>
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="1"/>
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="1"/>
-        <v>264</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -1784,15 +1831,15 @@
       </c>
       <c r="J31">
         <f t="shared" ca="1" si="1"/>
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="K31">
         <f t="shared" ca="1" si="1"/>
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="1"/>
-        <v>134</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -1825,15 +1872,15 @@
       </c>
       <c r="J32">
         <f t="shared" ca="1" si="1"/>
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="K32">
         <f t="shared" ca="1" si="1"/>
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="1"/>
-        <v>372</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -1866,15 +1913,15 @@
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="1"/>
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="1"/>
-        <v>225</v>
+        <v>338</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="1"/>
-        <v>256</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -1907,15 +1954,15 @@
       </c>
       <c r="J34">
         <f t="shared" ca="1" si="1"/>
-        <v>387</v>
+        <v>244</v>
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="1"/>
-        <v>136</v>
+        <v>365</v>
       </c>
       <c r="L34">
         <f t="shared" ca="1" si="1"/>
-        <v>144</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -1948,15 +1995,15 @@
       </c>
       <c r="J35">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>277</v>
       </c>
       <c r="K35">
         <f t="shared" ca="1" si="1"/>
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="L35">
         <f t="shared" ca="1" si="1"/>
-        <v>257</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -1989,15 +2036,15 @@
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="1"/>
-        <v>352</v>
+        <v>200</v>
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="1"/>
-        <v>274</v>
+        <v>150</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="1"/>
-        <v>321</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -2030,15 +2077,15 @@
       </c>
       <c r="J37">
         <f t="shared" ca="1" si="1"/>
-        <v>346</v>
+        <v>240</v>
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="L37">
         <f t="shared" ca="1" si="1"/>
-        <v>265</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2071,15 +2118,15 @@
       </c>
       <c r="J38">
         <f t="shared" ca="1" si="1"/>
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="K38">
         <f t="shared" ca="1" si="1"/>
-        <v>374</v>
+        <v>229</v>
       </c>
       <c r="L38">
         <f t="shared" ca="1" si="1"/>
-        <v>349</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2112,15 +2159,15 @@
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="1"/>
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>206</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="1"/>
-        <v>345</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2153,15 +2200,15 @@
       </c>
       <c r="J40">
         <f t="shared" ca="1" si="1"/>
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="K40">
         <f t="shared" ca="1" si="1"/>
-        <v>381</v>
+        <v>102</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2194,15 +2241,15 @@
       </c>
       <c r="J41">
         <f t="shared" ca="1" si="1"/>
-        <v>329</v>
+        <v>245</v>
       </c>
       <c r="K41">
         <f t="shared" ca="1" si="1"/>
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="1"/>
-        <v>220</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2235,15 +2282,15 @@
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="1"/>
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="1"/>
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="1"/>
-        <v>389</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2276,15 +2323,15 @@
       </c>
       <c r="J43">
         <f t="shared" ca="1" si="1"/>
-        <v>286</v>
+        <v>231</v>
       </c>
       <c r="K43">
         <f t="shared" ca="1" si="1"/>
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="L43">
         <f t="shared" ca="1" si="1"/>
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2317,15 +2364,15 @@
       </c>
       <c r="J44">
         <f t="shared" ca="1" si="1"/>
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="K44">
         <f t="shared" ca="1" si="1"/>
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="L44">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2358,15 +2405,15 @@
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="1"/>
-        <v>156</v>
+        <v>316</v>
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="1"/>
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="1"/>
-        <v>335</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2399,15 +2446,15 @@
       </c>
       <c r="J46">
         <f t="shared" ca="1" si="1"/>
-        <v>324</v>
+        <v>263</v>
       </c>
       <c r="K46">
         <f t="shared" ca="1" si="1"/>
-        <v>385</v>
+        <v>202</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="1"/>
-        <v>359</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2440,15 +2487,15 @@
       </c>
       <c r="J47">
         <f t="shared" ca="1" si="1"/>
-        <v>397</v>
+        <v>357</v>
       </c>
       <c r="K47">
         <f t="shared" ca="1" si="1"/>
-        <v>252</v>
+        <v>390</v>
       </c>
       <c r="L47">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2481,15 +2528,15 @@
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="1"/>
-        <v>394</v>
+        <v>231</v>
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="1"/>
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="1"/>
-        <v>261</v>
+        <v>370</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -2522,15 +2569,15 @@
       </c>
       <c r="J49">
         <f t="shared" ca="1" si="1"/>
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="1"/>
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="L49">
         <f t="shared" ca="1" si="1"/>
-        <v>351</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -2563,15 +2610,15 @@
       </c>
       <c r="J50">
         <f t="shared" ca="1" si="1"/>
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="1"/>
-        <v>155</v>
+        <v>363</v>
       </c>
       <c r="L50">
         <f t="shared" ca="1" si="1"/>
-        <v>303</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -2604,15 +2651,15 @@
       </c>
       <c r="J51">
         <f t="shared" ca="1" si="1"/>
-        <v>326</v>
+        <v>217</v>
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="1"/>
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -2645,7 +2692,7 @@
       </c>
       <c r="J52">
         <f t="shared" ca="1" si="1"/>
-        <v>171</v>
+        <v>391</v>
       </c>
       <c r="K52">
         <f t="shared" ca="1" si="1"/>
@@ -2653,7 +2700,7 @@
       </c>
       <c r="L52">
         <f t="shared" ca="1" si="1"/>
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -2686,15 +2733,15 @@
       </c>
       <c r="J53">
         <f t="shared" ca="1" si="1"/>
-        <v>141</v>
+        <v>285</v>
       </c>
       <c r="K53">
         <f t="shared" ca="1" si="1"/>
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="L53">
         <f t="shared" ca="1" si="1"/>
-        <v>311</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -2727,15 +2774,15 @@
       </c>
       <c r="J54">
         <f t="shared" ca="1" si="1"/>
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="K54">
         <f t="shared" ca="1" si="1"/>
-        <v>177</v>
+        <v>382</v>
       </c>
       <c r="L54">
         <f t="shared" ca="1" si="1"/>
-        <v>370</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -2768,15 +2815,15 @@
       </c>
       <c r="J55">
         <f t="shared" ca="1" si="1"/>
-        <v>320</v>
+        <v>374</v>
       </c>
       <c r="K55">
         <f t="shared" ca="1" si="1"/>
-        <v>371</v>
+        <v>219</v>
       </c>
       <c r="L55">
         <f t="shared" ca="1" si="1"/>
-        <v>152</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -2809,15 +2856,15 @@
       </c>
       <c r="J56">
         <f t="shared" ca="1" si="1"/>
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="K56">
         <f t="shared" ca="1" si="1"/>
-        <v>355</v>
+        <v>234</v>
       </c>
       <c r="L56">
         <f t="shared" ca="1" si="1"/>
-        <v>344</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -2850,15 +2897,15 @@
       </c>
       <c r="J57">
         <f t="shared" ca="1" si="1"/>
-        <v>357</v>
+        <v>216</v>
       </c>
       <c r="K57">
         <f t="shared" ca="1" si="1"/>
-        <v>345</v>
+        <v>104</v>
       </c>
       <c r="L57">
         <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <v>274</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -2891,15 +2938,15 @@
       </c>
       <c r="J58">
         <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <v>372</v>
       </c>
       <c r="K58">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>279</v>
       </c>
       <c r="L58">
         <f t="shared" ca="1" si="1"/>
-        <v>358</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -2932,15 +2979,15 @@
       </c>
       <c r="J59">
         <f t="shared" ca="1" si="1"/>
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="K59">
         <f t="shared" ca="1" si="1"/>
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="L59">
         <f t="shared" ca="1" si="1"/>
-        <v>265</v>
+        <v>334</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -2973,15 +3020,15 @@
       </c>
       <c r="J60">
         <f t="shared" ca="1" si="1"/>
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="K60">
         <f t="shared" ca="1" si="1"/>
-        <v>227</v>
+        <v>276</v>
       </c>
       <c r="L60">
         <f t="shared" ca="1" si="1"/>
-        <v>268</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -3014,15 +3061,15 @@
       </c>
       <c r="J61">
         <f t="shared" ca="1" si="1"/>
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="K61">
         <f t="shared" ca="1" si="1"/>
-        <v>111</v>
+        <v>361</v>
       </c>
       <c r="L61">
         <f t="shared" ca="1" si="1"/>
-        <v>350</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -3055,15 +3102,15 @@
       </c>
       <c r="J62">
         <f t="shared" ca="1" si="1"/>
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K62">
         <f t="shared" ca="1" si="1"/>
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="L62">
         <f t="shared" ca="1" si="1"/>
-        <v>102</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -3096,15 +3143,15 @@
       </c>
       <c r="J63">
         <f t="shared" ca="1" si="1"/>
-        <v>240</v>
+        <v>391</v>
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="1"/>
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="L63">
         <f t="shared" ca="1" si="1"/>
-        <v>298</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -3137,15 +3184,15 @@
       </c>
       <c r="J64">
         <f t="shared" ca="1" si="1"/>
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="K64">
         <f t="shared" ca="1" si="1"/>
-        <v>221</v>
+        <v>128</v>
       </c>
       <c r="L64">
         <f t="shared" ca="1" si="1"/>
-        <v>312</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -3178,15 +3225,15 @@
       </c>
       <c r="J65">
         <f t="shared" ca="1" si="1"/>
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="K65">
         <f t="shared" ca="1" si="1"/>
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="L65">
         <f t="shared" ca="1" si="1"/>
-        <v>306</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
@@ -3219,15 +3266,15 @@
       </c>
       <c r="J66">
         <f t="shared" ca="1" si="1"/>
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="K66">
         <f t="shared" ca="1" si="1"/>
-        <v>110</v>
+        <v>394</v>
       </c>
       <c r="L66">
         <f t="shared" ca="1" si="1"/>
-        <v>314</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -3260,15 +3307,15 @@
       </c>
       <c r="J67">
         <f t="shared" ref="J67:L130" ca="1" si="2">RANDBETWEEN(100,400)</f>
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="K67">
         <f t="shared" ca="1" si="2"/>
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L67">
         <f t="shared" ca="1" si="2"/>
-        <v>123</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -3301,15 +3348,15 @@
       </c>
       <c r="J68">
         <f t="shared" ca="1" si="2"/>
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="K68">
         <f t="shared" ca="1" si="2"/>
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="L68">
         <f t="shared" ca="1" si="2"/>
-        <v>317</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -3342,15 +3389,15 @@
       </c>
       <c r="J69">
         <f t="shared" ca="1" si="2"/>
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K69">
         <f t="shared" ca="1" si="2"/>
-        <v>198</v>
+        <v>281</v>
       </c>
       <c r="L69">
         <f t="shared" ca="1" si="2"/>
-        <v>300</v>
+        <v>359</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -3383,15 +3430,15 @@
       </c>
       <c r="J70">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="K70">
         <f t="shared" ca="1" si="2"/>
-        <v>354</v>
+        <v>201</v>
       </c>
       <c r="L70">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -3424,15 +3471,15 @@
       </c>
       <c r="J71">
         <f t="shared" ca="1" si="2"/>
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="K71">
         <f t="shared" ca="1" si="2"/>
-        <v>316</v>
+        <v>392</v>
       </c>
       <c r="L71">
         <f t="shared" ca="1" si="2"/>
-        <v>253</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -3465,15 +3512,15 @@
       </c>
       <c r="J72">
         <f t="shared" ca="1" si="2"/>
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="K72">
         <f t="shared" ca="1" si="2"/>
-        <v>226</v>
+        <v>396</v>
       </c>
       <c r="L72">
         <f t="shared" ca="1" si="2"/>
-        <v>180</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -3506,15 +3553,15 @@
       </c>
       <c r="J73">
         <f t="shared" ca="1" si="2"/>
-        <v>285</v>
+        <v>130</v>
       </c>
       <c r="K73">
         <f t="shared" ca="1" si="2"/>
-        <v>348</v>
+        <v>173</v>
       </c>
       <c r="L73">
         <f t="shared" ca="1" si="2"/>
-        <v>109</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -3547,15 +3594,15 @@
       </c>
       <c r="J74">
         <f t="shared" ca="1" si="2"/>
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="K74">
         <f t="shared" ca="1" si="2"/>
-        <v>345</v>
+        <v>179</v>
       </c>
       <c r="L74">
         <f t="shared" ca="1" si="2"/>
-        <v>357</v>
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -3588,15 +3635,15 @@
       </c>
       <c r="J75">
         <f t="shared" ca="1" si="2"/>
-        <v>234</v>
+        <v>345</v>
       </c>
       <c r="K75">
         <f t="shared" ca="1" si="2"/>
-        <v>390</v>
+        <v>294</v>
       </c>
       <c r="L75">
         <f t="shared" ca="1" si="2"/>
-        <v>263</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -3629,15 +3676,15 @@
       </c>
       <c r="J76">
         <f t="shared" ca="1" si="2"/>
-        <v>110</v>
+        <v>236</v>
       </c>
       <c r="K76">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>363</v>
       </c>
       <c r="L76">
         <f t="shared" ca="1" si="2"/>
-        <v>325</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -3670,15 +3717,15 @@
       </c>
       <c r="J77">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="K77">
         <f t="shared" ca="1" si="2"/>
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="L77">
         <f t="shared" ca="1" si="2"/>
-        <v>285</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
@@ -3711,15 +3758,15 @@
       </c>
       <c r="J78">
         <f t="shared" ca="1" si="2"/>
-        <v>328</v>
+        <v>141</v>
       </c>
       <c r="K78">
         <f t="shared" ca="1" si="2"/>
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="L78">
         <f t="shared" ca="1" si="2"/>
-        <v>180</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
@@ -3752,15 +3799,15 @@
       </c>
       <c r="J79">
         <f t="shared" ca="1" si="2"/>
-        <v>231</v>
+        <v>347</v>
       </c>
       <c r="K79">
         <f t="shared" ca="1" si="2"/>
-        <v>383</v>
+        <v>187</v>
       </c>
       <c r="L79">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
@@ -3793,15 +3840,15 @@
       </c>
       <c r="J80">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="K80">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="L80">
         <f t="shared" ca="1" si="2"/>
-        <v>158</v>
+        <v>133</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
@@ -3834,15 +3881,15 @@
       </c>
       <c r="J81">
         <f t="shared" ca="1" si="2"/>
-        <v>319</v>
+        <v>267</v>
       </c>
       <c r="K81">
         <f t="shared" ca="1" si="2"/>
-        <v>238</v>
+        <v>293</v>
       </c>
       <c r="L81">
         <f t="shared" ca="1" si="2"/>
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -3875,15 +3922,15 @@
       </c>
       <c r="J82">
         <f t="shared" ca="1" si="2"/>
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="K82">
         <f t="shared" ca="1" si="2"/>
-        <v>375</v>
+        <v>108</v>
       </c>
       <c r="L82">
         <f t="shared" ca="1" si="2"/>
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
@@ -3916,15 +3963,15 @@
       </c>
       <c r="J83">
         <f t="shared" ca="1" si="2"/>
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="K83">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>241</v>
       </c>
       <c r="L83">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
@@ -3957,15 +4004,15 @@
       </c>
       <c r="J84">
         <f t="shared" ca="1" si="2"/>
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="K84">
         <f t="shared" ca="1" si="2"/>
-        <v>377</v>
+        <v>144</v>
       </c>
       <c r="L84">
         <f t="shared" ca="1" si="2"/>
-        <v>198</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -3998,15 +4045,15 @@
       </c>
       <c r="J85">
         <f t="shared" ca="1" si="2"/>
-        <v>354</v>
+        <v>125</v>
       </c>
       <c r="K85">
         <f t="shared" ca="1" si="2"/>
-        <v>332</v>
+        <v>209</v>
       </c>
       <c r="L85">
         <f t="shared" ca="1" si="2"/>
-        <v>329</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
@@ -4039,15 +4086,15 @@
       </c>
       <c r="J86">
         <f t="shared" ca="1" si="2"/>
-        <v>239</v>
+        <v>326</v>
       </c>
       <c r="K86">
         <f t="shared" ca="1" si="2"/>
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="L86">
         <f t="shared" ca="1" si="2"/>
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
@@ -4080,15 +4127,15 @@
       </c>
       <c r="J87">
         <f t="shared" ca="1" si="2"/>
-        <v>358</v>
+        <v>289</v>
       </c>
       <c r="K87">
         <f t="shared" ca="1" si="2"/>
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="L87">
         <f t="shared" ca="1" si="2"/>
-        <v>193</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
@@ -4121,15 +4168,15 @@
       </c>
       <c r="J88">
         <f t="shared" ca="1" si="2"/>
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="K88">
         <f t="shared" ca="1" si="2"/>
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="L88">
         <f t="shared" ca="1" si="2"/>
-        <v>360</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
@@ -4162,15 +4209,15 @@
       </c>
       <c r="J89">
         <f t="shared" ca="1" si="2"/>
-        <v>148</v>
+        <v>387</v>
       </c>
       <c r="K89">
         <f t="shared" ca="1" si="2"/>
-        <v>196</v>
+        <v>368</v>
       </c>
       <c r="L89">
         <f t="shared" ca="1" si="2"/>
-        <v>197</v>
+        <v>246</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -4203,15 +4250,15 @@
       </c>
       <c r="J90">
         <f t="shared" ca="1" si="2"/>
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="K90">
         <f t="shared" ca="1" si="2"/>
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="L90">
         <f t="shared" ca="1" si="2"/>
-        <v>284</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
@@ -4244,15 +4291,15 @@
       </c>
       <c r="J91">
         <f t="shared" ca="1" si="2"/>
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="K91">
         <f t="shared" ca="1" si="2"/>
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="L91">
         <f t="shared" ca="1" si="2"/>
-        <v>311</v>
+        <v>368</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
@@ -4285,15 +4332,15 @@
       </c>
       <c r="J92">
         <f t="shared" ca="1" si="2"/>
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="K92">
         <f t="shared" ca="1" si="2"/>
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="L92">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -4326,15 +4373,15 @@
       </c>
       <c r="J93">
         <f t="shared" ca="1" si="2"/>
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K93">
         <f t="shared" ca="1" si="2"/>
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="L93">
         <f t="shared" ca="1" si="2"/>
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
@@ -4367,15 +4414,15 @@
       </c>
       <c r="J94">
         <f t="shared" ca="1" si="2"/>
-        <v>386</v>
+        <v>125</v>
       </c>
       <c r="K94">
         <f t="shared" ca="1" si="2"/>
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="L94">
         <f t="shared" ca="1" si="2"/>
-        <v>146</v>
+        <v>374</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -4408,15 +4455,15 @@
       </c>
       <c r="J95">
         <f t="shared" ca="1" si="2"/>
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="K95">
         <f t="shared" ca="1" si="2"/>
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="L95">
         <f t="shared" ca="1" si="2"/>
-        <v>237</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -4449,15 +4496,15 @@
       </c>
       <c r="J96">
         <f t="shared" ca="1" si="2"/>
-        <v>336</v>
+        <v>126</v>
       </c>
       <c r="K96">
         <f t="shared" ca="1" si="2"/>
-        <v>384</v>
+        <v>183</v>
       </c>
       <c r="L96">
         <f t="shared" ca="1" si="2"/>
-        <v>327</v>
+        <v>165</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -4490,15 +4537,15 @@
       </c>
       <c r="J97">
         <f t="shared" ca="1" si="2"/>
-        <v>113</v>
+        <v>202</v>
       </c>
       <c r="K97">
         <f t="shared" ca="1" si="2"/>
-        <v>397</v>
+        <v>282</v>
       </c>
       <c r="L97">
         <f t="shared" ca="1" si="2"/>
-        <v>355</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -4531,15 +4578,15 @@
       </c>
       <c r="J98">
         <f t="shared" ca="1" si="2"/>
-        <v>358</v>
+        <v>204</v>
       </c>
       <c r="K98">
         <f t="shared" ca="1" si="2"/>
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="L98">
         <f t="shared" ca="1" si="2"/>
-        <v>158</v>
+        <v>358</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -4572,15 +4619,15 @@
       </c>
       <c r="J99">
         <f t="shared" ca="1" si="2"/>
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="K99">
         <f t="shared" ca="1" si="2"/>
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="L99">
         <f t="shared" ca="1" si="2"/>
-        <v>311</v>
+        <v>150</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -4613,15 +4660,15 @@
       </c>
       <c r="J100">
         <f t="shared" ca="1" si="2"/>
-        <v>338</v>
+        <v>121</v>
       </c>
       <c r="K100">
         <f t="shared" ca="1" si="2"/>
-        <v>254</v>
+        <v>367</v>
       </c>
       <c r="L100">
         <f t="shared" ca="1" si="2"/>
-        <v>347</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -4654,15 +4701,15 @@
       </c>
       <c r="J101">
         <f t="shared" ca="1" si="2"/>
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="K101">
         <f t="shared" ca="1" si="2"/>
-        <v>237</v>
+        <v>389</v>
       </c>
       <c r="L101">
         <f t="shared" ca="1" si="2"/>
-        <v>366</v>
+        <v>289</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -4695,15 +4742,15 @@
       </c>
       <c r="J102">
         <f t="shared" ca="1" si="2"/>
-        <v>137</v>
+        <v>364</v>
       </c>
       <c r="K102">
         <f t="shared" ca="1" si="2"/>
-        <v>254</v>
+        <v>139</v>
       </c>
       <c r="L102">
         <f t="shared" ca="1" si="2"/>
-        <v>370</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -4736,15 +4783,15 @@
       </c>
       <c r="J103">
         <f t="shared" ca="1" si="2"/>
-        <v>193</v>
+        <v>358</v>
       </c>
       <c r="K103">
         <f t="shared" ca="1" si="2"/>
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="L103">
         <f t="shared" ca="1" si="2"/>
-        <v>123</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
@@ -4777,15 +4824,15 @@
       </c>
       <c r="J104">
         <f t="shared" ca="1" si="2"/>
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K104">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
+        <v>270</v>
       </c>
       <c r="L104">
         <f t="shared" ca="1" si="2"/>
-        <v>393</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -4818,15 +4865,15 @@
       </c>
       <c r="J105">
         <f t="shared" ca="1" si="2"/>
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="K105">
         <f t="shared" ca="1" si="2"/>
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="L105">
         <f t="shared" ca="1" si="2"/>
-        <v>379</v>
+        <v>142</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -4859,15 +4906,15 @@
       </c>
       <c r="J106">
         <f t="shared" ca="1" si="2"/>
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="K106">
         <f t="shared" ca="1" si="2"/>
-        <v>171</v>
+        <v>264</v>
       </c>
       <c r="L106">
         <f t="shared" ca="1" si="2"/>
-        <v>339</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -4900,15 +4947,15 @@
       </c>
       <c r="J107">
         <f t="shared" ca="1" si="2"/>
-        <v>222</v>
+        <v>103</v>
       </c>
       <c r="K107">
         <f t="shared" ca="1" si="2"/>
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="L107">
         <f t="shared" ca="1" si="2"/>
-        <v>309</v>
+        <v>192</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
@@ -4941,15 +4988,15 @@
       </c>
       <c r="J108">
         <f t="shared" ca="1" si="2"/>
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="K108">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>310</v>
       </c>
       <c r="L108">
         <f t="shared" ca="1" si="2"/>
-        <v>232</v>
+        <v>307</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -4982,15 +5029,15 @@
       </c>
       <c r="J109">
         <f t="shared" ca="1" si="2"/>
-        <v>329</v>
+        <v>144</v>
       </c>
       <c r="K109">
         <f t="shared" ca="1" si="2"/>
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="L109">
         <f t="shared" ca="1" si="2"/>
-        <v>345</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -5023,15 +5070,15 @@
       </c>
       <c r="J110">
         <f t="shared" ca="1" si="2"/>
-        <v>332</v>
+        <v>152</v>
       </c>
       <c r="K110">
         <f t="shared" ca="1" si="2"/>
-        <v>223</v>
+        <v>334</v>
       </c>
       <c r="L110">
         <f t="shared" ca="1" si="2"/>
-        <v>379</v>
+        <v>391</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -5064,15 +5111,15 @@
       </c>
       <c r="J111">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="K111">
         <f t="shared" ca="1" si="2"/>
-        <v>373</v>
+        <v>178</v>
       </c>
       <c r="L111">
         <f t="shared" ca="1" si="2"/>
-        <v>233</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -5105,15 +5152,15 @@
       </c>
       <c r="J112">
         <f t="shared" ca="1" si="2"/>
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="K112">
         <f t="shared" ca="1" si="2"/>
-        <v>347</v>
+        <v>396</v>
       </c>
       <c r="L112">
         <f t="shared" ca="1" si="2"/>
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
@@ -5146,15 +5193,15 @@
       </c>
       <c r="J113">
         <f t="shared" ca="1" si="2"/>
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="K113">
         <f t="shared" ca="1" si="2"/>
-        <v>220</v>
+        <v>358</v>
       </c>
       <c r="L113">
         <f t="shared" ca="1" si="2"/>
-        <v>257</v>
+        <v>214</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
@@ -5187,15 +5234,15 @@
       </c>
       <c r="J114">
         <f t="shared" ca="1" si="2"/>
-        <v>387</v>
+        <v>246</v>
       </c>
       <c r="K114">
         <f t="shared" ca="1" si="2"/>
-        <v>174</v>
+        <v>248</v>
       </c>
       <c r="L114">
         <f t="shared" ca="1" si="2"/>
-        <v>212</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
@@ -5228,15 +5275,15 @@
       </c>
       <c r="J115">
         <f t="shared" ca="1" si="2"/>
-        <v>359</v>
+        <v>132</v>
       </c>
       <c r="K115">
         <f t="shared" ca="1" si="2"/>
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="L115">
         <f t="shared" ca="1" si="2"/>
-        <v>340</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
@@ -5269,15 +5316,15 @@
       </c>
       <c r="J116">
         <f t="shared" ca="1" si="2"/>
-        <v>311</v>
+        <v>225</v>
       </c>
       <c r="K116">
         <f t="shared" ca="1" si="2"/>
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="L116">
         <f t="shared" ca="1" si="2"/>
-        <v>337</v>
+        <v>170</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
@@ -5310,15 +5357,15 @@
       </c>
       <c r="J117">
         <f t="shared" ca="1" si="2"/>
-        <v>153</v>
+        <v>235</v>
       </c>
       <c r="K117">
         <f t="shared" ca="1" si="2"/>
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="L117">
         <f t="shared" ca="1" si="2"/>
-        <v>123</v>
+        <v>334</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
@@ -5351,15 +5398,15 @@
       </c>
       <c r="J118">
         <f t="shared" ca="1" si="2"/>
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="K118">
         <f t="shared" ca="1" si="2"/>
-        <v>387</v>
+        <v>294</v>
       </c>
       <c r="L118">
         <f t="shared" ca="1" si="2"/>
-        <v>268</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
@@ -5392,15 +5439,15 @@
       </c>
       <c r="J119">
         <f t="shared" ca="1" si="2"/>
-        <v>124</v>
+        <v>310</v>
       </c>
       <c r="K119">
         <f t="shared" ca="1" si="2"/>
-        <v>344</v>
+        <v>236</v>
       </c>
       <c r="L119">
         <f t="shared" ca="1" si="2"/>
-        <v>275</v>
+        <v>227</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -5433,15 +5480,15 @@
       </c>
       <c r="J120">
         <f t="shared" ca="1" si="2"/>
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="K120">
         <f t="shared" ca="1" si="2"/>
-        <v>340</v>
+        <v>183</v>
       </c>
       <c r="L120">
         <f t="shared" ca="1" si="2"/>
-        <v>272</v>
+        <v>157</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
@@ -5474,15 +5521,15 @@
       </c>
       <c r="J121">
         <f t="shared" ca="1" si="2"/>
-        <v>234</v>
+        <v>107</v>
       </c>
       <c r="K121">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>337</v>
       </c>
       <c r="L121">
         <f t="shared" ca="1" si="2"/>
-        <v>370</v>
+        <v>221</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -5515,15 +5562,15 @@
       </c>
       <c r="J122">
         <f t="shared" ca="1" si="2"/>
-        <v>140</v>
+        <v>392</v>
       </c>
       <c r="K122">
         <f t="shared" ca="1" si="2"/>
-        <v>200</v>
+        <v>371</v>
       </c>
       <c r="L122">
         <f t="shared" ca="1" si="2"/>
-        <v>387</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -5556,15 +5603,15 @@
       </c>
       <c r="J123">
         <f t="shared" ca="1" si="2"/>
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="K123">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="L123">
         <f t="shared" ca="1" si="2"/>
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -5597,11 +5644,11 @@
       </c>
       <c r="J124">
         <f t="shared" ca="1" si="2"/>
-        <v>108</v>
+        <v>306</v>
       </c>
       <c r="K124">
         <f t="shared" ca="1" si="2"/>
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="L124">
         <f t="shared" ca="1" si="2"/>
@@ -5638,15 +5685,15 @@
       </c>
       <c r="J125">
         <f t="shared" ca="1" si="2"/>
-        <v>114</v>
+        <v>328</v>
       </c>
       <c r="K125">
         <f t="shared" ca="1" si="2"/>
-        <v>252</v>
+        <v>149</v>
       </c>
       <c r="L125">
         <f t="shared" ca="1" si="2"/>
-        <v>284</v>
+        <v>238</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
@@ -5679,15 +5726,15 @@
       </c>
       <c r="J126">
         <f t="shared" ca="1" si="2"/>
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="K126">
         <f t="shared" ca="1" si="2"/>
-        <v>327</v>
+        <v>149</v>
       </c>
       <c r="L126">
         <f t="shared" ca="1" si="2"/>
-        <v>373</v>
+        <v>137</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
@@ -5720,15 +5767,15 @@
       </c>
       <c r="J127">
         <f t="shared" ca="1" si="2"/>
-        <v>346</v>
+        <v>164</v>
       </c>
       <c r="K127">
         <f t="shared" ca="1" si="2"/>
-        <v>108</v>
+        <v>271</v>
       </c>
       <c r="L127">
         <f t="shared" ca="1" si="2"/>
-        <v>111</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
@@ -5761,15 +5808,15 @@
       </c>
       <c r="J128">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="K128">
         <f t="shared" ca="1" si="2"/>
-        <v>106</v>
+        <v>265</v>
       </c>
       <c r="L128">
         <f t="shared" ca="1" si="2"/>
-        <v>264</v>
+        <v>347</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
@@ -5802,15 +5849,15 @@
       </c>
       <c r="J129">
         <f t="shared" ca="1" si="2"/>
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K129">
         <f t="shared" ca="1" si="2"/>
-        <v>277</v>
+        <v>381</v>
       </c>
       <c r="L129">
         <f t="shared" ca="1" si="2"/>
-        <v>368</v>
+        <v>352</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -5843,15 +5890,15 @@
       </c>
       <c r="J130">
         <f t="shared" ca="1" si="2"/>
-        <v>357</v>
+        <v>205</v>
       </c>
       <c r="K130">
         <f t="shared" ca="1" si="2"/>
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="L130">
         <f t="shared" ca="1" si="2"/>
-        <v>117</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
@@ -5884,15 +5931,15 @@
       </c>
       <c r="J131">
         <f t="shared" ref="J131:L194" ca="1" si="3">RANDBETWEEN(100,400)</f>
-        <v>139</v>
+        <v>347</v>
       </c>
       <c r="K131">
         <f t="shared" ca="1" si="3"/>
-        <v>335</v>
+        <v>155</v>
       </c>
       <c r="L131">
         <f t="shared" ca="1" si="3"/>
-        <v>148</v>
+        <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -5925,15 +5972,15 @@
       </c>
       <c r="J132">
         <f t="shared" ca="1" si="3"/>
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="K132">
         <f t="shared" ca="1" si="3"/>
-        <v>312</v>
+        <v>167</v>
       </c>
       <c r="L132">
         <f t="shared" ca="1" si="3"/>
-        <v>165</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
@@ -5966,15 +6013,15 @@
       </c>
       <c r="J133">
         <f t="shared" ca="1" si="3"/>
-        <v>395</v>
+        <v>109</v>
       </c>
       <c r="K133">
         <f t="shared" ca="1" si="3"/>
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="L133">
         <f t="shared" ca="1" si="3"/>
-        <v>179</v>
+        <v>251</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -6007,15 +6054,15 @@
       </c>
       <c r="J134">
         <f t="shared" ca="1" si="3"/>
-        <v>272</v>
+        <v>359</v>
       </c>
       <c r="K134">
         <f t="shared" ca="1" si="3"/>
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="L134">
         <f t="shared" ca="1" si="3"/>
-        <v>314</v>
+        <v>144</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
@@ -6048,15 +6095,15 @@
       </c>
       <c r="J135">
         <f t="shared" ca="1" si="3"/>
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="K135">
         <f t="shared" ca="1" si="3"/>
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="L135">
         <f t="shared" ca="1" si="3"/>
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -6089,15 +6136,15 @@
       </c>
       <c r="J136">
         <f t="shared" ca="1" si="3"/>
-        <v>139</v>
+        <v>394</v>
       </c>
       <c r="K136">
         <f t="shared" ca="1" si="3"/>
-        <v>308</v>
+        <v>246</v>
       </c>
       <c r="L136">
         <f t="shared" ca="1" si="3"/>
-        <v>165</v>
+        <v>178</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
@@ -6130,15 +6177,15 @@
       </c>
       <c r="J137">
         <f t="shared" ca="1" si="3"/>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K137">
         <f t="shared" ca="1" si="3"/>
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="L137">
         <f t="shared" ca="1" si="3"/>
-        <v>226</v>
+        <v>314</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
@@ -6171,15 +6218,15 @@
       </c>
       <c r="J138">
         <f t="shared" ca="1" si="3"/>
-        <v>298</v>
+        <v>158</v>
       </c>
       <c r="K138">
         <f t="shared" ca="1" si="3"/>
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="L138">
         <f t="shared" ca="1" si="3"/>
-        <v>277</v>
+        <v>128</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
@@ -6212,15 +6259,15 @@
       </c>
       <c r="J139">
         <f t="shared" ca="1" si="3"/>
-        <v>380</v>
+        <v>144</v>
       </c>
       <c r="K139">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>354</v>
       </c>
       <c r="L139">
         <f t="shared" ca="1" si="3"/>
-        <v>371</v>
+        <v>211</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -6253,15 +6300,15 @@
       </c>
       <c r="J140">
         <f t="shared" ca="1" si="3"/>
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="K140">
         <f t="shared" ca="1" si="3"/>
-        <v>220</v>
+        <v>125</v>
       </c>
       <c r="L140">
         <f t="shared" ca="1" si="3"/>
-        <v>297</v>
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
@@ -6294,15 +6341,15 @@
       </c>
       <c r="J141">
         <f t="shared" ca="1" si="3"/>
-        <v>303</v>
+        <v>150</v>
       </c>
       <c r="K141">
         <f t="shared" ca="1" si="3"/>
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="L141">
         <f t="shared" ca="1" si="3"/>
-        <v>375</v>
+        <v>240</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
@@ -6335,15 +6382,15 @@
       </c>
       <c r="J142">
         <f t="shared" ca="1" si="3"/>
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K142">
         <f t="shared" ca="1" si="3"/>
-        <v>116</v>
+        <v>375</v>
       </c>
       <c r="L142">
         <f t="shared" ca="1" si="3"/>
-        <v>222</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -6376,15 +6423,15 @@
       </c>
       <c r="J143">
         <f t="shared" ca="1" si="3"/>
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="K143">
         <f t="shared" ca="1" si="3"/>
-        <v>182</v>
+        <v>239</v>
       </c>
       <c r="L143">
         <f t="shared" ca="1" si="3"/>
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -6417,15 +6464,15 @@
       </c>
       <c r="J144">
         <f t="shared" ca="1" si="3"/>
-        <v>342</v>
+        <v>239</v>
       </c>
       <c r="K144">
         <f t="shared" ca="1" si="3"/>
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="L144">
         <f t="shared" ca="1" si="3"/>
-        <v>135</v>
+        <v>374</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -6458,15 +6505,15 @@
       </c>
       <c r="J145">
         <f t="shared" ca="1" si="3"/>
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="K145">
         <f t="shared" ca="1" si="3"/>
-        <v>332</v>
+        <v>162</v>
       </c>
       <c r="L145">
         <f t="shared" ca="1" si="3"/>
-        <v>270</v>
+        <v>306</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
@@ -6499,15 +6546,15 @@
       </c>
       <c r="J146">
         <f t="shared" ca="1" si="3"/>
-        <v>389</v>
+        <v>174</v>
       </c>
       <c r="K146">
         <f t="shared" ca="1" si="3"/>
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="L146">
         <f t="shared" ca="1" si="3"/>
-        <v>106</v>
+        <v>185</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -6540,15 +6587,15 @@
       </c>
       <c r="J147">
         <f t="shared" ca="1" si="3"/>
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="K147">
         <f t="shared" ca="1" si="3"/>
-        <v>225</v>
+        <v>395</v>
       </c>
       <c r="L147">
         <f t="shared" ca="1" si="3"/>
-        <v>144</v>
+        <v>229</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -6581,15 +6628,15 @@
       </c>
       <c r="J148">
         <f t="shared" ca="1" si="3"/>
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="K148">
         <f t="shared" ca="1" si="3"/>
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="L148">
         <f t="shared" ca="1" si="3"/>
-        <v>161</v>
+        <v>357</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -6622,15 +6669,15 @@
       </c>
       <c r="J149">
         <f t="shared" ca="1" si="3"/>
-        <v>376</v>
+        <v>163</v>
       </c>
       <c r="K149">
         <f t="shared" ca="1" si="3"/>
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="L149">
         <f t="shared" ca="1" si="3"/>
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -6663,15 +6710,15 @@
       </c>
       <c r="J150">
         <f t="shared" ca="1" si="3"/>
-        <v>108</v>
+        <v>381</v>
       </c>
       <c r="K150">
         <f t="shared" ca="1" si="3"/>
-        <v>204</v>
+        <v>400</v>
       </c>
       <c r="L150">
         <f t="shared" ca="1" si="3"/>
-        <v>352</v>
+        <v>112</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -6704,15 +6751,15 @@
       </c>
       <c r="J151">
         <f t="shared" ca="1" si="3"/>
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="K151">
         <f t="shared" ca="1" si="3"/>
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="L151">
         <f t="shared" ca="1" si="3"/>
-        <v>105</v>
+        <v>388</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -6745,15 +6792,15 @@
       </c>
       <c r="J152">
         <f t="shared" ca="1" si="3"/>
-        <v>350</v>
+        <v>174</v>
       </c>
       <c r="K152">
         <f t="shared" ca="1" si="3"/>
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="L152">
         <f t="shared" ca="1" si="3"/>
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
@@ -6786,15 +6833,15 @@
       </c>
       <c r="J153">
         <f t="shared" ca="1" si="3"/>
-        <v>392</v>
+        <v>290</v>
       </c>
       <c r="K153">
         <f t="shared" ca="1" si="3"/>
-        <v>390</v>
+        <v>262</v>
       </c>
       <c r="L153">
         <f t="shared" ca="1" si="3"/>
-        <v>172</v>
+        <v>217</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -6827,15 +6874,15 @@
       </c>
       <c r="J154">
         <f t="shared" ca="1" si="3"/>
-        <v>307</v>
+        <v>179</v>
       </c>
       <c r="K154">
         <f t="shared" ca="1" si="3"/>
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="L154">
         <f t="shared" ca="1" si="3"/>
-        <v>114</v>
+        <v>375</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
@@ -6868,15 +6915,15 @@
       </c>
       <c r="J155">
         <f t="shared" ca="1" si="3"/>
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="K155">
         <f t="shared" ca="1" si="3"/>
-        <v>122</v>
+        <v>279</v>
       </c>
       <c r="L155">
         <f t="shared" ca="1" si="3"/>
-        <v>173</v>
+        <v>361</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
@@ -6909,15 +6956,15 @@
       </c>
       <c r="J156">
         <f t="shared" ca="1" si="3"/>
-        <v>179</v>
+        <v>322</v>
       </c>
       <c r="K156">
         <f t="shared" ca="1" si="3"/>
-        <v>298</v>
+        <v>212</v>
       </c>
       <c r="L156">
         <f t="shared" ca="1" si="3"/>
-        <v>199</v>
+        <v>347</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
@@ -6950,15 +6997,15 @@
       </c>
       <c r="J157">
         <f t="shared" ca="1" si="3"/>
-        <v>368</v>
+        <v>330</v>
       </c>
       <c r="K157">
         <f t="shared" ca="1" si="3"/>
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="L157">
         <f t="shared" ca="1" si="3"/>
-        <v>308</v>
+        <v>226</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
@@ -6991,15 +7038,15 @@
       </c>
       <c r="J158">
         <f t="shared" ca="1" si="3"/>
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="K158">
         <f t="shared" ca="1" si="3"/>
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="L158">
         <f t="shared" ca="1" si="3"/>
-        <v>201</v>
+        <v>378</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
@@ -7032,15 +7079,15 @@
       </c>
       <c r="J159">
         <f t="shared" ca="1" si="3"/>
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="K159">
         <f t="shared" ca="1" si="3"/>
-        <v>344</v>
+        <v>111</v>
       </c>
       <c r="L159">
         <f t="shared" ca="1" si="3"/>
-        <v>307</v>
+        <v>364</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
@@ -7073,15 +7120,15 @@
       </c>
       <c r="J160">
         <f t="shared" ca="1" si="3"/>
-        <v>187</v>
+        <v>314</v>
       </c>
       <c r="K160">
         <f t="shared" ca="1" si="3"/>
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="L160">
         <f t="shared" ca="1" si="3"/>
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
@@ -7114,15 +7161,15 @@
       </c>
       <c r="J161">
         <f t="shared" ca="1" si="3"/>
-        <v>387</v>
+        <v>190</v>
       </c>
       <c r="K161">
         <f t="shared" ca="1" si="3"/>
-        <v>331</v>
+        <v>397</v>
       </c>
       <c r="L161">
         <f t="shared" ca="1" si="3"/>
-        <v>124</v>
+        <v>191</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -7155,15 +7202,15 @@
       </c>
       <c r="J162">
         <f t="shared" ca="1" si="3"/>
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="K162">
         <f t="shared" ca="1" si="3"/>
-        <v>378</v>
+        <v>240</v>
       </c>
       <c r="L162">
         <f t="shared" ca="1" si="3"/>
-        <v>155</v>
+        <v>248</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
@@ -7196,15 +7243,15 @@
       </c>
       <c r="J163">
         <f t="shared" ca="1" si="3"/>
-        <v>131</v>
+        <v>251</v>
       </c>
       <c r="K163">
         <f t="shared" ca="1" si="3"/>
-        <v>251</v>
+        <v>334</v>
       </c>
       <c r="L163">
         <f t="shared" ca="1" si="3"/>
-        <v>265</v>
+        <v>146</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
@@ -7237,15 +7284,15 @@
       </c>
       <c r="J164">
         <f t="shared" ca="1" si="3"/>
-        <v>364</v>
+        <v>168</v>
       </c>
       <c r="K164">
         <f t="shared" ca="1" si="3"/>
-        <v>342</v>
+        <v>252</v>
       </c>
       <c r="L164">
         <f t="shared" ca="1" si="3"/>
-        <v>286</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
@@ -7278,15 +7325,15 @@
       </c>
       <c r="J165">
         <f t="shared" ca="1" si="3"/>
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="K165">
         <f t="shared" ca="1" si="3"/>
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L165">
         <f t="shared" ca="1" si="3"/>
-        <v>327</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
@@ -7319,15 +7366,15 @@
       </c>
       <c r="J166">
         <f t="shared" ca="1" si="3"/>
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="K166">
         <f t="shared" ca="1" si="3"/>
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="L166">
         <f t="shared" ca="1" si="3"/>
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
@@ -7360,15 +7407,15 @@
       </c>
       <c r="J167">
         <f t="shared" ca="1" si="3"/>
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="K167">
         <f t="shared" ca="1" si="3"/>
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="L167">
         <f t="shared" ca="1" si="3"/>
-        <v>138</v>
+        <v>160</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
@@ -7401,15 +7448,15 @@
       </c>
       <c r="J168">
         <f t="shared" ca="1" si="3"/>
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="K168">
         <f t="shared" ca="1" si="3"/>
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="L168">
         <f t="shared" ca="1" si="3"/>
-        <v>375</v>
+        <v>176</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -7442,15 +7489,15 @@
       </c>
       <c r="J169">
         <f t="shared" ca="1" si="3"/>
-        <v>139</v>
+        <v>389</v>
       </c>
       <c r="K169">
         <f t="shared" ca="1" si="3"/>
-        <v>317</v>
+        <v>156</v>
       </c>
       <c r="L169">
         <f t="shared" ca="1" si="3"/>
-        <v>394</v>
+        <v>118</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
@@ -7483,15 +7530,15 @@
       </c>
       <c r="J170">
         <f t="shared" ca="1" si="3"/>
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="K170">
         <f t="shared" ca="1" si="3"/>
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="L170">
         <f t="shared" ca="1" si="3"/>
-        <v>141</v>
+        <v>299</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -7524,15 +7571,15 @@
       </c>
       <c r="J171">
         <f t="shared" ca="1" si="3"/>
-        <v>335</v>
+        <v>293</v>
       </c>
       <c r="K171">
         <f t="shared" ca="1" si="3"/>
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="L171">
         <f t="shared" ca="1" si="3"/>
-        <v>352</v>
+        <v>325</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -7565,15 +7612,15 @@
       </c>
       <c r="J172">
         <f t="shared" ca="1" si="3"/>
-        <v>124</v>
+        <v>290</v>
       </c>
       <c r="K172">
         <f t="shared" ca="1" si="3"/>
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="L172">
         <f t="shared" ca="1" si="3"/>
-        <v>307</v>
+        <v>177</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
@@ -7606,15 +7653,15 @@
       </c>
       <c r="J173">
         <f t="shared" ca="1" si="3"/>
-        <v>343</v>
+        <v>165</v>
       </c>
       <c r="K173">
         <f t="shared" ca="1" si="3"/>
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="L173">
         <f t="shared" ca="1" si="3"/>
-        <v>348</v>
+        <v>178</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
@@ -7647,15 +7694,15 @@
       </c>
       <c r="J174">
         <f t="shared" ca="1" si="3"/>
-        <v>227</v>
+        <v>267</v>
       </c>
       <c r="K174">
         <f t="shared" ca="1" si="3"/>
-        <v>363</v>
+        <v>179</v>
       </c>
       <c r="L174">
         <f t="shared" ca="1" si="3"/>
-        <v>229</v>
+        <v>158</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
@@ -7688,15 +7735,15 @@
       </c>
       <c r="J175">
         <f t="shared" ca="1" si="3"/>
-        <v>372</v>
+        <v>224</v>
       </c>
       <c r="K175">
         <f t="shared" ca="1" si="3"/>
-        <v>246</v>
+        <v>329</v>
       </c>
       <c r="L175">
         <f t="shared" ca="1" si="3"/>
-        <v>363</v>
+        <v>131</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
@@ -7729,15 +7776,15 @@
       </c>
       <c r="J176">
         <f t="shared" ca="1" si="3"/>
-        <v>278</v>
+        <v>125</v>
       </c>
       <c r="K176">
         <f t="shared" ca="1" si="3"/>
-        <v>321</v>
+        <v>122</v>
       </c>
       <c r="L176">
         <f t="shared" ca="1" si="3"/>
-        <v>317</v>
+        <v>160</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
@@ -7770,15 +7817,15 @@
       </c>
       <c r="J177">
         <f t="shared" ca="1" si="3"/>
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K177">
         <f t="shared" ca="1" si="3"/>
-        <v>366</v>
+        <v>182</v>
       </c>
       <c r="L177">
         <f t="shared" ca="1" si="3"/>
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
@@ -7811,15 +7858,15 @@
       </c>
       <c r="J178">
         <f t="shared" ca="1" si="3"/>
-        <v>319</v>
+        <v>391</v>
       </c>
       <c r="K178">
         <f t="shared" ca="1" si="3"/>
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="L178">
         <f t="shared" ca="1" si="3"/>
-        <v>146</v>
+        <v>213</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
@@ -7852,15 +7899,15 @@
       </c>
       <c r="J179">
         <f t="shared" ca="1" si="3"/>
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="K179">
         <f t="shared" ca="1" si="3"/>
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="L179">
         <f t="shared" ca="1" si="3"/>
-        <v>106</v>
+        <v>288</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -7893,15 +7940,15 @@
       </c>
       <c r="J180">
         <f t="shared" ca="1" si="3"/>
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="K180">
         <f t="shared" ca="1" si="3"/>
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="L180">
         <f t="shared" ca="1" si="3"/>
-        <v>373</v>
+        <v>202</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -7934,15 +7981,15 @@
       </c>
       <c r="J181">
         <f t="shared" ca="1" si="3"/>
-        <v>374</v>
+        <v>158</v>
       </c>
       <c r="K181">
         <f t="shared" ca="1" si="3"/>
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="L181">
         <f t="shared" ca="1" si="3"/>
-        <v>381</v>
+        <v>329</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -7975,15 +8022,15 @@
       </c>
       <c r="J182">
         <f t="shared" ca="1" si="3"/>
-        <v>346</v>
+        <v>189</v>
       </c>
       <c r="K182">
         <f t="shared" ca="1" si="3"/>
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="L182">
         <f t="shared" ca="1" si="3"/>
-        <v>194</v>
+        <v>317</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
@@ -8016,15 +8063,15 @@
       </c>
       <c r="J183">
         <f t="shared" ca="1" si="3"/>
-        <v>225</v>
+        <v>389</v>
       </c>
       <c r="K183">
         <f t="shared" ca="1" si="3"/>
-        <v>339</v>
+        <v>131</v>
       </c>
       <c r="L183">
         <f t="shared" ca="1" si="3"/>
-        <v>284</v>
+        <v>148</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
@@ -8057,15 +8104,15 @@
       </c>
       <c r="J184">
         <f t="shared" ca="1" si="3"/>
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="K184">
         <f t="shared" ca="1" si="3"/>
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="L184">
         <f t="shared" ca="1" si="3"/>
-        <v>163</v>
+        <v>226</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
@@ -8098,15 +8145,15 @@
       </c>
       <c r="J185">
         <f t="shared" ca="1" si="3"/>
-        <v>134</v>
+        <v>215</v>
       </c>
       <c r="K185">
         <f t="shared" ca="1" si="3"/>
-        <v>196</v>
+        <v>333</v>
       </c>
       <c r="L185">
         <f t="shared" ca="1" si="3"/>
-        <v>158</v>
+        <v>305</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
@@ -8139,15 +8186,15 @@
       </c>
       <c r="J186">
         <f t="shared" ca="1" si="3"/>
-        <v>387</v>
+        <v>114</v>
       </c>
       <c r="K186">
         <f t="shared" ca="1" si="3"/>
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="L186">
         <f t="shared" ca="1" si="3"/>
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
@@ -8180,15 +8227,15 @@
       </c>
       <c r="J187">
         <f t="shared" ca="1" si="3"/>
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="K187">
         <f t="shared" ca="1" si="3"/>
-        <v>249</v>
+        <v>371</v>
       </c>
       <c r="L187">
         <f t="shared" ca="1" si="3"/>
-        <v>170</v>
+        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
@@ -8221,15 +8268,15 @@
       </c>
       <c r="J188">
         <f t="shared" ca="1" si="3"/>
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="K188">
         <f t="shared" ca="1" si="3"/>
-        <v>211</v>
+        <v>389</v>
       </c>
       <c r="L188">
         <f t="shared" ca="1" si="3"/>
-        <v>271</v>
+        <v>314</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
@@ -8262,15 +8309,15 @@
       </c>
       <c r="J189">
         <f t="shared" ca="1" si="3"/>
-        <v>260</v>
+        <v>398</v>
       </c>
       <c r="K189">
         <f t="shared" ca="1" si="3"/>
-        <v>167</v>
+        <v>369</v>
       </c>
       <c r="L189">
         <f t="shared" ca="1" si="3"/>
-        <v>243</v>
+        <v>137</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
@@ -8303,15 +8350,15 @@
       </c>
       <c r="J190">
         <f t="shared" ca="1" si="3"/>
-        <v>195</v>
+        <v>265</v>
       </c>
       <c r="K190">
         <f t="shared" ca="1" si="3"/>
-        <v>154</v>
+        <v>272</v>
       </c>
       <c r="L190">
         <f t="shared" ca="1" si="3"/>
-        <v>328</v>
+        <v>260</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
@@ -8344,15 +8391,15 @@
       </c>
       <c r="J191">
         <f t="shared" ca="1" si="3"/>
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="K191">
         <f t="shared" ca="1" si="3"/>
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L191">
         <f t="shared" ca="1" si="3"/>
-        <v>299</v>
+        <v>151</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
@@ -8385,15 +8432,15 @@
       </c>
       <c r="J192">
         <f t="shared" ca="1" si="3"/>
-        <v>253</v>
+        <v>183</v>
       </c>
       <c r="K192">
         <f t="shared" ca="1" si="3"/>
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="L192">
         <f t="shared" ca="1" si="3"/>
-        <v>342</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
@@ -8426,11 +8473,11 @@
       </c>
       <c r="J193">
         <f t="shared" ca="1" si="3"/>
-        <v>361</v>
+        <v>194</v>
       </c>
       <c r="K193">
         <f t="shared" ca="1" si="3"/>
-        <v>308</v>
+        <v>130</v>
       </c>
       <c r="L193">
         <f t="shared" ca="1" si="3"/>
@@ -8467,15 +8514,15 @@
       </c>
       <c r="J194">
         <f t="shared" ca="1" si="3"/>
-        <v>201</v>
+        <v>112</v>
       </c>
       <c r="K194">
         <f t="shared" ca="1" si="3"/>
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="L194">
         <f t="shared" ca="1" si="3"/>
-        <v>397</v>
+        <v>332</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
@@ -8508,15 +8555,15 @@
       </c>
       <c r="J195">
         <f t="shared" ref="J195:L258" ca="1" si="4">RANDBETWEEN(100,400)</f>
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="K195">
         <f t="shared" ca="1" si="4"/>
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="L195">
         <f t="shared" ca="1" si="4"/>
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
@@ -8549,15 +8596,15 @@
       </c>
       <c r="J196">
         <f t="shared" ca="1" si="4"/>
-        <v>129</v>
+        <v>234</v>
       </c>
       <c r="K196">
         <f t="shared" ca="1" si="4"/>
-        <v>349</v>
+        <v>140</v>
       </c>
       <c r="L196">
         <f t="shared" ca="1" si="4"/>
-        <v>150</v>
+        <v>267</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
@@ -8590,15 +8637,15 @@
       </c>
       <c r="J197">
         <f t="shared" ca="1" si="4"/>
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="K197">
         <f t="shared" ca="1" si="4"/>
-        <v>124</v>
+        <v>357</v>
       </c>
       <c r="L197">
         <f t="shared" ca="1" si="4"/>
-        <v>332</v>
+        <v>216</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
@@ -8631,15 +8678,15 @@
       </c>
       <c r="J198">
         <f t="shared" ca="1" si="4"/>
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="K198">
         <f t="shared" ca="1" si="4"/>
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="L198">
         <f t="shared" ca="1" si="4"/>
-        <v>238</v>
+        <v>191</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -8672,15 +8719,15 @@
       </c>
       <c r="J199">
         <f t="shared" ca="1" si="4"/>
-        <v>354</v>
+        <v>252</v>
       </c>
       <c r="K199">
         <f t="shared" ca="1" si="4"/>
-        <v>369</v>
+        <v>300</v>
       </c>
       <c r="L199">
         <f t="shared" ca="1" si="4"/>
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -8713,15 +8760,15 @@
       </c>
       <c r="J200">
         <f t="shared" ca="1" si="4"/>
-        <v>230</v>
+        <v>372</v>
       </c>
       <c r="K200">
         <f t="shared" ca="1" si="4"/>
-        <v>239</v>
+        <v>130</v>
       </c>
       <c r="L200">
         <f t="shared" ca="1" si="4"/>
-        <v>301</v>
+        <v>393</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -8754,15 +8801,15 @@
       </c>
       <c r="J201">
         <f t="shared" ca="1" si="4"/>
-        <v>230</v>
+        <v>342</v>
       </c>
       <c r="K201">
         <f t="shared" ca="1" si="4"/>
-        <v>337</v>
+        <v>149</v>
       </c>
       <c r="L201">
         <f t="shared" ca="1" si="4"/>
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
@@ -8795,15 +8842,15 @@
       </c>
       <c r="J202">
         <f t="shared" ca="1" si="4"/>
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K202">
         <f t="shared" ca="1" si="4"/>
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="L202">
         <f t="shared" ca="1" si="4"/>
-        <v>209</v>
+        <v>311</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
@@ -8836,15 +8883,15 @@
       </c>
       <c r="J203">
         <f t="shared" ca="1" si="4"/>
-        <v>380</v>
+        <v>202</v>
       </c>
       <c r="K203">
         <f t="shared" ca="1" si="4"/>
-        <v>139</v>
+        <v>327</v>
       </c>
       <c r="L203">
         <f t="shared" ca="1" si="4"/>
-        <v>330</v>
+        <v>258</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
@@ -8877,15 +8924,15 @@
       </c>
       <c r="J204">
         <f t="shared" ca="1" si="4"/>
-        <v>266</v>
+        <v>110</v>
       </c>
       <c r="K204">
         <f t="shared" ca="1" si="4"/>
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="L204">
         <f t="shared" ca="1" si="4"/>
-        <v>237</v>
+        <v>269</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
@@ -8918,15 +8965,15 @@
       </c>
       <c r="J205">
         <f t="shared" ca="1" si="4"/>
-        <v>124</v>
+        <v>242</v>
       </c>
       <c r="K205">
         <f t="shared" ca="1" si="4"/>
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="L205">
         <f t="shared" ca="1" si="4"/>
-        <v>126</v>
+        <v>375</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
@@ -8959,15 +9006,15 @@
       </c>
       <c r="J206">
         <f t="shared" ca="1" si="4"/>
-        <v>291</v>
+        <v>232</v>
       </c>
       <c r="K206">
         <f t="shared" ca="1" si="4"/>
-        <v>289</v>
+        <v>341</v>
       </c>
       <c r="L206">
         <f t="shared" ca="1" si="4"/>
-        <v>319</v>
+        <v>266</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
@@ -9000,15 +9047,15 @@
       </c>
       <c r="J207">
         <f t="shared" ca="1" si="4"/>
-        <v>207</v>
+        <v>323</v>
       </c>
       <c r="K207">
         <f t="shared" ca="1" si="4"/>
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="L207">
         <f t="shared" ca="1" si="4"/>
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
@@ -9041,15 +9088,15 @@
       </c>
       <c r="J208">
         <f t="shared" ca="1" si="4"/>
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="K208">
         <f t="shared" ca="1" si="4"/>
-        <v>275</v>
+        <v>149</v>
       </c>
       <c r="L208">
         <f t="shared" ca="1" si="4"/>
-        <v>122</v>
+        <v>296</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
@@ -9082,15 +9129,15 @@
       </c>
       <c r="J209">
         <f t="shared" ca="1" si="4"/>
-        <v>102</v>
+        <v>270</v>
       </c>
       <c r="K209">
         <f t="shared" ca="1" si="4"/>
-        <v>171</v>
+        <v>365</v>
       </c>
       <c r="L209">
         <f t="shared" ca="1" si="4"/>
-        <v>234</v>
+        <v>313</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
@@ -9123,15 +9170,15 @@
       </c>
       <c r="J210">
         <f t="shared" ca="1" si="4"/>
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="K210">
         <f t="shared" ca="1" si="4"/>
-        <v>383</v>
+        <v>184</v>
       </c>
       <c r="L210">
         <f t="shared" ca="1" si="4"/>
-        <v>250</v>
+        <v>108</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
@@ -9164,15 +9211,15 @@
       </c>
       <c r="J211">
         <f t="shared" ca="1" si="4"/>
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K211">
         <f t="shared" ca="1" si="4"/>
-        <v>399</v>
+        <v>133</v>
       </c>
       <c r="L211">
         <f t="shared" ca="1" si="4"/>
-        <v>114</v>
+        <v>396</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
@@ -9205,15 +9252,15 @@
       </c>
       <c r="J212">
         <f t="shared" ca="1" si="4"/>
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="K212">
         <f t="shared" ca="1" si="4"/>
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="L212">
         <f t="shared" ca="1" si="4"/>
-        <v>297</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
@@ -9246,15 +9293,15 @@
       </c>
       <c r="J213">
         <f t="shared" ca="1" si="4"/>
-        <v>263</v>
+        <v>128</v>
       </c>
       <c r="K213">
         <f t="shared" ca="1" si="4"/>
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L213">
         <f t="shared" ca="1" si="4"/>
-        <v>207</v>
+        <v>307</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
@@ -9287,15 +9334,15 @@
       </c>
       <c r="J214">
         <f t="shared" ca="1" si="4"/>
-        <v>171</v>
+        <v>274</v>
       </c>
       <c r="K214">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="L214">
         <f t="shared" ca="1" si="4"/>
-        <v>125</v>
+        <v>365</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
@@ -9328,15 +9375,15 @@
       </c>
       <c r="J215">
         <f t="shared" ca="1" si="4"/>
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="K215">
         <f t="shared" ca="1" si="4"/>
-        <v>220</v>
+        <v>384</v>
       </c>
       <c r="L215">
         <f t="shared" ca="1" si="4"/>
-        <v>200</v>
+        <v>357</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
@@ -9369,15 +9416,15 @@
       </c>
       <c r="J216">
         <f t="shared" ca="1" si="4"/>
-        <v>145</v>
+        <v>334</v>
       </c>
       <c r="K216">
         <f t="shared" ca="1" si="4"/>
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="L216">
         <f t="shared" ca="1" si="4"/>
-        <v>256</v>
+        <v>156</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
@@ -9410,15 +9457,15 @@
       </c>
       <c r="J217">
         <f t="shared" ca="1" si="4"/>
-        <v>109</v>
+        <v>392</v>
       </c>
       <c r="K217">
         <f t="shared" ca="1" si="4"/>
-        <v>384</v>
+        <v>299</v>
       </c>
       <c r="L217">
         <f t="shared" ca="1" si="4"/>
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
@@ -9451,15 +9498,15 @@
       </c>
       <c r="J218">
         <f t="shared" ca="1" si="4"/>
-        <v>355</v>
+        <v>236</v>
       </c>
       <c r="K218">
         <f t="shared" ca="1" si="4"/>
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="L218">
         <f t="shared" ca="1" si="4"/>
-        <v>123</v>
+        <v>259</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
@@ -9492,15 +9539,15 @@
       </c>
       <c r="J219">
         <f t="shared" ca="1" si="4"/>
-        <v>213</v>
+        <v>357</v>
       </c>
       <c r="K219">
         <f t="shared" ca="1" si="4"/>
-        <v>129</v>
+        <v>267</v>
       </c>
       <c r="L219">
         <f t="shared" ca="1" si="4"/>
-        <v>165</v>
+        <v>202</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
@@ -9533,15 +9580,15 @@
       </c>
       <c r="J220">
         <f t="shared" ca="1" si="4"/>
-        <v>390</v>
+        <v>217</v>
       </c>
       <c r="K220">
         <f t="shared" ca="1" si="4"/>
-        <v>314</v>
+        <v>245</v>
       </c>
       <c r="L220">
         <f t="shared" ca="1" si="4"/>
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
@@ -9574,15 +9621,15 @@
       </c>
       <c r="J221">
         <f t="shared" ca="1" si="4"/>
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="K221">
         <f t="shared" ca="1" si="4"/>
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="L221">
         <f t="shared" ca="1" si="4"/>
-        <v>203</v>
+        <v>348</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
@@ -9615,15 +9662,15 @@
       </c>
       <c r="J222">
         <f t="shared" ca="1" si="4"/>
-        <v>318</v>
+        <v>385</v>
       </c>
       <c r="K222">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>136</v>
       </c>
       <c r="L222">
         <f t="shared" ca="1" si="4"/>
-        <v>263</v>
+        <v>229</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
@@ -9656,15 +9703,15 @@
       </c>
       <c r="J223">
         <f t="shared" ca="1" si="4"/>
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="K223">
         <f t="shared" ca="1" si="4"/>
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="L223">
         <f t="shared" ca="1" si="4"/>
-        <v>237</v>
+        <v>214</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
@@ -9697,15 +9744,15 @@
       </c>
       <c r="J224">
         <f t="shared" ca="1" si="4"/>
-        <v>272</v>
+        <v>122</v>
       </c>
       <c r="K224">
         <f t="shared" ca="1" si="4"/>
-        <v>392</v>
+        <v>201</v>
       </c>
       <c r="L224">
         <f t="shared" ca="1" si="4"/>
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
@@ -9738,15 +9785,15 @@
       </c>
       <c r="J225">
         <f t="shared" ca="1" si="4"/>
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="K225">
         <f t="shared" ca="1" si="4"/>
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="L225">
         <f t="shared" ca="1" si="4"/>
-        <v>350</v>
+        <v>100</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
@@ -9779,15 +9826,15 @@
       </c>
       <c r="J226">
         <f t="shared" ca="1" si="4"/>
-        <v>266</v>
+        <v>347</v>
       </c>
       <c r="K226">
         <f t="shared" ca="1" si="4"/>
-        <v>338</v>
+        <v>113</v>
       </c>
       <c r="L226">
         <f t="shared" ca="1" si="4"/>
-        <v>231</v>
+        <v>397</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
@@ -9820,15 +9867,15 @@
       </c>
       <c r="J227">
         <f t="shared" ca="1" si="4"/>
-        <v>302</v>
+        <v>161</v>
       </c>
       <c r="K227">
         <f t="shared" ca="1" si="4"/>
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="L227">
         <f t="shared" ca="1" si="4"/>
-        <v>366</v>
+        <v>138</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
@@ -9861,15 +9908,15 @@
       </c>
       <c r="J228">
         <f t="shared" ca="1" si="4"/>
-        <v>274</v>
+        <v>343</v>
       </c>
       <c r="K228">
         <f t="shared" ca="1" si="4"/>
-        <v>183</v>
+        <v>278</v>
       </c>
       <c r="L228">
         <f t="shared" ca="1" si="4"/>
-        <v>341</v>
+        <v>223</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
@@ -9902,15 +9949,15 @@
       </c>
       <c r="J229">
         <f t="shared" ca="1" si="4"/>
-        <v>351</v>
+        <v>179</v>
       </c>
       <c r="K229">
         <f t="shared" ca="1" si="4"/>
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="L229">
         <f t="shared" ca="1" si="4"/>
-        <v>305</v>
+        <v>193</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
@@ -9943,15 +9990,15 @@
       </c>
       <c r="J230">
         <f t="shared" ca="1" si="4"/>
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K230">
         <f t="shared" ca="1" si="4"/>
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="L230">
         <f t="shared" ca="1" si="4"/>
-        <v>383</v>
+        <v>209</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
@@ -9984,15 +10031,15 @@
       </c>
       <c r="J231">
         <f t="shared" ca="1" si="4"/>
-        <v>178</v>
+        <v>391</v>
       </c>
       <c r="K231">
         <f t="shared" ca="1" si="4"/>
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="L231">
         <f t="shared" ca="1" si="4"/>
-        <v>109</v>
+        <v>249</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
@@ -10025,15 +10072,15 @@
       </c>
       <c r="J232">
         <f t="shared" ca="1" si="4"/>
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="K232">
         <f t="shared" ca="1" si="4"/>
-        <v>141</v>
+        <v>335</v>
       </c>
       <c r="L232">
         <f t="shared" ca="1" si="4"/>
-        <v>136</v>
+        <v>241</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
@@ -10066,15 +10113,15 @@
       </c>
       <c r="J233">
         <f t="shared" ca="1" si="4"/>
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="K233">
         <f t="shared" ca="1" si="4"/>
-        <v>263</v>
+        <v>394</v>
       </c>
       <c r="L233">
         <f t="shared" ca="1" si="4"/>
-        <v>202</v>
+        <v>318</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
@@ -10107,15 +10154,15 @@
       </c>
       <c r="J234">
         <f t="shared" ca="1" si="4"/>
-        <v>252</v>
+        <v>329</v>
       </c>
       <c r="K234">
         <f t="shared" ca="1" si="4"/>
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="L234">
         <f t="shared" ca="1" si="4"/>
-        <v>165</v>
+        <v>245</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
@@ -10148,15 +10195,15 @@
       </c>
       <c r="J235">
         <f t="shared" ca="1" si="4"/>
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="K235">
         <f t="shared" ca="1" si="4"/>
-        <v>155</v>
+        <v>343</v>
       </c>
       <c r="L235">
         <f t="shared" ca="1" si="4"/>
-        <v>333</v>
+        <v>236</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
@@ -10189,15 +10236,15 @@
       </c>
       <c r="J236">
         <f t="shared" ca="1" si="4"/>
-        <v>340</v>
+        <v>128</v>
       </c>
       <c r="K236">
         <f t="shared" ca="1" si="4"/>
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="L236">
         <f t="shared" ca="1" si="4"/>
-        <v>134</v>
+        <v>389</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
@@ -10230,15 +10277,15 @@
       </c>
       <c r="J237">
         <f t="shared" ca="1" si="4"/>
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="K237">
         <f t="shared" ca="1" si="4"/>
-        <v>212</v>
+        <v>340</v>
       </c>
       <c r="L237">
         <f t="shared" ca="1" si="4"/>
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
@@ -10271,15 +10318,15 @@
       </c>
       <c r="J238">
         <f t="shared" ca="1" si="4"/>
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="K238">
         <f t="shared" ca="1" si="4"/>
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="L238">
         <f t="shared" ca="1" si="4"/>
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
@@ -10312,15 +10359,15 @@
       </c>
       <c r="J239">
         <f t="shared" ca="1" si="4"/>
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K239">
         <f t="shared" ca="1" si="4"/>
-        <v>292</v>
+        <v>176</v>
       </c>
       <c r="L239">
         <f t="shared" ca="1" si="4"/>
-        <v>250</v>
+        <v>115</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
@@ -10353,15 +10400,15 @@
       </c>
       <c r="J240">
         <f t="shared" ca="1" si="4"/>
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="K240">
         <f t="shared" ca="1" si="4"/>
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="L240">
         <f t="shared" ca="1" si="4"/>
-        <v>263</v>
+        <v>387</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
@@ -10394,15 +10441,15 @@
       </c>
       <c r="J241">
         <f t="shared" ca="1" si="4"/>
-        <v>375</v>
+        <v>181</v>
       </c>
       <c r="K241">
         <f t="shared" ca="1" si="4"/>
-        <v>206</v>
+        <v>353</v>
       </c>
       <c r="L241">
         <f t="shared" ca="1" si="4"/>
-        <v>285</v>
+        <v>400</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.3">
@@ -10435,15 +10482,15 @@
       </c>
       <c r="J242">
         <f t="shared" ca="1" si="4"/>
-        <v>159</v>
+        <v>371</v>
       </c>
       <c r="K242">
         <f t="shared" ca="1" si="4"/>
-        <v>218</v>
+        <v>374</v>
       </c>
       <c r="L242">
         <f t="shared" ca="1" si="4"/>
-        <v>397</v>
+        <v>181</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
@@ -10476,15 +10523,15 @@
       </c>
       <c r="J243">
         <f t="shared" ca="1" si="4"/>
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="K243">
         <f t="shared" ca="1" si="4"/>
-        <v>122</v>
+        <v>226</v>
       </c>
       <c r="L243">
         <f t="shared" ca="1" si="4"/>
-        <v>166</v>
+        <v>321</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
@@ -10517,15 +10564,15 @@
       </c>
       <c r="J244">
         <f t="shared" ca="1" si="4"/>
-        <v>306</v>
+        <v>119</v>
       </c>
       <c r="K244">
         <f t="shared" ca="1" si="4"/>
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="L244">
         <f t="shared" ca="1" si="4"/>
-        <v>111</v>
+        <v>245</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
@@ -10558,15 +10605,15 @@
       </c>
       <c r="J245">
         <f t="shared" ca="1" si="4"/>
-        <v>371</v>
+        <v>126</v>
       </c>
       <c r="K245">
         <f t="shared" ca="1" si="4"/>
-        <v>104</v>
+        <v>382</v>
       </c>
       <c r="L245">
         <f t="shared" ca="1" si="4"/>
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
@@ -10599,15 +10646,15 @@
       </c>
       <c r="J246">
         <f t="shared" ca="1" si="4"/>
-        <v>322</v>
+        <v>126</v>
       </c>
       <c r="K246">
         <f t="shared" ca="1" si="4"/>
-        <v>104</v>
+        <v>313</v>
       </c>
       <c r="L246">
         <f t="shared" ca="1" si="4"/>
-        <v>141</v>
+        <v>274</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
@@ -10640,15 +10687,15 @@
       </c>
       <c r="J247">
         <f t="shared" ca="1" si="4"/>
-        <v>224</v>
+        <v>142</v>
       </c>
       <c r="K247">
         <f t="shared" ca="1" si="4"/>
-        <v>123</v>
+        <v>302</v>
       </c>
       <c r="L247">
         <f t="shared" ca="1" si="4"/>
-        <v>316</v>
+        <v>108</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
@@ -10681,15 +10728,15 @@
       </c>
       <c r="J248">
         <f t="shared" ca="1" si="4"/>
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="K248">
         <f t="shared" ca="1" si="4"/>
-        <v>265</v>
+        <v>376</v>
       </c>
       <c r="L248">
         <f t="shared" ca="1" si="4"/>
-        <v>243</v>
+        <v>321</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
@@ -10722,15 +10769,15 @@
       </c>
       <c r="J249">
         <f t="shared" ca="1" si="4"/>
-        <v>399</v>
+        <v>292</v>
       </c>
       <c r="K249">
         <f t="shared" ca="1" si="4"/>
-        <v>378</v>
+        <v>248</v>
       </c>
       <c r="L249">
         <f t="shared" ca="1" si="4"/>
-        <v>194</v>
+        <v>147</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
@@ -10763,15 +10810,15 @@
       </c>
       <c r="J250">
         <f t="shared" ca="1" si="4"/>
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="K250">
         <f t="shared" ca="1" si="4"/>
-        <v>276</v>
+        <v>194</v>
       </c>
       <c r="L250">
         <f t="shared" ca="1" si="4"/>
-        <v>367</v>
+        <v>174</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
@@ -10804,15 +10851,15 @@
       </c>
       <c r="J251">
         <f t="shared" ca="1" si="4"/>
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="K251">
         <f t="shared" ca="1" si="4"/>
-        <v>301</v>
+        <v>251</v>
       </c>
       <c r="L251">
         <f t="shared" ca="1" si="4"/>
-        <v>267</v>
+        <v>366</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
@@ -10845,15 +10892,15 @@
       </c>
       <c r="J252">
         <f t="shared" ca="1" si="4"/>
-        <v>110</v>
+        <v>334</v>
       </c>
       <c r="K252">
         <f t="shared" ca="1" si="4"/>
-        <v>121</v>
+        <v>326</v>
       </c>
       <c r="L252">
         <f t="shared" ca="1" si="4"/>
-        <v>393</v>
+        <v>338</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
@@ -10886,15 +10933,15 @@
       </c>
       <c r="J253">
         <f t="shared" ca="1" si="4"/>
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="K253">
         <f t="shared" ca="1" si="4"/>
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L253">
         <f t="shared" ca="1" si="4"/>
-        <v>203</v>
+        <v>246</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
@@ -10927,15 +10974,15 @@
       </c>
       <c r="J254">
         <f t="shared" ca="1" si="4"/>
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="K254">
         <f t="shared" ca="1" si="4"/>
-        <v>104</v>
+        <v>269</v>
       </c>
       <c r="L254">
         <f t="shared" ca="1" si="4"/>
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
@@ -10968,15 +11015,15 @@
       </c>
       <c r="J255">
         <f t="shared" ca="1" si="4"/>
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="K255">
         <f t="shared" ca="1" si="4"/>
-        <v>305</v>
+        <v>174</v>
       </c>
       <c r="L255">
         <f t="shared" ca="1" si="4"/>
-        <v>124</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
@@ -11009,15 +11056,15 @@
       </c>
       <c r="J256">
         <f t="shared" ca="1" si="4"/>
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="K256">
         <f t="shared" ca="1" si="4"/>
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="L256">
         <f t="shared" ca="1" si="4"/>
-        <v>139</v>
+        <v>306</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
@@ -11050,15 +11097,15 @@
       </c>
       <c r="J257">
         <f t="shared" ca="1" si="4"/>
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="K257">
         <f t="shared" ca="1" si="4"/>
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="L257">
         <f t="shared" ca="1" si="4"/>
-        <v>173</v>
+        <v>318</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
@@ -11091,15 +11138,15 @@
       </c>
       <c r="J258">
         <f t="shared" ca="1" si="4"/>
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="K258">
         <f t="shared" ca="1" si="4"/>
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="L258">
         <f t="shared" ca="1" si="4"/>
-        <v>233</v>
+        <v>364</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
@@ -11132,15 +11179,15 @@
       </c>
       <c r="J259">
         <f t="shared" ref="J259:L322" ca="1" si="5">RANDBETWEEN(100,400)</f>
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="K259">
         <f t="shared" ca="1" si="5"/>
-        <v>234</v>
+        <v>382</v>
       </c>
       <c r="L259">
         <f t="shared" ca="1" si="5"/>
-        <v>288</v>
+        <v>125</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
@@ -11173,15 +11220,15 @@
       </c>
       <c r="J260">
         <f t="shared" ca="1" si="5"/>
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="K260">
         <f t="shared" ca="1" si="5"/>
-        <v>178</v>
+        <v>285</v>
       </c>
       <c r="L260">
         <f t="shared" ca="1" si="5"/>
-        <v>395</v>
+        <v>296</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
@@ -11214,15 +11261,15 @@
       </c>
       <c r="J261">
         <f t="shared" ca="1" si="5"/>
-        <v>333</v>
+        <v>206</v>
       </c>
       <c r="K261">
         <f t="shared" ca="1" si="5"/>
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="L261">
         <f t="shared" ca="1" si="5"/>
-        <v>153</v>
+        <v>359</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
@@ -11255,15 +11302,15 @@
       </c>
       <c r="J262">
         <f t="shared" ca="1" si="5"/>
-        <v>117</v>
+        <v>257</v>
       </c>
       <c r="K262">
         <f t="shared" ca="1" si="5"/>
-        <v>278</v>
+        <v>375</v>
       </c>
       <c r="L262">
         <f t="shared" ca="1" si="5"/>
-        <v>176</v>
+        <v>203</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
@@ -11296,15 +11343,15 @@
       </c>
       <c r="J263">
         <f t="shared" ca="1" si="5"/>
-        <v>381</v>
+        <v>236</v>
       </c>
       <c r="K263">
         <f t="shared" ca="1" si="5"/>
-        <v>134</v>
+        <v>295</v>
       </c>
       <c r="L263">
         <f t="shared" ca="1" si="5"/>
-        <v>265</v>
+        <v>329</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
@@ -11337,15 +11384,15 @@
       </c>
       <c r="J264">
         <f t="shared" ca="1" si="5"/>
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="K264">
         <f t="shared" ca="1" si="5"/>
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="L264">
         <f t="shared" ca="1" si="5"/>
-        <v>221</v>
+        <v>178</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
@@ -11378,15 +11425,15 @@
       </c>
       <c r="J265">
         <f t="shared" ca="1" si="5"/>
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="K265">
         <f t="shared" ca="1" si="5"/>
-        <v>331</v>
+        <v>386</v>
       </c>
       <c r="L265">
         <f t="shared" ca="1" si="5"/>
-        <v>137</v>
+        <v>308</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
@@ -11419,15 +11466,15 @@
       </c>
       <c r="J266">
         <f t="shared" ca="1" si="5"/>
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="K266">
         <f t="shared" ca="1" si="5"/>
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="L266">
         <f t="shared" ca="1" si="5"/>
-        <v>126</v>
+        <v>269</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
@@ -11460,15 +11507,15 @@
       </c>
       <c r="J267">
         <f t="shared" ca="1" si="5"/>
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="K267">
         <f t="shared" ca="1" si="5"/>
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="L267">
         <f t="shared" ca="1" si="5"/>
-        <v>141</v>
+        <v>326</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
@@ -11501,15 +11548,15 @@
       </c>
       <c r="J268">
         <f t="shared" ca="1" si="5"/>
-        <v>101</v>
+        <v>343</v>
       </c>
       <c r="K268">
         <f t="shared" ca="1" si="5"/>
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="L268">
         <f t="shared" ca="1" si="5"/>
-        <v>289</v>
+        <v>173</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
@@ -11542,15 +11589,15 @@
       </c>
       <c r="J269">
         <f t="shared" ca="1" si="5"/>
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="K269">
         <f t="shared" ca="1" si="5"/>
-        <v>258</v>
+        <v>370</v>
       </c>
       <c r="L269">
         <f t="shared" ca="1" si="5"/>
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
@@ -11583,15 +11630,15 @@
       </c>
       <c r="J270">
         <f t="shared" ca="1" si="5"/>
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="K270">
         <f t="shared" ca="1" si="5"/>
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="L270">
         <f t="shared" ca="1" si="5"/>
-        <v>216</v>
+        <v>354</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
@@ -11624,15 +11671,15 @@
       </c>
       <c r="J271">
         <f t="shared" ca="1" si="5"/>
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="K271">
         <f t="shared" ca="1" si="5"/>
-        <v>385</v>
+        <v>272</v>
       </c>
       <c r="L271">
         <f t="shared" ca="1" si="5"/>
-        <v>231</v>
+        <v>190</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
@@ -11665,15 +11712,15 @@
       </c>
       <c r="J272">
         <f t="shared" ca="1" si="5"/>
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="K272">
         <f t="shared" ca="1" si="5"/>
-        <v>109</v>
+        <v>368</v>
       </c>
       <c r="L272">
         <f t="shared" ca="1" si="5"/>
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
@@ -11706,15 +11753,15 @@
       </c>
       <c r="J273">
         <f t="shared" ca="1" si="5"/>
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="K273">
         <f t="shared" ca="1" si="5"/>
-        <v>378</v>
+        <v>187</v>
       </c>
       <c r="L273">
         <f t="shared" ca="1" si="5"/>
-        <v>397</v>
+        <v>173</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
@@ -11747,15 +11794,15 @@
       </c>
       <c r="J274">
         <f t="shared" ca="1" si="5"/>
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="K274">
         <f t="shared" ca="1" si="5"/>
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="L274">
         <f t="shared" ca="1" si="5"/>
-        <v>129</v>
+        <v>192</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
@@ -11788,15 +11835,15 @@
       </c>
       <c r="J275">
         <f t="shared" ca="1" si="5"/>
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="K275">
         <f t="shared" ca="1" si="5"/>
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="L275">
         <f t="shared" ca="1" si="5"/>
-        <v>302</v>
+        <v>241</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
@@ -11829,15 +11876,15 @@
       </c>
       <c r="J276">
         <f t="shared" ca="1" si="5"/>
-        <v>386</v>
+        <v>136</v>
       </c>
       <c r="K276">
         <f t="shared" ca="1" si="5"/>
-        <v>368</v>
+        <v>126</v>
       </c>
       <c r="L276">
         <f t="shared" ca="1" si="5"/>
-        <v>186</v>
+        <v>217</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
@@ -11870,15 +11917,15 @@
       </c>
       <c r="J277">
         <f t="shared" ca="1" si="5"/>
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="K277">
         <f t="shared" ca="1" si="5"/>
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="L277">
         <f t="shared" ca="1" si="5"/>
-        <v>265</v>
+        <v>309</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
@@ -11911,15 +11958,15 @@
       </c>
       <c r="J278">
         <f t="shared" ca="1" si="5"/>
-        <v>305</v>
+        <v>109</v>
       </c>
       <c r="K278">
         <f t="shared" ca="1" si="5"/>
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="L278">
         <f t="shared" ca="1" si="5"/>
-        <v>142</v>
+        <v>196</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
@@ -11952,15 +11999,15 @@
       </c>
       <c r="J279">
         <f t="shared" ca="1" si="5"/>
-        <v>388</v>
+        <v>107</v>
       </c>
       <c r="K279">
         <f t="shared" ca="1" si="5"/>
-        <v>375</v>
+        <v>228</v>
       </c>
       <c r="L279">
         <f t="shared" ca="1" si="5"/>
-        <v>104</v>
+        <v>379</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
@@ -11993,15 +12040,15 @@
       </c>
       <c r="J280">
         <f t="shared" ca="1" si="5"/>
-        <v>399</v>
+        <v>148</v>
       </c>
       <c r="K280">
         <f t="shared" ca="1" si="5"/>
-        <v>150</v>
+        <v>308</v>
       </c>
       <c r="L280">
         <f t="shared" ca="1" si="5"/>
-        <v>368</v>
+        <v>272</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
@@ -12034,15 +12081,15 @@
       </c>
       <c r="J281">
         <f t="shared" ca="1" si="5"/>
-        <v>102</v>
+        <v>244</v>
       </c>
       <c r="K281">
         <f t="shared" ca="1" si="5"/>
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="L281">
         <f t="shared" ca="1" si="5"/>
-        <v>313</v>
+        <v>373</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
@@ -12075,15 +12122,15 @@
       </c>
       <c r="J282">
         <f t="shared" ca="1" si="5"/>
-        <v>142</v>
+        <v>317</v>
       </c>
       <c r="K282">
         <f t="shared" ca="1" si="5"/>
-        <v>189</v>
+        <v>396</v>
       </c>
       <c r="L282">
         <f t="shared" ca="1" si="5"/>
-        <v>254</v>
+        <v>329</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
@@ -12116,15 +12163,15 @@
       </c>
       <c r="J283">
         <f t="shared" ca="1" si="5"/>
-        <v>370</v>
+        <v>217</v>
       </c>
       <c r="K283">
         <f t="shared" ca="1" si="5"/>
-        <v>122</v>
+        <v>374</v>
       </c>
       <c r="L283">
         <f t="shared" ca="1" si="5"/>
-        <v>172</v>
+        <v>119</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
@@ -12157,15 +12204,15 @@
       </c>
       <c r="J284">
         <f t="shared" ca="1" si="5"/>
-        <v>136</v>
+        <v>366</v>
       </c>
       <c r="K284">
         <f t="shared" ca="1" si="5"/>
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="L284">
         <f t="shared" ca="1" si="5"/>
-        <v>115</v>
+        <v>235</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
@@ -12198,15 +12245,15 @@
       </c>
       <c r="J285">
         <f t="shared" ca="1" si="5"/>
-        <v>288</v>
+        <v>160</v>
       </c>
       <c r="K285">
         <f t="shared" ca="1" si="5"/>
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="L285">
         <f t="shared" ca="1" si="5"/>
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
@@ -12239,15 +12286,15 @@
       </c>
       <c r="J286">
         <f t="shared" ca="1" si="5"/>
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="K286">
         <f t="shared" ca="1" si="5"/>
-        <v>389</v>
+        <v>243</v>
       </c>
       <c r="L286">
         <f t="shared" ca="1" si="5"/>
-        <v>357</v>
+        <v>134</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
@@ -12280,15 +12327,15 @@
       </c>
       <c r="J287">
         <f t="shared" ca="1" si="5"/>
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="K287">
         <f t="shared" ca="1" si="5"/>
-        <v>340</v>
+        <v>258</v>
       </c>
       <c r="L287">
         <f t="shared" ca="1" si="5"/>
-        <v>310</v>
+        <v>259</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
@@ -12321,15 +12368,15 @@
       </c>
       <c r="J288">
         <f t="shared" ca="1" si="5"/>
-        <v>309</v>
+        <v>238</v>
       </c>
       <c r="K288">
         <f t="shared" ca="1" si="5"/>
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="L288">
         <f t="shared" ca="1" si="5"/>
-        <v>207</v>
+        <v>326</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
@@ -12362,15 +12409,15 @@
       </c>
       <c r="J289">
         <f t="shared" ca="1" si="5"/>
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="K289">
         <f t="shared" ca="1" si="5"/>
-        <v>166</v>
+        <v>375</v>
       </c>
       <c r="L289">
         <f t="shared" ca="1" si="5"/>
-        <v>372</v>
+        <v>361</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.3">
@@ -12403,15 +12450,15 @@
       </c>
       <c r="J290">
         <f t="shared" ca="1" si="5"/>
-        <v>397</v>
+        <v>277</v>
       </c>
       <c r="K290">
         <f t="shared" ca="1" si="5"/>
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="L290">
         <f t="shared" ca="1" si="5"/>
-        <v>340</v>
+        <v>275</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
@@ -12444,15 +12491,15 @@
       </c>
       <c r="J291">
         <f t="shared" ca="1" si="5"/>
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="K291">
         <f t="shared" ca="1" si="5"/>
-        <v>393</v>
+        <v>187</v>
       </c>
       <c r="L291">
         <f t="shared" ca="1" si="5"/>
-        <v>388</v>
+        <v>297</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
@@ -12485,15 +12532,15 @@
       </c>
       <c r="J292">
         <f t="shared" ca="1" si="5"/>
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="K292">
         <f t="shared" ca="1" si="5"/>
-        <v>301</v>
+        <v>113</v>
       </c>
       <c r="L292">
         <f t="shared" ca="1" si="5"/>
-        <v>212</v>
+        <v>336</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
@@ -12526,15 +12573,15 @@
       </c>
       <c r="J293">
         <f t="shared" ca="1" si="5"/>
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="K293">
         <f t="shared" ca="1" si="5"/>
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="L293">
         <f t="shared" ca="1" si="5"/>
-        <v>369</v>
+        <v>181</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
@@ -12567,15 +12614,15 @@
       </c>
       <c r="J294">
         <f t="shared" ca="1" si="5"/>
-        <v>314</v>
+        <v>158</v>
       </c>
       <c r="K294">
         <f t="shared" ca="1" si="5"/>
-        <v>114</v>
+        <v>366</v>
       </c>
       <c r="L294">
         <f t="shared" ca="1" si="5"/>
-        <v>114</v>
+        <v>354</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
@@ -12608,15 +12655,15 @@
       </c>
       <c r="J295">
         <f t="shared" ca="1" si="5"/>
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="K295">
         <f t="shared" ca="1" si="5"/>
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="L295">
         <f t="shared" ca="1" si="5"/>
-        <v>179</v>
+        <v>238</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
@@ -12649,15 +12696,15 @@
       </c>
       <c r="J296">
         <f t="shared" ca="1" si="5"/>
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="K296">
         <f t="shared" ca="1" si="5"/>
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="L296">
         <f t="shared" ca="1" si="5"/>
-        <v>235</v>
+        <v>376</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
@@ -12690,15 +12737,15 @@
       </c>
       <c r="J297">
         <f t="shared" ca="1" si="5"/>
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="K297">
         <f t="shared" ca="1" si="5"/>
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="L297">
         <f t="shared" ca="1" si="5"/>
-        <v>391</v>
+        <v>308</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
@@ -12735,11 +12782,11 @@
       </c>
       <c r="K298">
         <f t="shared" ca="1" si="5"/>
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L298">
         <f t="shared" ca="1" si="5"/>
-        <v>155</v>
+        <v>400</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
@@ -12772,15 +12819,15 @@
       </c>
       <c r="J299">
         <f t="shared" ca="1" si="5"/>
-        <v>154</v>
+        <v>384</v>
       </c>
       <c r="K299">
         <f t="shared" ca="1" si="5"/>
-        <v>190</v>
+        <v>345</v>
       </c>
       <c r="L299">
         <f t="shared" ca="1" si="5"/>
-        <v>183</v>
+        <v>157</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
@@ -12813,15 +12860,15 @@
       </c>
       <c r="J300">
         <f t="shared" ca="1" si="5"/>
-        <v>246</v>
+        <v>108</v>
       </c>
       <c r="K300">
         <f t="shared" ca="1" si="5"/>
-        <v>234</v>
+        <v>398</v>
       </c>
       <c r="L300">
         <f t="shared" ca="1" si="5"/>
-        <v>275</v>
+        <v>214</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
@@ -12854,15 +12901,15 @@
       </c>
       <c r="J301">
         <f t="shared" ca="1" si="5"/>
-        <v>315</v>
+        <v>214</v>
       </c>
       <c r="K301">
         <f t="shared" ca="1" si="5"/>
-        <v>256</v>
+        <v>385</v>
       </c>
       <c r="L301">
         <f t="shared" ca="1" si="5"/>
-        <v>340</v>
+        <v>109</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
@@ -12895,15 +12942,15 @@
       </c>
       <c r="J302">
         <f t="shared" ca="1" si="5"/>
-        <v>171</v>
+        <v>382</v>
       </c>
       <c r="K302">
         <f t="shared" ca="1" si="5"/>
-        <v>262</v>
+        <v>354</v>
       </c>
       <c r="L302">
         <f t="shared" ca="1" si="5"/>
-        <v>334</v>
+        <v>256</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
@@ -12936,15 +12983,15 @@
       </c>
       <c r="J303">
         <f t="shared" ca="1" si="5"/>
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="K303">
         <f t="shared" ca="1" si="5"/>
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="L303">
         <f t="shared" ca="1" si="5"/>
-        <v>236</v>
+        <v>172</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
@@ -12977,15 +13024,15 @@
       </c>
       <c r="J304">
         <f t="shared" ca="1" si="5"/>
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="K304">
         <f t="shared" ca="1" si="5"/>
-        <v>250</v>
+        <v>338</v>
       </c>
       <c r="L304">
         <f t="shared" ca="1" si="5"/>
-        <v>185</v>
+        <v>365</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
@@ -13018,15 +13065,15 @@
       </c>
       <c r="J305">
         <f t="shared" ca="1" si="5"/>
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="K305">
         <f t="shared" ca="1" si="5"/>
-        <v>362</v>
+        <v>248</v>
       </c>
       <c r="L305">
         <f t="shared" ca="1" si="5"/>
-        <v>166</v>
+        <v>124</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
@@ -13059,15 +13106,15 @@
       </c>
       <c r="J306">
         <f t="shared" ca="1" si="5"/>
-        <v>192</v>
+        <v>354</v>
       </c>
       <c r="K306">
         <f t="shared" ca="1" si="5"/>
-        <v>372</v>
+        <v>203</v>
       </c>
       <c r="L306">
         <f t="shared" ca="1" si="5"/>
-        <v>256</v>
+        <v>281</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
@@ -13100,15 +13147,15 @@
       </c>
       <c r="J307">
         <f t="shared" ca="1" si="5"/>
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="K307">
         <f t="shared" ca="1" si="5"/>
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L307">
         <f t="shared" ca="1" si="5"/>
-        <v>344</v>
+        <v>386</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
@@ -13141,15 +13188,15 @@
       </c>
       <c r="J308">
         <f t="shared" ca="1" si="5"/>
-        <v>301</v>
+        <v>385</v>
       </c>
       <c r="K308">
         <f t="shared" ca="1" si="5"/>
-        <v>400</v>
+        <v>303</v>
       </c>
       <c r="L308">
         <f t="shared" ca="1" si="5"/>
-        <v>277</v>
+        <v>193</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
@@ -13182,15 +13229,15 @@
       </c>
       <c r="J309">
         <f t="shared" ca="1" si="5"/>
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="K309">
         <f t="shared" ca="1" si="5"/>
-        <v>383</v>
+        <v>199</v>
       </c>
       <c r="L309">
         <f t="shared" ca="1" si="5"/>
-        <v>210</v>
+        <v>282</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
@@ -13223,15 +13270,15 @@
       </c>
       <c r="J310">
         <f t="shared" ca="1" si="5"/>
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="K310">
         <f t="shared" ca="1" si="5"/>
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="L310">
         <f t="shared" ca="1" si="5"/>
-        <v>196</v>
+        <v>389</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
@@ -13264,15 +13311,15 @@
       </c>
       <c r="J311">
         <f t="shared" ca="1" si="5"/>
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="K311">
         <f t="shared" ca="1" si="5"/>
-        <v>349</v>
+        <v>151</v>
       </c>
       <c r="L311">
         <f t="shared" ca="1" si="5"/>
-        <v>353</v>
+        <v>204</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
@@ -13305,15 +13352,15 @@
       </c>
       <c r="J312">
         <f t="shared" ca="1" si="5"/>
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K312">
         <f t="shared" ca="1" si="5"/>
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="L312">
         <f t="shared" ca="1" si="5"/>
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
@@ -13346,15 +13393,15 @@
       </c>
       <c r="J313">
         <f t="shared" ca="1" si="5"/>
-        <v>200</v>
+        <v>371</v>
       </c>
       <c r="K313">
         <f t="shared" ca="1" si="5"/>
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L313">
         <f t="shared" ca="1" si="5"/>
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.3">
@@ -13387,15 +13434,15 @@
       </c>
       <c r="J314">
         <f t="shared" ca="1" si="5"/>
-        <v>235</v>
+        <v>384</v>
       </c>
       <c r="K314">
         <f t="shared" ca="1" si="5"/>
-        <v>121</v>
+        <v>221</v>
       </c>
       <c r="L314">
         <f t="shared" ca="1" si="5"/>
-        <v>333</v>
+        <v>231</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
@@ -13428,15 +13475,15 @@
       </c>
       <c r="J315">
         <f t="shared" ca="1" si="5"/>
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="K315">
         <f t="shared" ca="1" si="5"/>
-        <v>346</v>
+        <v>163</v>
       </c>
       <c r="L315">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>365</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
@@ -13469,15 +13516,15 @@
       </c>
       <c r="J316">
         <f t="shared" ca="1" si="5"/>
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="K316">
         <f t="shared" ca="1" si="5"/>
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="L316">
         <f t="shared" ca="1" si="5"/>
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
@@ -13510,15 +13557,15 @@
       </c>
       <c r="J317">
         <f t="shared" ca="1" si="5"/>
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="K317">
         <f t="shared" ca="1" si="5"/>
-        <v>396</v>
+        <v>351</v>
       </c>
       <c r="L317">
         <f t="shared" ca="1" si="5"/>
-        <v>128</v>
+        <v>329</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
@@ -13551,15 +13598,15 @@
       </c>
       <c r="J318">
         <f t="shared" ca="1" si="5"/>
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="K318">
         <f t="shared" ca="1" si="5"/>
-        <v>150</v>
+        <v>348</v>
       </c>
       <c r="L318">
         <f t="shared" ca="1" si="5"/>
-        <v>367</v>
+        <v>399</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.3">
@@ -13592,15 +13639,15 @@
       </c>
       <c r="J319">
         <f t="shared" ca="1" si="5"/>
-        <v>398</v>
+        <v>173</v>
       </c>
       <c r="K319">
         <f t="shared" ca="1" si="5"/>
-        <v>388</v>
+        <v>331</v>
       </c>
       <c r="L319">
         <f t="shared" ca="1" si="5"/>
-        <v>387</v>
+        <v>196</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.3">
@@ -13633,15 +13680,15 @@
       </c>
       <c r="J320">
         <f t="shared" ca="1" si="5"/>
-        <v>383</v>
+        <v>267</v>
       </c>
       <c r="K320">
         <f t="shared" ca="1" si="5"/>
-        <v>116</v>
+        <v>386</v>
       </c>
       <c r="L320">
         <f t="shared" ca="1" si="5"/>
-        <v>237</v>
+        <v>385</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.3">
@@ -13674,15 +13721,15 @@
       </c>
       <c r="J321">
         <f t="shared" ca="1" si="5"/>
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="K321">
         <f t="shared" ca="1" si="5"/>
-        <v>250</v>
+        <v>156</v>
       </c>
       <c r="L321">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.3">
@@ -13715,15 +13762,15 @@
       </c>
       <c r="J322">
         <f t="shared" ca="1" si="5"/>
-        <v>156</v>
+        <v>369</v>
       </c>
       <c r="K322">
         <f t="shared" ca="1" si="5"/>
-        <v>112</v>
+        <v>343</v>
       </c>
       <c r="L322">
         <f t="shared" ca="1" si="5"/>
-        <v>200</v>
+        <v>357</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
@@ -13756,15 +13803,15 @@
       </c>
       <c r="J323">
         <f t="shared" ref="J323:L354" ca="1" si="6">RANDBETWEEN(100,400)</f>
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="K323">
         <f t="shared" ca="1" si="6"/>
-        <v>121</v>
+        <v>250</v>
       </c>
       <c r="L323">
         <f t="shared" ca="1" si="6"/>
-        <v>393</v>
+        <v>131</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.3">
@@ -13797,15 +13844,15 @@
       </c>
       <c r="J324">
         <f t="shared" ca="1" si="6"/>
-        <v>245</v>
+        <v>371</v>
       </c>
       <c r="K324">
         <f t="shared" ca="1" si="6"/>
-        <v>132</v>
+        <v>325</v>
       </c>
       <c r="L324">
         <f t="shared" ca="1" si="6"/>
-        <v>347</v>
+        <v>139</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.3">
@@ -13838,15 +13885,15 @@
       </c>
       <c r="J325">
         <f t="shared" ca="1" si="6"/>
-        <v>317</v>
+        <v>171</v>
       </c>
       <c r="K325">
         <f t="shared" ca="1" si="6"/>
-        <v>106</v>
+        <v>339</v>
       </c>
       <c r="L325">
         <f t="shared" ca="1" si="6"/>
-        <v>105</v>
+        <v>137</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.3">
@@ -13879,15 +13926,15 @@
       </c>
       <c r="J326">
         <f t="shared" ca="1" si="6"/>
-        <v>344</v>
+        <v>154</v>
       </c>
       <c r="K326">
         <f t="shared" ca="1" si="6"/>
-        <v>220</v>
+        <v>306</v>
       </c>
       <c r="L326">
         <f t="shared" ca="1" si="6"/>
-        <v>148</v>
+        <v>324</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.3">
@@ -13920,15 +13967,15 @@
       </c>
       <c r="J327">
         <f t="shared" ca="1" si="6"/>
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="K327">
         <f t="shared" ca="1" si="6"/>
-        <v>312</v>
+        <v>212</v>
       </c>
       <c r="L327">
         <f t="shared" ca="1" si="6"/>
-        <v>253</v>
+        <v>127</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.3">
@@ -13961,15 +14008,15 @@
       </c>
       <c r="J328">
         <f t="shared" ca="1" si="6"/>
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="K328">
         <f t="shared" ca="1" si="6"/>
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="L328">
         <f t="shared" ca="1" si="6"/>
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.3">
@@ -14002,15 +14049,15 @@
       </c>
       <c r="J329">
         <f t="shared" ca="1" si="6"/>
-        <v>325</v>
+        <v>181</v>
       </c>
       <c r="K329">
         <f t="shared" ca="1" si="6"/>
-        <v>187</v>
+        <v>283</v>
       </c>
       <c r="L329">
         <f t="shared" ca="1" si="6"/>
-        <v>142</v>
+        <v>228</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.3">
@@ -14043,15 +14090,15 @@
       </c>
       <c r="J330">
         <f t="shared" ca="1" si="6"/>
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="K330">
         <f t="shared" ca="1" si="6"/>
-        <v>112</v>
+        <v>356</v>
       </c>
       <c r="L330">
         <f t="shared" ca="1" si="6"/>
-        <v>298</v>
+        <v>260</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.3">
@@ -14084,15 +14131,15 @@
       </c>
       <c r="J331">
         <f t="shared" ca="1" si="6"/>
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="K331">
         <f t="shared" ca="1" si="6"/>
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="L331">
         <f t="shared" ca="1" si="6"/>
-        <v>393</v>
+        <v>122</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.3">
@@ -14125,15 +14172,15 @@
       </c>
       <c r="J332">
         <f t="shared" ca="1" si="6"/>
-        <v>348</v>
+        <v>309</v>
       </c>
       <c r="K332">
         <f t="shared" ca="1" si="6"/>
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="L332">
         <f t="shared" ca="1" si="6"/>
-        <v>189</v>
+        <v>234</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.3">
@@ -14166,15 +14213,15 @@
       </c>
       <c r="J333">
         <f t="shared" ca="1" si="6"/>
-        <v>375</v>
+        <v>108</v>
       </c>
       <c r="K333">
         <f t="shared" ca="1" si="6"/>
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="L333">
         <f t="shared" ca="1" si="6"/>
-        <v>313</v>
+        <v>257</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.3">
@@ -14207,15 +14254,15 @@
       </c>
       <c r="J334">
         <f t="shared" ca="1" si="6"/>
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="K334">
         <f t="shared" ca="1" si="6"/>
-        <v>157</v>
+        <v>243</v>
       </c>
       <c r="L334">
         <f t="shared" ca="1" si="6"/>
-        <v>256</v>
+        <v>392</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.3">
@@ -14248,15 +14295,15 @@
       </c>
       <c r="J335">
         <f t="shared" ca="1" si="6"/>
-        <v>397</v>
+        <v>224</v>
       </c>
       <c r="K335">
         <f t="shared" ca="1" si="6"/>
-        <v>364</v>
+        <v>260</v>
       </c>
       <c r="L335">
         <f t="shared" ca="1" si="6"/>
-        <v>310</v>
+        <v>121</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.3">
@@ -14289,15 +14336,15 @@
       </c>
       <c r="J336">
         <f t="shared" ca="1" si="6"/>
-        <v>170</v>
+        <v>268</v>
       </c>
       <c r="K336">
         <f t="shared" ca="1" si="6"/>
-        <v>361</v>
+        <v>153</v>
       </c>
       <c r="L336">
         <f t="shared" ca="1" si="6"/>
-        <v>242</v>
+        <v>179</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.3">
@@ -14330,15 +14377,15 @@
       </c>
       <c r="J337">
         <f t="shared" ca="1" si="6"/>
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="K337">
         <f t="shared" ca="1" si="6"/>
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="L337">
         <f t="shared" ca="1" si="6"/>
-        <v>177</v>
+        <v>369</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.3">
@@ -14371,15 +14418,15 @@
       </c>
       <c r="J338">
         <f t="shared" ca="1" si="6"/>
-        <v>101</v>
+        <v>260</v>
       </c>
       <c r="K338">
         <f t="shared" ca="1" si="6"/>
-        <v>296</v>
+        <v>400</v>
       </c>
       <c r="L338">
         <f t="shared" ca="1" si="6"/>
-        <v>117</v>
+        <v>317</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.3">
@@ -14412,15 +14459,15 @@
       </c>
       <c r="J339">
         <f t="shared" ca="1" si="6"/>
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="K339">
         <f t="shared" ca="1" si="6"/>
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="L339">
         <f t="shared" ca="1" si="6"/>
-        <v>331</v>
+        <v>215</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.3">
@@ -14453,15 +14500,15 @@
       </c>
       <c r="J340">
         <f t="shared" ca="1" si="6"/>
-        <v>234</v>
+        <v>162</v>
       </c>
       <c r="K340">
         <f t="shared" ca="1" si="6"/>
-        <v>104</v>
+        <v>376</v>
       </c>
       <c r="L340">
         <f t="shared" ca="1" si="6"/>
-        <v>266</v>
+        <v>201</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.3">
@@ -14494,15 +14541,15 @@
       </c>
       <c r="J341">
         <f t="shared" ca="1" si="6"/>
-        <v>269</v>
+        <v>125</v>
       </c>
       <c r="K341">
         <f t="shared" ca="1" si="6"/>
-        <v>293</v>
+        <v>220</v>
       </c>
       <c r="L341">
         <f t="shared" ca="1" si="6"/>
-        <v>363</v>
+        <v>309</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.3">
@@ -14535,15 +14582,15 @@
       </c>
       <c r="J342">
         <f t="shared" ca="1" si="6"/>
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="K342">
         <f t="shared" ca="1" si="6"/>
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="L342">
         <f t="shared" ca="1" si="6"/>
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.3">
@@ -14576,15 +14623,15 @@
       </c>
       <c r="J343">
         <f t="shared" ca="1" si="6"/>
-        <v>266</v>
+        <v>177</v>
       </c>
       <c r="K343">
         <f t="shared" ca="1" si="6"/>
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="L343">
         <f t="shared" ca="1" si="6"/>
-        <v>207</v>
+        <v>242</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.3">
@@ -14617,15 +14664,15 @@
       </c>
       <c r="J344">
         <f t="shared" ca="1" si="6"/>
-        <v>143</v>
+        <v>222</v>
       </c>
       <c r="K344">
         <f t="shared" ca="1" si="6"/>
-        <v>317</v>
+        <v>196</v>
       </c>
       <c r="L344">
         <f t="shared" ca="1" si="6"/>
-        <v>296</v>
+        <v>100</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.3">
@@ -14658,15 +14705,15 @@
       </c>
       <c r="J345">
         <f t="shared" ca="1" si="6"/>
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="K345">
         <f t="shared" ca="1" si="6"/>
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="L345">
         <f t="shared" ca="1" si="6"/>
-        <v>292</v>
+        <v>143</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.3">
@@ -14699,15 +14746,15 @@
       </c>
       <c r="J346">
         <f t="shared" ca="1" si="6"/>
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="K346">
         <f t="shared" ca="1" si="6"/>
-        <v>312</v>
+        <v>391</v>
       </c>
       <c r="L346">
         <f t="shared" ca="1" si="6"/>
-        <v>393</v>
+        <v>191</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.3">
@@ -14740,15 +14787,15 @@
       </c>
       <c r="J347">
         <f t="shared" ca="1" si="6"/>
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="K347">
         <f t="shared" ca="1" si="6"/>
-        <v>400</v>
+        <v>301</v>
       </c>
       <c r="L347">
         <f t="shared" ca="1" si="6"/>
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.3">
@@ -14781,15 +14828,15 @@
       </c>
       <c r="J348">
         <f t="shared" ca="1" si="6"/>
-        <v>191</v>
+        <v>347</v>
       </c>
       <c r="K348">
         <f t="shared" ca="1" si="6"/>
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="L348">
         <f t="shared" ca="1" si="6"/>
-        <v>314</v>
+        <v>360</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.3">
@@ -14822,15 +14869,15 @@
       </c>
       <c r="J349">
         <f t="shared" ca="1" si="6"/>
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K349">
         <f t="shared" ca="1" si="6"/>
-        <v>305</v>
+        <v>352</v>
       </c>
       <c r="L349">
         <f t="shared" ca="1" si="6"/>
-        <v>193</v>
+        <v>320</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.3">
@@ -14863,15 +14910,15 @@
       </c>
       <c r="J350">
         <f t="shared" ca="1" si="6"/>
-        <v>158</v>
+        <v>351</v>
       </c>
       <c r="K350">
         <f t="shared" ca="1" si="6"/>
-        <v>349</v>
+        <v>193</v>
       </c>
       <c r="L350">
         <f t="shared" ca="1" si="6"/>
-        <v>252</v>
+        <v>236</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.3">
@@ -14904,15 +14951,15 @@
       </c>
       <c r="J351">
         <f t="shared" ca="1" si="6"/>
-        <v>271</v>
+        <v>204</v>
       </c>
       <c r="K351">
         <f t="shared" ca="1" si="6"/>
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="L351">
         <f t="shared" ca="1" si="6"/>
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.3">
@@ -14945,15 +14992,15 @@
       </c>
       <c r="J352">
         <f t="shared" ca="1" si="6"/>
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="K352">
         <f t="shared" ca="1" si="6"/>
-        <v>133</v>
+        <v>372</v>
       </c>
       <c r="L352">
         <f t="shared" ca="1" si="6"/>
-        <v>309</v>
+        <v>214</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.3">
@@ -14986,15 +15033,15 @@
       </c>
       <c r="J353">
         <f t="shared" ca="1" si="6"/>
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="K353">
         <f t="shared" ca="1" si="6"/>
-        <v>316</v>
+        <v>389</v>
       </c>
       <c r="L353">
         <f t="shared" ca="1" si="6"/>
-        <v>351</v>
+        <v>201</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.3">
@@ -15027,15 +15074,15 @@
       </c>
       <c r="J354">
         <f t="shared" ca="1" si="6"/>
-        <v>198</v>
+        <v>358</v>
       </c>
       <c r="K354">
         <f t="shared" ca="1" si="6"/>
-        <v>374</v>
+        <v>136</v>
       </c>
       <c r="L354">
         <f t="shared" ca="1" si="6"/>
-        <v>319</v>
+        <v>164</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.3">
@@ -15068,15 +15115,15 @@
       </c>
       <c r="J355">
         <f t="shared" ref="J355:L386" ca="1" si="7">RANDBETWEEN(100,400)</f>
-        <v>230</v>
+        <v>292</v>
       </c>
       <c r="K355">
         <f t="shared" ca="1" si="7"/>
-        <v>216</v>
+        <v>130</v>
       </c>
       <c r="L355">
         <f t="shared" ca="1" si="7"/>
-        <v>311</v>
+        <v>365</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.3">
@@ -15109,15 +15156,15 @@
       </c>
       <c r="J356">
         <f t="shared" ca="1" si="7"/>
-        <v>259</v>
+        <v>147</v>
       </c>
       <c r="K356">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="L356">
         <f t="shared" ca="1" si="7"/>
-        <v>303</v>
+        <v>385</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.3">
@@ -15150,15 +15197,15 @@
       </c>
       <c r="J357">
         <f t="shared" ca="1" si="7"/>
-        <v>318</v>
+        <v>150</v>
       </c>
       <c r="K357">
         <f t="shared" ca="1" si="7"/>
-        <v>157</v>
+        <v>276</v>
       </c>
       <c r="L357">
         <f t="shared" ca="1" si="7"/>
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.3">
@@ -15191,15 +15238,15 @@
       </c>
       <c r="J358">
         <f t="shared" ca="1" si="7"/>
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="K358">
         <f t="shared" ca="1" si="7"/>
-        <v>274</v>
+        <v>160</v>
       </c>
       <c r="L358">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
+        <v>179</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.3">
@@ -15232,15 +15279,15 @@
       </c>
       <c r="J359">
         <f t="shared" ca="1" si="7"/>
-        <v>332</v>
+        <v>157</v>
       </c>
       <c r="K359">
         <f t="shared" ca="1" si="7"/>
-        <v>234</v>
+        <v>390</v>
       </c>
       <c r="L359">
         <f t="shared" ca="1" si="7"/>
-        <v>217</v>
+        <v>142</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.3">
@@ -15273,15 +15320,15 @@
       </c>
       <c r="J360">
         <f t="shared" ca="1" si="7"/>
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="K360">
         <f t="shared" ca="1" si="7"/>
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="L360">
         <f t="shared" ca="1" si="7"/>
-        <v>309</v>
+        <v>202</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.3">
@@ -15314,15 +15361,15 @@
       </c>
       <c r="J361">
         <f t="shared" ca="1" si="7"/>
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="K361">
         <f t="shared" ca="1" si="7"/>
-        <v>258</v>
+        <v>355</v>
       </c>
       <c r="L361">
         <f t="shared" ca="1" si="7"/>
-        <v>313</v>
+        <v>170</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.3">
@@ -15355,15 +15402,15 @@
       </c>
       <c r="J362">
         <f t="shared" ca="1" si="7"/>
-        <v>249</v>
+        <v>357</v>
       </c>
       <c r="K362">
         <f t="shared" ca="1" si="7"/>
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="L362">
         <f t="shared" ca="1" si="7"/>
-        <v>194</v>
+        <v>158</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.3">
@@ -15396,15 +15443,15 @@
       </c>
       <c r="J363">
         <f t="shared" ca="1" si="7"/>
-        <v>100</v>
+        <v>369</v>
       </c>
       <c r="K363">
         <f t="shared" ca="1" si="7"/>
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="L363">
         <f t="shared" ca="1" si="7"/>
-        <v>203</v>
+        <v>376</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
@@ -15437,15 +15484,15 @@
       </c>
       <c r="J364">
         <f t="shared" ca="1" si="7"/>
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="K364">
         <f t="shared" ca="1" si="7"/>
-        <v>362</v>
+        <v>176</v>
       </c>
       <c r="L364">
         <f t="shared" ca="1" si="7"/>
-        <v>379</v>
+        <v>178</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.3">
@@ -15478,15 +15525,15 @@
       </c>
       <c r="J365">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>251</v>
       </c>
       <c r="K365">
         <f t="shared" ca="1" si="7"/>
-        <v>395</v>
+        <v>231</v>
       </c>
       <c r="L365">
         <f t="shared" ca="1" si="7"/>
-        <v>394</v>
+        <v>365</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.3">
@@ -15519,15 +15566,15 @@
       </c>
       <c r="J366">
         <f t="shared" ca="1" si="7"/>
-        <v>161</v>
+        <v>255</v>
       </c>
       <c r="K366">
         <f t="shared" ca="1" si="7"/>
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="L366">
         <f t="shared" ca="1" si="7"/>
-        <v>297</v>
+        <v>198</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.3">
@@ -15560,15 +15607,15 @@
       </c>
       <c r="J367">
         <f t="shared" ca="1" si="7"/>
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="K367">
         <f t="shared" ca="1" si="7"/>
-        <v>326</v>
+        <v>265</v>
       </c>
       <c r="L367">
         <f t="shared" ca="1" si="7"/>
-        <v>376</v>
+        <v>119</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.3">
@@ -15601,15 +15648,15 @@
       </c>
       <c r="J368">
         <f t="shared" ca="1" si="7"/>
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="K368">
         <f t="shared" ca="1" si="7"/>
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="L368">
         <f t="shared" ca="1" si="7"/>
-        <v>344</v>
+        <v>164</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.3">
@@ -15642,15 +15689,15 @@
       </c>
       <c r="J369">
         <f t="shared" ca="1" si="7"/>
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="K369">
         <f t="shared" ca="1" si="7"/>
-        <v>375</v>
+        <v>240</v>
       </c>
       <c r="L369">
         <f t="shared" ca="1" si="7"/>
-        <v>251</v>
+        <v>207</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.3">
@@ -15683,7 +15730,7 @@
       </c>
       <c r="J370">
         <f t="shared" ca="1" si="7"/>
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="K370">
         <f t="shared" ca="1" si="7"/>
@@ -15691,7 +15738,7 @@
       </c>
       <c r="L370">
         <f t="shared" ca="1" si="7"/>
-        <v>321</v>
+        <v>251</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.3">
@@ -15724,15 +15771,15 @@
       </c>
       <c r="J371">
         <f t="shared" ca="1" si="7"/>
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="K371">
         <f t="shared" ca="1" si="7"/>
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="L371">
         <f t="shared" ca="1" si="7"/>
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.3">
@@ -15765,15 +15812,15 @@
       </c>
       <c r="J372">
         <f t="shared" ca="1" si="7"/>
-        <v>253</v>
+        <v>162</v>
       </c>
       <c r="K372">
         <f t="shared" ca="1" si="7"/>
-        <v>400</v>
+        <v>157</v>
       </c>
       <c r="L372">
         <f t="shared" ca="1" si="7"/>
-        <v>327</v>
+        <v>389</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.3">
@@ -15806,15 +15853,15 @@
       </c>
       <c r="J373">
         <f t="shared" ca="1" si="7"/>
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="K373">
         <f t="shared" ca="1" si="7"/>
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="L373">
         <f t="shared" ca="1" si="7"/>
-        <v>245</v>
+        <v>382</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.3">
@@ -15847,15 +15894,15 @@
       </c>
       <c r="J374">
         <f t="shared" ca="1" si="7"/>
-        <v>286</v>
+        <v>202</v>
       </c>
       <c r="K374">
         <f t="shared" ca="1" si="7"/>
-        <v>273</v>
+        <v>389</v>
       </c>
       <c r="L374">
         <f t="shared" ca="1" si="7"/>
-        <v>264</v>
+        <v>374</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.3">
@@ -15888,15 +15935,15 @@
       </c>
       <c r="J375">
         <f t="shared" ca="1" si="7"/>
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="K375">
         <f t="shared" ca="1" si="7"/>
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="L375">
         <f t="shared" ca="1" si="7"/>
-        <v>317</v>
+        <v>327</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.3">
@@ -15929,15 +15976,15 @@
       </c>
       <c r="J376">
         <f t="shared" ca="1" si="7"/>
-        <v>291</v>
+        <v>236</v>
       </c>
       <c r="K376">
         <f t="shared" ca="1" si="7"/>
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="L376">
         <f t="shared" ca="1" si="7"/>
-        <v>216</v>
+        <v>355</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.3">
@@ -15970,15 +16017,15 @@
       </c>
       <c r="J377">
         <f t="shared" ca="1" si="7"/>
-        <v>193</v>
+        <v>327</v>
       </c>
       <c r="K377">
         <f t="shared" ca="1" si="7"/>
-        <v>307</v>
+        <v>142</v>
       </c>
       <c r="L377">
         <f t="shared" ca="1" si="7"/>
-        <v>218</v>
+        <v>305</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.3">
@@ -16011,15 +16058,15 @@
       </c>
       <c r="J378">
         <f t="shared" ca="1" si="7"/>
-        <v>232</v>
+        <v>149</v>
       </c>
       <c r="K378">
         <f t="shared" ca="1" si="7"/>
-        <v>322</v>
+        <v>195</v>
       </c>
       <c r="L378">
         <f t="shared" ca="1" si="7"/>
-        <v>388</v>
+        <v>212</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.3">
@@ -16052,15 +16099,15 @@
       </c>
       <c r="J379">
         <f t="shared" ca="1" si="7"/>
-        <v>222</v>
+        <v>392</v>
       </c>
       <c r="K379">
         <f t="shared" ca="1" si="7"/>
-        <v>212</v>
+        <v>310</v>
       </c>
       <c r="L379">
         <f t="shared" ca="1" si="7"/>
-        <v>362</v>
+        <v>105</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.3">
@@ -16093,15 +16140,15 @@
       </c>
       <c r="J380">
         <f t="shared" ca="1" si="7"/>
-        <v>107</v>
+        <v>388</v>
       </c>
       <c r="K380">
         <f t="shared" ca="1" si="7"/>
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="L380">
         <f t="shared" ca="1" si="7"/>
-        <v>120</v>
+        <v>308</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.3">
@@ -16134,15 +16181,15 @@
       </c>
       <c r="J381">
         <f t="shared" ca="1" si="7"/>
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="K381">
         <f t="shared" ca="1" si="7"/>
-        <v>397</v>
+        <v>156</v>
       </c>
       <c r="L381">
         <f t="shared" ca="1" si="7"/>
-        <v>144</v>
+        <v>390</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.3">
@@ -16175,15 +16222,15 @@
       </c>
       <c r="J382">
         <f t="shared" ca="1" si="7"/>
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="K382">
         <f t="shared" ca="1" si="7"/>
-        <v>169</v>
+        <v>283</v>
       </c>
       <c r="L382">
         <f t="shared" ca="1" si="7"/>
-        <v>104</v>
+        <v>213</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.3">
@@ -16216,15 +16263,15 @@
       </c>
       <c r="J383">
         <f t="shared" ca="1" si="7"/>
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K383">
         <f t="shared" ca="1" si="7"/>
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="L383">
         <f t="shared" ca="1" si="7"/>
-        <v>340</v>
+        <v>214</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.3">
@@ -16257,15 +16304,15 @@
       </c>
       <c r="J384">
         <f t="shared" ca="1" si="7"/>
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K384">
         <f t="shared" ca="1" si="7"/>
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="L384">
         <f t="shared" ca="1" si="7"/>
-        <v>116</v>
+        <v>185</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.3">
@@ -16298,15 +16345,15 @@
       </c>
       <c r="J385">
         <f t="shared" ca="1" si="7"/>
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="K385">
         <f t="shared" ca="1" si="7"/>
-        <v>238</v>
+        <v>363</v>
       </c>
       <c r="L385">
         <f t="shared" ca="1" si="7"/>
-        <v>113</v>
+        <v>363</v>
       </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.3">
@@ -16339,15 +16386,15 @@
       </c>
       <c r="J386">
         <f t="shared" ca="1" si="7"/>
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="K386">
         <f t="shared" ca="1" si="7"/>
-        <v>144</v>
+        <v>387</v>
       </c>
       <c r="L386">
         <f t="shared" ca="1" si="7"/>
-        <v>239</v>
+        <v>129</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.3">
@@ -16380,15 +16427,15 @@
       </c>
       <c r="J387">
         <f t="shared" ref="J387:L418" ca="1" si="8">RANDBETWEEN(100,400)</f>
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="K387">
         <f t="shared" ca="1" si="8"/>
-        <v>372</v>
+        <v>216</v>
       </c>
       <c r="L387">
         <f t="shared" ca="1" si="8"/>
-        <v>372</v>
+        <v>280</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.3">
@@ -16421,15 +16468,15 @@
       </c>
       <c r="J388">
         <f t="shared" ca="1" si="8"/>
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="K388">
         <f t="shared" ca="1" si="8"/>
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="L388">
         <f t="shared" ca="1" si="8"/>
-        <v>173</v>
+        <v>264</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.3">
@@ -16462,15 +16509,15 @@
       </c>
       <c r="J389">
         <f t="shared" ca="1" si="8"/>
-        <v>238</v>
+        <v>126</v>
       </c>
       <c r="K389">
         <f t="shared" ca="1" si="8"/>
-        <v>378</v>
+        <v>180</v>
       </c>
       <c r="L389">
         <f t="shared" ca="1" si="8"/>
-        <v>367</v>
+        <v>353</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.3">
@@ -16503,15 +16550,15 @@
       </c>
       <c r="J390">
         <f t="shared" ca="1" si="8"/>
-        <v>168</v>
+        <v>357</v>
       </c>
       <c r="K390">
         <f t="shared" ca="1" si="8"/>
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="L390">
         <f t="shared" ca="1" si="8"/>
-        <v>197</v>
+        <v>271</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.3">
@@ -16544,15 +16591,15 @@
       </c>
       <c r="J391">
         <f t="shared" ca="1" si="8"/>
-        <v>355</v>
+        <v>172</v>
       </c>
       <c r="K391">
         <f t="shared" ca="1" si="8"/>
-        <v>356</v>
+        <v>253</v>
       </c>
       <c r="L391">
         <f t="shared" ca="1" si="8"/>
-        <v>284</v>
+        <v>319</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.3">
@@ -16585,15 +16632,15 @@
       </c>
       <c r="J392">
         <f t="shared" ca="1" si="8"/>
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="K392">
         <f t="shared" ca="1" si="8"/>
-        <v>146</v>
+        <v>301</v>
       </c>
       <c r="L392">
         <f t="shared" ca="1" si="8"/>
-        <v>395</v>
+        <v>170</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.3">
@@ -16626,15 +16673,15 @@
       </c>
       <c r="J393">
         <f t="shared" ca="1" si="8"/>
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="K393">
         <f t="shared" ca="1" si="8"/>
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="L393">
         <f t="shared" ca="1" si="8"/>
-        <v>355</v>
+        <v>210</v>
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.3">
@@ -16667,15 +16714,15 @@
       </c>
       <c r="J394">
         <f t="shared" ca="1" si="8"/>
-        <v>133</v>
+        <v>316</v>
       </c>
       <c r="K394">
         <f t="shared" ca="1" si="8"/>
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="L394">
         <f t="shared" ca="1" si="8"/>
-        <v>310</v>
+        <v>221</v>
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.3">
@@ -16708,15 +16755,15 @@
       </c>
       <c r="J395">
         <f t="shared" ca="1" si="8"/>
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="K395">
         <f t="shared" ca="1" si="8"/>
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="L395">
         <f t="shared" ca="1" si="8"/>
-        <v>319</v>
+        <v>396</v>
       </c>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.3">
@@ -16749,11 +16796,11 @@
       </c>
       <c r="J396">
         <f t="shared" ca="1" si="8"/>
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="K396">
         <f t="shared" ca="1" si="8"/>
-        <v>155</v>
+        <v>289</v>
       </c>
       <c r="L396">
         <f t="shared" ca="1" si="8"/>
@@ -16790,15 +16837,15 @@
       </c>
       <c r="J397">
         <f t="shared" ca="1" si="8"/>
-        <v>375</v>
+        <v>230</v>
       </c>
       <c r="K397">
         <f t="shared" ca="1" si="8"/>
-        <v>128</v>
+        <v>372</v>
       </c>
       <c r="L397">
         <f t="shared" ca="1" si="8"/>
-        <v>171</v>
+        <v>132</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.3">
@@ -16831,15 +16878,15 @@
       </c>
       <c r="J398">
         <f t="shared" ca="1" si="8"/>
-        <v>340</v>
+        <v>242</v>
       </c>
       <c r="K398">
         <f t="shared" ca="1" si="8"/>
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L398">
         <f t="shared" ca="1" si="8"/>
-        <v>236</v>
+        <v>380</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.3">
@@ -16872,15 +16919,15 @@
       </c>
       <c r="J399">
         <f t="shared" ca="1" si="8"/>
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="K399">
         <f t="shared" ca="1" si="8"/>
-        <v>235</v>
+        <v>389</v>
       </c>
       <c r="L399">
         <f t="shared" ca="1" si="8"/>
-        <v>313</v>
+        <v>126</v>
       </c>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.3">
@@ -16913,15 +16960,15 @@
       </c>
       <c r="J400">
         <f t="shared" ca="1" si="8"/>
-        <v>321</v>
+        <v>123</v>
       </c>
       <c r="K400">
         <f t="shared" ca="1" si="8"/>
-        <v>285</v>
+        <v>109</v>
       </c>
       <c r="L400">
         <f t="shared" ca="1" si="8"/>
-        <v>209</v>
+        <v>300</v>
       </c>
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.3">
@@ -16954,15 +17001,15 @@
       </c>
       <c r="J401">
         <f t="shared" ca="1" si="8"/>
-        <v>266</v>
+        <v>116</v>
       </c>
       <c r="K401">
         <f t="shared" ca="1" si="8"/>
-        <v>232</v>
+        <v>393</v>
       </c>
       <c r="L401">
         <f t="shared" ca="1" si="8"/>
-        <v>359</v>
+        <v>179</v>
       </c>
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.3">
@@ -16995,15 +17042,15 @@
       </c>
       <c r="J402">
         <f t="shared" ca="1" si="8"/>
-        <v>317</v>
+        <v>397</v>
       </c>
       <c r="K402">
         <f t="shared" ca="1" si="8"/>
-        <v>205</v>
+        <v>115</v>
       </c>
       <c r="L402">
         <f t="shared" ca="1" si="8"/>
-        <v>200</v>
+        <v>123</v>
       </c>
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.3">
@@ -17036,15 +17083,15 @@
       </c>
       <c r="J403">
         <f t="shared" ca="1" si="8"/>
-        <v>288</v>
+        <v>341</v>
       </c>
       <c r="K403">
         <f t="shared" ca="1" si="8"/>
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="L403">
         <f t="shared" ca="1" si="8"/>
-        <v>100</v>
+        <v>233</v>
       </c>
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.3">
@@ -17077,15 +17124,15 @@
       </c>
       <c r="J404">
         <f t="shared" ca="1" si="8"/>
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="K404">
         <f t="shared" ca="1" si="8"/>
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="L404">
         <f t="shared" ca="1" si="8"/>
-        <v>398</v>
+        <v>228</v>
       </c>
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.3">
@@ -17118,15 +17165,15 @@
       </c>
       <c r="J405">
         <f t="shared" ca="1" si="8"/>
-        <v>319</v>
+        <v>392</v>
       </c>
       <c r="K405">
         <f t="shared" ca="1" si="8"/>
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="L405">
         <f t="shared" ca="1" si="8"/>
-        <v>219</v>
+        <v>287</v>
       </c>
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.3">
@@ -17159,15 +17206,15 @@
       </c>
       <c r="J406">
         <f t="shared" ca="1" si="8"/>
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="K406">
         <f t="shared" ca="1" si="8"/>
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="L406">
         <f t="shared" ca="1" si="8"/>
-        <v>376</v>
+        <v>257</v>
       </c>
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.3">
@@ -17200,15 +17247,15 @@
       </c>
       <c r="J407">
         <f t="shared" ca="1" si="8"/>
-        <v>164</v>
+        <v>307</v>
       </c>
       <c r="K407">
         <f t="shared" ca="1" si="8"/>
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="L407">
         <f t="shared" ca="1" si="8"/>
-        <v>104</v>
+        <v>307</v>
       </c>
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.3">
@@ -17241,15 +17288,15 @@
       </c>
       <c r="J408">
         <f t="shared" ca="1" si="8"/>
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="K408">
         <f t="shared" ca="1" si="8"/>
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L408">
         <f t="shared" ca="1" si="8"/>
-        <v>385</v>
+        <v>240</v>
       </c>
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.3">
@@ -17282,15 +17329,15 @@
       </c>
       <c r="J409">
         <f t="shared" ca="1" si="8"/>
-        <v>380</v>
+        <v>337</v>
       </c>
       <c r="K409">
         <f t="shared" ca="1" si="8"/>
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="L409">
         <f t="shared" ca="1" si="8"/>
-        <v>290</v>
+        <v>262</v>
       </c>
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.3">
@@ -17323,15 +17370,15 @@
       </c>
       <c r="J410">
         <f t="shared" ca="1" si="8"/>
-        <v>164</v>
+        <v>353</v>
       </c>
       <c r="K410">
         <f t="shared" ca="1" si="8"/>
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="L410">
         <f t="shared" ca="1" si="8"/>
-        <v>376</v>
+        <v>399</v>
       </c>
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.3">
@@ -17364,15 +17411,15 @@
       </c>
       <c r="J411">
         <f t="shared" ca="1" si="8"/>
-        <v>331</v>
+        <v>182</v>
       </c>
       <c r="K411">
         <f t="shared" ca="1" si="8"/>
-        <v>336</v>
+        <v>106</v>
       </c>
       <c r="L411">
         <f t="shared" ca="1" si="8"/>
-        <v>243</v>
+        <v>208</v>
       </c>
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.3">
@@ -17405,15 +17452,15 @@
       </c>
       <c r="J412">
         <f t="shared" ca="1" si="8"/>
-        <v>211</v>
+        <v>264</v>
       </c>
       <c r="K412">
         <f t="shared" ca="1" si="8"/>
-        <v>217</v>
+        <v>154</v>
       </c>
       <c r="L412">
         <f t="shared" ca="1" si="8"/>
-        <v>185</v>
+        <v>270</v>
       </c>
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.3">
@@ -17446,15 +17493,15 @@
       </c>
       <c r="J413">
         <f t="shared" ca="1" si="8"/>
-        <v>130</v>
+        <v>389</v>
       </c>
       <c r="K413">
         <f t="shared" ca="1" si="8"/>
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="L413">
         <f t="shared" ca="1" si="8"/>
-        <v>296</v>
+        <v>192</v>
       </c>
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.3">
@@ -17487,15 +17534,15 @@
       </c>
       <c r="J414">
         <f t="shared" ca="1" si="8"/>
-        <v>248</v>
+        <v>367</v>
       </c>
       <c r="K414">
         <f t="shared" ca="1" si="8"/>
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="L414">
         <f t="shared" ca="1" si="8"/>
-        <v>147</v>
+        <v>368</v>
       </c>
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.3">
@@ -17528,15 +17575,15 @@
       </c>
       <c r="J415">
         <f t="shared" ca="1" si="8"/>
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="K415">
         <f t="shared" ca="1" si="8"/>
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="L415">
         <f t="shared" ca="1" si="8"/>
-        <v>381</v>
+        <v>181</v>
       </c>
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.3">
@@ -17569,15 +17616,15 @@
       </c>
       <c r="J416">
         <f t="shared" ca="1" si="8"/>
-        <v>382</v>
+        <v>160</v>
       </c>
       <c r="K416">
         <f t="shared" ca="1" si="8"/>
-        <v>198</v>
+        <v>320</v>
       </c>
       <c r="L416">
         <f t="shared" ca="1" si="8"/>
-        <v>387</v>
+        <v>329</v>
       </c>
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.3">
@@ -17610,15 +17657,15 @@
       </c>
       <c r="J417">
         <f t="shared" ca="1" si="8"/>
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="K417">
         <f t="shared" ca="1" si="8"/>
-        <v>381</v>
+        <v>339</v>
       </c>
       <c r="L417">
         <f t="shared" ca="1" si="8"/>
-        <v>190</v>
+        <v>362</v>
       </c>
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.3">
@@ -17651,15 +17698,15 @@
       </c>
       <c r="J418">
         <f t="shared" ca="1" si="8"/>
-        <v>209</v>
+        <v>148</v>
       </c>
       <c r="K418">
         <f t="shared" ca="1" si="8"/>
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="L418">
         <f t="shared" ca="1" si="8"/>
-        <v>117</v>
+        <v>198</v>
       </c>
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.3">
@@ -17692,15 +17739,15 @@
       </c>
       <c r="J419">
         <f t="shared" ref="J419:L450" ca="1" si="9">RANDBETWEEN(100,400)</f>
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="K419">
         <f t="shared" ca="1" si="9"/>
-        <v>122</v>
+        <v>258</v>
       </c>
       <c r="L419">
         <f t="shared" ca="1" si="9"/>
-        <v>145</v>
+        <v>373</v>
       </c>
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.3">
@@ -17733,15 +17780,15 @@
       </c>
       <c r="J420">
         <f t="shared" ca="1" si="9"/>
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="K420">
         <f t="shared" ca="1" si="9"/>
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="L420">
         <f t="shared" ca="1" si="9"/>
-        <v>327</v>
+        <v>264</v>
       </c>
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.3">
@@ -17774,15 +17821,15 @@
       </c>
       <c r="J421">
         <f t="shared" ca="1" si="9"/>
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="K421">
         <f t="shared" ca="1" si="9"/>
-        <v>383</v>
+        <v>247</v>
       </c>
       <c r="L421">
         <f t="shared" ca="1" si="9"/>
-        <v>367</v>
+        <v>354</v>
       </c>
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.3">
@@ -17815,15 +17862,15 @@
       </c>
       <c r="J422">
         <f t="shared" ca="1" si="9"/>
-        <v>314</v>
+        <v>141</v>
       </c>
       <c r="K422">
         <f t="shared" ca="1" si="9"/>
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="L422">
         <f t="shared" ca="1" si="9"/>
-        <v>229</v>
+        <v>176</v>
       </c>
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.3">
@@ -17856,15 +17903,15 @@
       </c>
       <c r="J423">
         <f t="shared" ca="1" si="9"/>
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="K423">
         <f t="shared" ca="1" si="9"/>
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="L423">
         <f t="shared" ca="1" si="9"/>
-        <v>251</v>
+        <v>369</v>
       </c>
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.3">
@@ -17897,15 +17944,15 @@
       </c>
       <c r="J424">
         <f t="shared" ca="1" si="9"/>
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="K424">
         <f t="shared" ca="1" si="9"/>
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="L424">
         <f t="shared" ca="1" si="9"/>
-        <v>206</v>
+        <v>382</v>
       </c>
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.3">
@@ -17938,15 +17985,15 @@
       </c>
       <c r="J425">
         <f t="shared" ca="1" si="9"/>
-        <v>389</v>
+        <v>252</v>
       </c>
       <c r="K425">
         <f t="shared" ca="1" si="9"/>
-        <v>155</v>
+        <v>219</v>
       </c>
       <c r="L425">
         <f t="shared" ca="1" si="9"/>
-        <v>259</v>
+        <v>162</v>
       </c>
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.3">
@@ -17979,15 +18026,15 @@
       </c>
       <c r="J426">
         <f t="shared" ca="1" si="9"/>
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="K426">
         <f t="shared" ca="1" si="9"/>
-        <v>234</v>
+        <v>103</v>
       </c>
       <c r="L426">
         <f t="shared" ca="1" si="9"/>
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.3">
@@ -18020,15 +18067,15 @@
       </c>
       <c r="J427">
         <f t="shared" ca="1" si="9"/>
-        <v>186</v>
+        <v>396</v>
       </c>
       <c r="K427">
         <f t="shared" ca="1" si="9"/>
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="L427">
         <f t="shared" ca="1" si="9"/>
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.3">
@@ -18061,15 +18108,15 @@
       </c>
       <c r="J428">
         <f t="shared" ca="1" si="9"/>
-        <v>203</v>
+        <v>312</v>
       </c>
       <c r="K428">
         <f t="shared" ca="1" si="9"/>
-        <v>361</v>
+        <v>267</v>
       </c>
       <c r="L428">
         <f t="shared" ca="1" si="9"/>
-        <v>207</v>
+        <v>254</v>
       </c>
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.3">
@@ -18102,15 +18149,15 @@
       </c>
       <c r="J429">
         <f t="shared" ca="1" si="9"/>
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="K429">
         <f t="shared" ca="1" si="9"/>
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="L429">
         <f t="shared" ca="1" si="9"/>
-        <v>132</v>
+        <v>278</v>
       </c>
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.3">
@@ -18143,15 +18190,15 @@
       </c>
       <c r="J430">
         <f t="shared" ca="1" si="9"/>
-        <v>125</v>
+        <v>396</v>
       </c>
       <c r="K430">
         <f t="shared" ca="1" si="9"/>
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="L430">
         <f t="shared" ca="1" si="9"/>
-        <v>183</v>
+        <v>369</v>
       </c>
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.3">
@@ -18184,15 +18231,15 @@
       </c>
       <c r="J431">
         <f t="shared" ca="1" si="9"/>
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="K431">
         <f t="shared" ca="1" si="9"/>
-        <v>124</v>
+        <v>271</v>
       </c>
       <c r="L431">
         <f t="shared" ca="1" si="9"/>
-        <v>126</v>
+        <v>285</v>
       </c>
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.3">
@@ -18225,15 +18272,15 @@
       </c>
       <c r="J432">
         <f t="shared" ca="1" si="9"/>
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="K432">
         <f t="shared" ca="1" si="9"/>
-        <v>242</v>
+        <v>127</v>
       </c>
       <c r="L432">
         <f t="shared" ca="1" si="9"/>
-        <v>250</v>
+        <v>156</v>
       </c>
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.3">
@@ -18266,15 +18313,15 @@
       </c>
       <c r="J433">
         <f t="shared" ca="1" si="9"/>
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="K433">
         <f t="shared" ca="1" si="9"/>
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="L433">
         <f t="shared" ca="1" si="9"/>
-        <v>318</v>
+        <v>127</v>
       </c>
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.3">
@@ -18307,15 +18354,15 @@
       </c>
       <c r="J434">
         <f t="shared" ca="1" si="9"/>
-        <v>207</v>
+        <v>295</v>
       </c>
       <c r="K434">
         <f t="shared" ca="1" si="9"/>
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="L434">
         <f t="shared" ca="1" si="9"/>
-        <v>257</v>
+        <v>319</v>
       </c>
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.3">
@@ -18348,15 +18395,15 @@
       </c>
       <c r="J435">
         <f t="shared" ca="1" si="9"/>
-        <v>194</v>
+        <v>304</v>
       </c>
       <c r="K435">
         <f t="shared" ca="1" si="9"/>
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="L435">
         <f t="shared" ca="1" si="9"/>
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.3">
@@ -18389,15 +18436,15 @@
       </c>
       <c r="J436">
         <f t="shared" ca="1" si="9"/>
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="K436">
         <f t="shared" ca="1" si="9"/>
-        <v>138</v>
+        <v>256</v>
       </c>
       <c r="L436">
         <f t="shared" ca="1" si="9"/>
-        <v>203</v>
+        <v>340</v>
       </c>
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.3">
@@ -18430,15 +18477,15 @@
       </c>
       <c r="J437">
         <f t="shared" ca="1" si="9"/>
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="K437">
         <f t="shared" ca="1" si="9"/>
-        <v>112</v>
+        <v>214</v>
       </c>
       <c r="L437">
         <f t="shared" ca="1" si="9"/>
-        <v>161</v>
+        <v>289</v>
       </c>
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.3">
@@ -18471,15 +18518,15 @@
       </c>
       <c r="J438">
         <f t="shared" ca="1" si="9"/>
-        <v>398</v>
+        <v>112</v>
       </c>
       <c r="K438">
         <f t="shared" ca="1" si="9"/>
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="L438">
         <f t="shared" ca="1" si="9"/>
-        <v>335</v>
+        <v>262</v>
       </c>
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.3">
@@ -18512,15 +18559,15 @@
       </c>
       <c r="J439">
         <f t="shared" ca="1" si="9"/>
-        <v>295</v>
+        <v>398</v>
       </c>
       <c r="K439">
         <f t="shared" ca="1" si="9"/>
-        <v>325</v>
+        <v>189</v>
       </c>
       <c r="L439">
         <f t="shared" ca="1" si="9"/>
-        <v>132</v>
+        <v>387</v>
       </c>
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.3">
@@ -18553,15 +18600,15 @@
       </c>
       <c r="J440">
         <f t="shared" ca="1" si="9"/>
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="K440">
         <f t="shared" ca="1" si="9"/>
-        <v>120</v>
+        <v>233</v>
       </c>
       <c r="L440">
         <f t="shared" ca="1" si="9"/>
-        <v>167</v>
+        <v>128</v>
       </c>
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.3">
@@ -18594,15 +18641,15 @@
       </c>
       <c r="J441">
         <f t="shared" ca="1" si="9"/>
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="K441">
         <f t="shared" ca="1" si="9"/>
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L441">
         <f t="shared" ca="1" si="9"/>
-        <v>237</v>
+        <v>340</v>
       </c>
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.3">
@@ -18635,15 +18682,15 @@
       </c>
       <c r="J442">
         <f t="shared" ca="1" si="9"/>
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="K442">
         <f t="shared" ca="1" si="9"/>
-        <v>290</v>
+        <v>357</v>
       </c>
       <c r="L442">
         <f t="shared" ca="1" si="9"/>
-        <v>135</v>
+        <v>366</v>
       </c>
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.3">
@@ -18676,15 +18723,15 @@
       </c>
       <c r="J443">
         <f t="shared" ca="1" si="9"/>
-        <v>188</v>
+        <v>383</v>
       </c>
       <c r="K443">
         <f t="shared" ca="1" si="9"/>
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="L443">
         <f t="shared" ca="1" si="9"/>
-        <v>205</v>
+        <v>372</v>
       </c>
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.3">
@@ -18717,15 +18764,15 @@
       </c>
       <c r="J444">
         <f t="shared" ca="1" si="9"/>
-        <v>381</v>
+        <v>245</v>
       </c>
       <c r="K444">
         <f t="shared" ca="1" si="9"/>
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="L444">
         <f t="shared" ca="1" si="9"/>
-        <v>293</v>
+        <v>358</v>
       </c>
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.3">
@@ -18758,15 +18805,15 @@
       </c>
       <c r="J445">
         <f t="shared" ca="1" si="9"/>
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="K445">
         <f t="shared" ca="1" si="9"/>
-        <v>276</v>
+        <v>117</v>
       </c>
       <c r="L445">
         <f t="shared" ca="1" si="9"/>
-        <v>127</v>
+        <v>390</v>
       </c>
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.3">
@@ -18803,11 +18850,11 @@
       </c>
       <c r="K446">
         <f t="shared" ca="1" si="9"/>
-        <v>398</v>
+        <v>177</v>
       </c>
       <c r="L446">
         <f t="shared" ca="1" si="9"/>
-        <v>400</v>
+        <v>311</v>
       </c>
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.3">
@@ -18840,15 +18887,15 @@
       </c>
       <c r="J447">
         <f t="shared" ca="1" si="9"/>
-        <v>343</v>
+        <v>189</v>
       </c>
       <c r="K447">
         <f t="shared" ca="1" si="9"/>
-        <v>332</v>
+        <v>187</v>
       </c>
       <c r="L447">
         <f t="shared" ca="1" si="9"/>
-        <v>358</v>
+        <v>295</v>
       </c>
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.3">
@@ -18881,15 +18928,15 @@
       </c>
       <c r="J448">
         <f t="shared" ca="1" si="9"/>
-        <v>361</v>
+        <v>250</v>
       </c>
       <c r="K448">
         <f t="shared" ca="1" si="9"/>
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="L448">
         <f t="shared" ca="1" si="9"/>
-        <v>379</v>
+        <v>153</v>
       </c>
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.3">
@@ -18922,15 +18969,15 @@
       </c>
       <c r="J449">
         <f t="shared" ca="1" si="9"/>
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K449">
         <f t="shared" ca="1" si="9"/>
-        <v>385</v>
+        <v>161</v>
       </c>
       <c r="L449">
         <f t="shared" ca="1" si="9"/>
-        <v>146</v>
+        <v>188</v>
       </c>
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.3">
@@ -18963,15 +19010,15 @@
       </c>
       <c r="J450">
         <f t="shared" ca="1" si="9"/>
-        <v>353</v>
+        <v>141</v>
       </c>
       <c r="K450">
         <f t="shared" ca="1" si="9"/>
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="L450">
         <f t="shared" ca="1" si="9"/>
-        <v>115</v>
+        <v>171</v>
       </c>
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.3">
@@ -19004,15 +19051,15 @@
       </c>
       <c r="J451">
         <f t="shared" ref="J451:L481" ca="1" si="10">RANDBETWEEN(100,400)</f>
-        <v>160</v>
+        <v>315</v>
       </c>
       <c r="K451">
         <f t="shared" ca="1" si="10"/>
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="L451">
         <f t="shared" ca="1" si="10"/>
-        <v>132</v>
+        <v>222</v>
       </c>
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.3">
@@ -19045,15 +19092,15 @@
       </c>
       <c r="J452">
         <f t="shared" ca="1" si="10"/>
-        <v>116</v>
+        <v>316</v>
       </c>
       <c r="K452">
         <f t="shared" ca="1" si="10"/>
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="L452">
         <f t="shared" ca="1" si="10"/>
-        <v>379</v>
+        <v>362</v>
       </c>
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.3">
@@ -19086,15 +19133,15 @@
       </c>
       <c r="J453">
         <f t="shared" ca="1" si="10"/>
-        <v>282</v>
+        <v>166</v>
       </c>
       <c r="K453">
         <f t="shared" ca="1" si="10"/>
-        <v>160</v>
+        <v>382</v>
       </c>
       <c r="L453">
         <f t="shared" ca="1" si="10"/>
-        <v>222</v>
+        <v>270</v>
       </c>
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.3">
@@ -19127,15 +19174,15 @@
       </c>
       <c r="J454">
         <f t="shared" ca="1" si="10"/>
-        <v>131</v>
+        <v>337</v>
       </c>
       <c r="K454">
         <f t="shared" ca="1" si="10"/>
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="L454">
         <f t="shared" ca="1" si="10"/>
-        <v>387</v>
+        <v>257</v>
       </c>
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.3">
@@ -19168,15 +19215,15 @@
       </c>
       <c r="J455">
         <f t="shared" ca="1" si="10"/>
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="K455">
         <f t="shared" ca="1" si="10"/>
-        <v>332</v>
+        <v>103</v>
       </c>
       <c r="L455">
         <f t="shared" ca="1" si="10"/>
-        <v>350</v>
+        <v>191</v>
       </c>
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.3">
@@ -19209,15 +19256,15 @@
       </c>
       <c r="J456">
         <f t="shared" ca="1" si="10"/>
-        <v>341</v>
+        <v>110</v>
       </c>
       <c r="K456">
         <f t="shared" ca="1" si="10"/>
-        <v>385</v>
+        <v>268</v>
       </c>
       <c r="L456">
         <f t="shared" ca="1" si="10"/>
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.3">
@@ -19250,15 +19297,15 @@
       </c>
       <c r="J457">
         <f t="shared" ca="1" si="10"/>
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="K457">
         <f t="shared" ca="1" si="10"/>
-        <v>174</v>
+        <v>395</v>
       </c>
       <c r="L457">
         <f t="shared" ca="1" si="10"/>
-        <v>219</v>
+        <v>185</v>
       </c>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.3">
@@ -19291,15 +19338,15 @@
       </c>
       <c r="J458">
         <f t="shared" ca="1" si="10"/>
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="K458">
         <f t="shared" ca="1" si="10"/>
-        <v>227</v>
+        <v>389</v>
       </c>
       <c r="L458">
         <f t="shared" ca="1" si="10"/>
-        <v>363</v>
+        <v>294</v>
       </c>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.3">
@@ -19332,15 +19379,15 @@
       </c>
       <c r="J459">
         <f t="shared" ca="1" si="10"/>
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K459">
         <f t="shared" ca="1" si="10"/>
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="L459">
         <f t="shared" ca="1" si="10"/>
-        <v>355</v>
+        <v>237</v>
       </c>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.3">
@@ -19373,15 +19420,15 @@
       </c>
       <c r="J460">
         <f t="shared" ca="1" si="10"/>
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="K460">
         <f t="shared" ca="1" si="10"/>
-        <v>192</v>
+        <v>290</v>
       </c>
       <c r="L460">
         <f t="shared" ca="1" si="10"/>
-        <v>194</v>
+        <v>360</v>
       </c>
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.3">
@@ -19414,11 +19461,11 @@
       </c>
       <c r="J461">
         <f t="shared" ca="1" si="10"/>
-        <v>200</v>
+        <v>359</v>
       </c>
       <c r="K461">
         <f t="shared" ca="1" si="10"/>
-        <v>117</v>
+        <v>216</v>
       </c>
       <c r="L461">
         <f t="shared" ca="1" si="10"/>
@@ -19455,15 +19502,15 @@
       </c>
       <c r="J462">
         <f t="shared" ca="1" si="10"/>
-        <v>372</v>
+        <v>125</v>
       </c>
       <c r="K462">
         <f t="shared" ca="1" si="10"/>
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="L462">
         <f t="shared" ca="1" si="10"/>
-        <v>252</v>
+        <v>297</v>
       </c>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.3">
@@ -19496,15 +19543,15 @@
       </c>
       <c r="J463">
         <f t="shared" ca="1" si="10"/>
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="K463">
         <f t="shared" ca="1" si="10"/>
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="L463">
         <f t="shared" ca="1" si="10"/>
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.3">
@@ -19537,15 +19584,15 @@
       </c>
       <c r="J464">
         <f t="shared" ca="1" si="10"/>
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="K464">
         <f t="shared" ca="1" si="10"/>
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="L464">
         <f t="shared" ca="1" si="10"/>
-        <v>284</v>
+        <v>194</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.3">
@@ -19578,15 +19625,15 @@
       </c>
       <c r="J465">
         <f t="shared" ca="1" si="10"/>
-        <v>398</v>
+        <v>259</v>
       </c>
       <c r="K465">
         <f t="shared" ca="1" si="10"/>
-        <v>370</v>
+        <v>242</v>
       </c>
       <c r="L465">
         <f t="shared" ca="1" si="10"/>
-        <v>309</v>
+        <v>338</v>
       </c>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.3">
@@ -19619,15 +19666,15 @@
       </c>
       <c r="J466">
         <f t="shared" ca="1" si="10"/>
-        <v>272</v>
+        <v>207</v>
       </c>
       <c r="K466">
         <f t="shared" ca="1" si="10"/>
-        <v>182</v>
+        <v>344</v>
       </c>
       <c r="L466">
         <f t="shared" ca="1" si="10"/>
-        <v>328</v>
+        <v>365</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.3">
@@ -19660,15 +19707,15 @@
       </c>
       <c r="J467">
         <f t="shared" ca="1" si="10"/>
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="K467">
         <f t="shared" ca="1" si="10"/>
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="L467">
         <f t="shared" ca="1" si="10"/>
-        <v>235</v>
+        <v>167</v>
       </c>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.3">
@@ -19701,15 +19748,15 @@
       </c>
       <c r="J468">
         <f t="shared" ca="1" si="10"/>
-        <v>101</v>
+        <v>253</v>
       </c>
       <c r="K468">
         <f t="shared" ca="1" si="10"/>
-        <v>130</v>
+        <v>354</v>
       </c>
       <c r="L468">
         <f t="shared" ca="1" si="10"/>
-        <v>120</v>
+        <v>373</v>
       </c>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.3">
@@ -19742,15 +19789,15 @@
       </c>
       <c r="J469">
         <f t="shared" ca="1" si="10"/>
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K469">
         <f t="shared" ca="1" si="10"/>
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="L469">
         <f t="shared" ca="1" si="10"/>
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.3">
@@ -19783,15 +19830,15 @@
       </c>
       <c r="J470">
         <f t="shared" ca="1" si="10"/>
-        <v>122</v>
+        <v>359</v>
       </c>
       <c r="K470">
         <f t="shared" ca="1" si="10"/>
-        <v>229</v>
+        <v>141</v>
       </c>
       <c r="L470">
         <f t="shared" ca="1" si="10"/>
-        <v>216</v>
+        <v>293</v>
       </c>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.3">
@@ -19824,15 +19871,15 @@
       </c>
       <c r="J471">
         <f t="shared" ca="1" si="10"/>
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="K471">
         <f t="shared" ca="1" si="10"/>
-        <v>317</v>
+        <v>133</v>
       </c>
       <c r="L471">
         <f t="shared" ca="1" si="10"/>
-        <v>214</v>
+        <v>142</v>
       </c>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.3">
@@ -19865,15 +19912,15 @@
       </c>
       <c r="J472">
         <f t="shared" ca="1" si="10"/>
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="K472">
         <f t="shared" ca="1" si="10"/>
-        <v>220</v>
+        <v>117</v>
       </c>
       <c r="L472">
         <f t="shared" ca="1" si="10"/>
-        <v>388</v>
+        <v>303</v>
       </c>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.3">
@@ -19906,15 +19953,15 @@
       </c>
       <c r="J473">
         <f t="shared" ca="1" si="10"/>
-        <v>218</v>
+        <v>395</v>
       </c>
       <c r="K473">
         <f t="shared" ca="1" si="10"/>
-        <v>398</v>
+        <v>149</v>
       </c>
       <c r="L473">
         <f t="shared" ca="1" si="10"/>
-        <v>340</v>
+        <v>250</v>
       </c>
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.3">
@@ -19947,15 +19994,15 @@
       </c>
       <c r="J474">
         <f t="shared" ca="1" si="10"/>
-        <v>139</v>
+        <v>287</v>
       </c>
       <c r="K474">
         <f t="shared" ca="1" si="10"/>
-        <v>293</v>
+        <v>207</v>
       </c>
       <c r="L474">
         <f t="shared" ca="1" si="10"/>
-        <v>106</v>
+        <v>355</v>
       </c>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.3">
@@ -19988,15 +20035,15 @@
       </c>
       <c r="J475">
         <f t="shared" ca="1" si="10"/>
-        <v>251</v>
+        <v>147</v>
       </c>
       <c r="K475">
         <f t="shared" ca="1" si="10"/>
-        <v>298</v>
+        <v>400</v>
       </c>
       <c r="L475">
         <f t="shared" ca="1" si="10"/>
-        <v>188</v>
+        <v>204</v>
       </c>
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.3">
@@ -20029,15 +20076,15 @@
       </c>
       <c r="J476">
         <f t="shared" ca="1" si="10"/>
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K476">
         <f t="shared" ca="1" si="10"/>
-        <v>327</v>
+        <v>284</v>
       </c>
       <c r="L476">
         <f t="shared" ca="1" si="10"/>
-        <v>291</v>
+        <v>366</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.3">
@@ -20070,15 +20117,15 @@
       </c>
       <c r="J477">
         <f t="shared" ca="1" si="10"/>
-        <v>360</v>
+        <v>160</v>
       </c>
       <c r="K477">
         <f t="shared" ca="1" si="10"/>
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="L477">
         <f t="shared" ca="1" si="10"/>
-        <v>175</v>
+        <v>199</v>
       </c>
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.3">
@@ -20111,15 +20158,15 @@
       </c>
       <c r="J478">
         <f t="shared" ca="1" si="10"/>
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="K478">
         <f t="shared" ca="1" si="10"/>
-        <v>290</v>
+        <v>161</v>
       </c>
       <c r="L478">
         <f t="shared" ca="1" si="10"/>
-        <v>181</v>
+        <v>393</v>
       </c>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.3">
@@ -20152,15 +20199,15 @@
       </c>
       <c r="J479">
         <f t="shared" ca="1" si="10"/>
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="K479">
         <f t="shared" ca="1" si="10"/>
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="L479">
         <f t="shared" ca="1" si="10"/>
-        <v>122</v>
+        <v>377</v>
       </c>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.3">
@@ -20193,15 +20240,15 @@
       </c>
       <c r="J480">
         <f t="shared" ca="1" si="10"/>
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="K480">
         <f t="shared" ca="1" si="10"/>
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="L480">
         <f t="shared" ca="1" si="10"/>
-        <v>246</v>
+        <v>351</v>
       </c>
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.3">
@@ -20234,15 +20281,15 @@
       </c>
       <c r="J481">
         <f t="shared" ca="1" si="10"/>
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="K481">
         <f t="shared" ca="1" si="10"/>
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="L481">
         <f t="shared" ca="1" si="10"/>
-        <v>397</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data_panen_dummy.xlsx
+++ b/data_panen_dummy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vansa\Documents\Kulyeah\Epidem\db_tajumase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2A0BF8-B514-44CF-8656-48A21AED0331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE23770F-E1F9-4C90-A061-BE6962A32A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="56">
   <si>
     <t>Program</t>
   </si>
@@ -193,6 +193,12 @@
   </si>
   <si>
     <t>Sampo</t>
+  </si>
+  <si>
+    <t>Bubuk Cabai</t>
+  </si>
+  <si>
+    <t>Kain</t>
   </si>
 </sst>
 </file>
@@ -537,6 +543,7 @@
   <cols>
     <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
     <col min="9" max="9" width="13.77734375" customWidth="1"/>
     <col min="10" max="10" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -624,15 +631,15 @@
       </c>
       <c r="J2">
         <f ca="1">RANDBETWEEN(100,400)</f>
-        <v>358</v>
+        <v>128</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:L17" ca="1" si="0">RANDBETWEEN(100,400)</f>
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="L2">
         <f t="shared" ca="1" si="0"/>
-        <v>233</v>
+        <v>395</v>
       </c>
       <c r="M2" t="s">
         <v>50</v>
@@ -674,15 +681,15 @@
       </c>
       <c r="J3">
         <f t="shared" ref="J3:L66" ca="1" si="1">RANDBETWEEN(100,400)</f>
-        <v>272</v>
+        <v>143</v>
       </c>
       <c r="K3">
         <f t="shared" ca="1" si="0"/>
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="0"/>
-        <v>179</v>
+        <v>296</v>
       </c>
       <c r="M3" t="s">
         <v>53</v>
@@ -724,15 +731,15 @@
       </c>
       <c r="J4">
         <f t="shared" ca="1" si="1"/>
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="0"/>
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="0"/>
-        <v>306</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -765,15 +772,15 @@
       </c>
       <c r="J5">
         <f t="shared" ca="1" si="1"/>
-        <v>337</v>
+        <v>157</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="0"/>
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="0"/>
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -806,15 +813,15 @@
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="1"/>
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="0"/>
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="0"/>
-        <v>190</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -847,15 +854,15 @@
       </c>
       <c r="J7">
         <f t="shared" ca="1" si="1"/>
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="0"/>
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="0"/>
-        <v>139</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -892,11 +899,11 @@
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="0"/>
-        <v>344</v>
+        <v>124</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="0"/>
-        <v>198</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -929,15 +936,15 @@
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="1"/>
-        <v>251</v>
+        <v>179</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="0"/>
-        <v>195</v>
+        <v>384</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="0"/>
-        <v>362</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -970,15 +977,15 @@
       </c>
       <c r="J10">
         <f t="shared" ca="1" si="1"/>
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="0"/>
-        <v>312</v>
+        <v>134</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="0"/>
-        <v>145</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1011,15 +1018,15 @@
       </c>
       <c r="J11">
         <f t="shared" ca="1" si="1"/>
-        <v>371</v>
+        <v>186</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="0"/>
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="0"/>
-        <v>328</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1052,15 +1059,15 @@
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="1"/>
-        <v>245</v>
+        <v>152</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="0"/>
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="0"/>
-        <v>371</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1093,15 +1100,15 @@
       </c>
       <c r="J13">
         <f t="shared" ca="1" si="1"/>
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="0"/>
-        <v>220</v>
+        <v>167</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="0"/>
-        <v>340</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1134,15 +1141,15 @@
       </c>
       <c r="J14">
         <f t="shared" ca="1" si="1"/>
-        <v>162</v>
+        <v>297</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="0"/>
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="0"/>
-        <v>161</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -1175,15 +1182,15 @@
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="0"/>
-        <v>245</v>
+        <v>125</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="0"/>
-        <v>146</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1216,15 +1223,15 @@
       </c>
       <c r="J16">
         <f t="shared" ca="1" si="1"/>
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="0"/>
-        <v>152</v>
+        <v>400</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="0"/>
-        <v>393</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1257,15 +1264,15 @@
       </c>
       <c r="J17">
         <f t="shared" ca="1" si="1"/>
-        <v>342</v>
+        <v>121</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="0"/>
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="0"/>
-        <v>225</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1298,15 +1305,15 @@
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="1"/>
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="1"/>
-        <v>269</v>
+        <v>382</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="1"/>
-        <v>183</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1339,15 +1346,15 @@
       </c>
       <c r="J19">
         <f t="shared" ca="1" si="1"/>
-        <v>356</v>
+        <v>248</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="1"/>
-        <v>275</v>
+        <v>370</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="1"/>
-        <v>274</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1380,15 +1387,15 @@
       </c>
       <c r="J20">
         <f t="shared" ca="1" si="1"/>
-        <v>363</v>
+        <v>202</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="1"/>
-        <v>179</v>
+        <v>400</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="1"/>
-        <v>280</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1421,11 +1428,11 @@
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="1"/>
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="1"/>
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="1"/>
@@ -1462,15 +1469,15 @@
       </c>
       <c r="J22">
         <f t="shared" ca="1" si="1"/>
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="1"/>
-        <v>384</v>
+        <v>295</v>
       </c>
       <c r="L22">
         <f t="shared" ca="1" si="1"/>
-        <v>152</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1503,15 +1510,15 @@
       </c>
       <c r="J23">
         <f t="shared" ca="1" si="1"/>
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="K23">
         <f t="shared" ca="1" si="1"/>
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="L23">
         <f t="shared" ca="1" si="1"/>
-        <v>300</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1544,15 +1551,15 @@
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="1"/>
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="1"/>
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="L24">
         <f t="shared" ca="1" si="1"/>
-        <v>169</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1585,15 +1592,15 @@
       </c>
       <c r="J25">
         <f t="shared" ca="1" si="1"/>
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="1"/>
-        <v>366</v>
+        <v>269</v>
       </c>
       <c r="L25">
         <f t="shared" ca="1" si="1"/>
-        <v>142</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -1626,15 +1633,15 @@
       </c>
       <c r="J26">
         <f t="shared" ca="1" si="1"/>
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="K26">
         <f t="shared" ca="1" si="1"/>
-        <v>374</v>
+        <v>298</v>
       </c>
       <c r="L26">
         <f t="shared" ca="1" si="1"/>
-        <v>167</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -1667,15 +1674,15 @@
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="1"/>
-        <v>359</v>
+        <v>114</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="1"/>
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="L27">
         <f t="shared" ca="1" si="1"/>
-        <v>145</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -1708,15 +1715,15 @@
       </c>
       <c r="J28">
         <f t="shared" ca="1" si="1"/>
-        <v>335</v>
+        <v>163</v>
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="1"/>
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="L28">
         <f t="shared" ca="1" si="1"/>
-        <v>124</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -1749,15 +1756,15 @@
       </c>
       <c r="J29">
         <f t="shared" ca="1" si="1"/>
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="K29">
         <f t="shared" ca="1" si="1"/>
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="L29">
         <f t="shared" ca="1" si="1"/>
-        <v>378</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -1790,15 +1797,15 @@
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="1"/>
-        <v>398</v>
+        <v>259</v>
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="1"/>
-        <v>198</v>
+        <v>129</v>
       </c>
       <c r="L30">
         <f t="shared" ca="1" si="1"/>
-        <v>322</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -1831,15 +1838,15 @@
       </c>
       <c r="J31">
         <f t="shared" ca="1" si="1"/>
-        <v>138</v>
+        <v>391</v>
       </c>
       <c r="K31">
         <f t="shared" ca="1" si="1"/>
-        <v>205</v>
+        <v>316</v>
       </c>
       <c r="L31">
         <f t="shared" ca="1" si="1"/>
-        <v>356</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -1872,15 +1879,15 @@
       </c>
       <c r="J32">
         <f t="shared" ca="1" si="1"/>
-        <v>118</v>
+        <v>257</v>
       </c>
       <c r="K32">
         <f t="shared" ca="1" si="1"/>
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="L32">
         <f t="shared" ca="1" si="1"/>
-        <v>298</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -1913,15 +1920,15 @@
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="1"/>
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="1"/>
-        <v>338</v>
+        <v>269</v>
       </c>
       <c r="L33">
         <f t="shared" ca="1" si="1"/>
-        <v>208</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -1954,15 +1961,15 @@
       </c>
       <c r="J34">
         <f t="shared" ca="1" si="1"/>
-        <v>244</v>
+        <v>190</v>
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="1"/>
-        <v>365</v>
+        <v>236</v>
       </c>
       <c r="L34">
         <f t="shared" ca="1" si="1"/>
-        <v>211</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -1995,15 +2002,15 @@
       </c>
       <c r="J35">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K35">
         <f t="shared" ca="1" si="1"/>
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="L35">
         <f t="shared" ca="1" si="1"/>
-        <v>306</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -2036,15 +2043,15 @@
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="1"/>
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="1"/>
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="L36">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
+        <v>379</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -2077,15 +2084,15 @@
       </c>
       <c r="J37">
         <f t="shared" ca="1" si="1"/>
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="1"/>
-        <v>337</v>
+        <v>116</v>
       </c>
       <c r="L37">
         <f t="shared" ca="1" si="1"/>
-        <v>314</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2118,15 +2125,15 @@
       </c>
       <c r="J38">
         <f t="shared" ca="1" si="1"/>
-        <v>271</v>
+        <v>102</v>
       </c>
       <c r="K38">
         <f t="shared" ca="1" si="1"/>
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="L38">
         <f t="shared" ca="1" si="1"/>
-        <v>239</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2159,15 +2166,15 @@
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="1"/>
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="1"/>
-        <v>206</v>
+        <v>394</v>
       </c>
       <c r="L39">
         <f t="shared" ca="1" si="1"/>
-        <v>275</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2200,15 +2207,15 @@
       </c>
       <c r="J40">
         <f t="shared" ca="1" si="1"/>
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="K40">
         <f t="shared" ca="1" si="1"/>
-        <v>102</v>
+        <v>238</v>
       </c>
       <c r="L40">
         <f t="shared" ca="1" si="1"/>
-        <v>364</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2241,15 +2248,15 @@
       </c>
       <c r="J41">
         <f t="shared" ca="1" si="1"/>
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="K41">
         <f t="shared" ca="1" si="1"/>
-        <v>199</v>
+        <v>392</v>
       </c>
       <c r="L41">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2282,15 +2289,15 @@
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="1"/>
-        <v>398</v>
+        <v>147</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="1"/>
-        <v>201</v>
+        <v>348</v>
       </c>
       <c r="L42">
         <f t="shared" ca="1" si="1"/>
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2323,15 +2330,15 @@
       </c>
       <c r="J43">
         <f t="shared" ca="1" si="1"/>
-        <v>231</v>
+        <v>329</v>
       </c>
       <c r="K43">
         <f t="shared" ca="1" si="1"/>
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="L43">
         <f t="shared" ca="1" si="1"/>
-        <v>124</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -2364,15 +2371,15 @@
       </c>
       <c r="J44">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>378</v>
       </c>
       <c r="K44">
         <f t="shared" ca="1" si="1"/>
-        <v>179</v>
+        <v>339</v>
       </c>
       <c r="L44">
         <f t="shared" ca="1" si="1"/>
-        <v>207</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2405,15 +2412,15 @@
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="1"/>
-        <v>316</v>
+        <v>133</v>
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="1"/>
-        <v>355</v>
+        <v>396</v>
       </c>
       <c r="L45">
         <f t="shared" ca="1" si="1"/>
-        <v>164</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -2446,15 +2453,15 @@
       </c>
       <c r="J46">
         <f t="shared" ca="1" si="1"/>
-        <v>263</v>
+        <v>321</v>
       </c>
       <c r="K46">
         <f t="shared" ca="1" si="1"/>
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="L46">
         <f t="shared" ca="1" si="1"/>
-        <v>170</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -2487,15 +2494,15 @@
       </c>
       <c r="J47">
         <f t="shared" ca="1" si="1"/>
-        <v>357</v>
+        <v>162</v>
       </c>
       <c r="K47">
         <f t="shared" ca="1" si="1"/>
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="L47">
         <f t="shared" ca="1" si="1"/>
-        <v>178</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -2528,18 +2535,18 @@
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="1"/>
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="1"/>
-        <v>346</v>
+        <v>254</v>
       </c>
       <c r="L48">
         <f t="shared" ca="1" si="1"/>
-        <v>370</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -2569,18 +2576,18 @@
       </c>
       <c r="J49">
         <f t="shared" ca="1" si="1"/>
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="1"/>
-        <v>221</v>
+        <v>306</v>
       </c>
       <c r="L49">
         <f t="shared" ca="1" si="1"/>
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -2610,18 +2617,18 @@
       </c>
       <c r="J50">
         <f t="shared" ca="1" si="1"/>
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="1"/>
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="L50">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -2651,18 +2658,18 @@
       </c>
       <c r="J51">
         <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="1"/>
-        <v>283</v>
+        <v>180</v>
       </c>
       <c r="L51">
         <f t="shared" ca="1" si="1"/>
-        <v>284</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -2692,18 +2699,27 @@
       </c>
       <c r="J52">
         <f t="shared" ca="1" si="1"/>
-        <v>391</v>
+        <v>227</v>
       </c>
       <c r="K52">
         <f t="shared" ca="1" si="1"/>
-        <v>128</v>
+        <v>273</v>
       </c>
       <c r="L52">
         <f t="shared" ca="1" si="1"/>
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+        <v>364</v>
+      </c>
+      <c r="M52" t="s">
+        <v>54</v>
+      </c>
+      <c r="N52">
+        <v>23</v>
+      </c>
+      <c r="O52">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>26</v>
       </c>
@@ -2733,18 +2749,27 @@
       </c>
       <c r="J53">
         <f t="shared" ca="1" si="1"/>
-        <v>285</v>
+        <v>146</v>
       </c>
       <c r="K53">
         <f t="shared" ca="1" si="1"/>
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="L53">
         <f t="shared" ca="1" si="1"/>
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+      <c r="M53" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53">
+        <v>42</v>
+      </c>
+      <c r="O53">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -2774,18 +2799,18 @@
       </c>
       <c r="J54">
         <f t="shared" ca="1" si="1"/>
-        <v>238</v>
+        <v>147</v>
       </c>
       <c r="K54">
         <f t="shared" ca="1" si="1"/>
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="L54">
         <f t="shared" ca="1" si="1"/>
-        <v>261</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>26</v>
       </c>
@@ -2815,18 +2840,18 @@
       </c>
       <c r="J55">
         <f t="shared" ca="1" si="1"/>
-        <v>374</v>
+        <v>231</v>
       </c>
       <c r="K55">
         <f t="shared" ca="1" si="1"/>
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="L55">
         <f t="shared" ca="1" si="1"/>
-        <v>191</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -2856,18 +2881,18 @@
       </c>
       <c r="J56">
         <f t="shared" ca="1" si="1"/>
-        <v>149</v>
+        <v>311</v>
       </c>
       <c r="K56">
         <f t="shared" ca="1" si="1"/>
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="L56">
         <f t="shared" ca="1" si="1"/>
-        <v>323</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -2897,18 +2922,18 @@
       </c>
       <c r="J57">
         <f t="shared" ca="1" si="1"/>
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K57">
         <f t="shared" ca="1" si="1"/>
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="L57">
         <f t="shared" ca="1" si="1"/>
-        <v>274</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -2938,18 +2963,18 @@
       </c>
       <c r="J58">
         <f t="shared" ca="1" si="1"/>
-        <v>372</v>
+        <v>227</v>
       </c>
       <c r="K58">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="L58">
         <f t="shared" ca="1" si="1"/>
-        <v>326</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -2979,18 +3004,18 @@
       </c>
       <c r="J59">
         <f t="shared" ca="1" si="1"/>
-        <v>366</v>
+        <v>162</v>
       </c>
       <c r="K59">
         <f t="shared" ca="1" si="1"/>
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="L59">
         <f t="shared" ca="1" si="1"/>
-        <v>334</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -3020,18 +3045,18 @@
       </c>
       <c r="J60">
         <f t="shared" ca="1" si="1"/>
-        <v>150</v>
+        <v>223</v>
       </c>
       <c r="K60">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
+        <v>162</v>
       </c>
       <c r="L60">
         <f t="shared" ca="1" si="1"/>
-        <v>252</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -3061,18 +3086,18 @@
       </c>
       <c r="J61">
         <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="K61">
         <f t="shared" ca="1" si="1"/>
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="L61">
         <f t="shared" ca="1" si="1"/>
-        <v>134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>26</v>
       </c>
@@ -3102,18 +3127,18 @@
       </c>
       <c r="J62">
         <f t="shared" ca="1" si="1"/>
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="K62">
         <f t="shared" ca="1" si="1"/>
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="L62">
         <f t="shared" ca="1" si="1"/>
-        <v>328</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>26</v>
       </c>
@@ -3143,18 +3168,18 @@
       </c>
       <c r="J63">
         <f t="shared" ca="1" si="1"/>
-        <v>391</v>
+        <v>230</v>
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="1"/>
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="L63">
         <f t="shared" ca="1" si="1"/>
-        <v>117</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>26</v>
       </c>
@@ -3184,15 +3209,15 @@
       </c>
       <c r="J64">
         <f t="shared" ca="1" si="1"/>
-        <v>360</v>
+        <v>265</v>
       </c>
       <c r="K64">
         <f t="shared" ca="1" si="1"/>
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="L64">
         <f t="shared" ca="1" si="1"/>
-        <v>297</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -3225,15 +3250,15 @@
       </c>
       <c r="J65">
         <f t="shared" ca="1" si="1"/>
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="K65">
         <f t="shared" ca="1" si="1"/>
-        <v>122</v>
+        <v>357</v>
       </c>
       <c r="L65">
         <f t="shared" ca="1" si="1"/>
-        <v>191</v>
+        <v>306</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
@@ -3266,15 +3291,15 @@
       </c>
       <c r="J66">
         <f t="shared" ca="1" si="1"/>
-        <v>306</v>
+        <v>166</v>
       </c>
       <c r="K66">
         <f t="shared" ca="1" si="1"/>
-        <v>394</v>
+        <v>213</v>
       </c>
       <c r="L66">
         <f t="shared" ca="1" si="1"/>
-        <v>361</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -3307,15 +3332,15 @@
       </c>
       <c r="J67">
         <f t="shared" ref="J67:L130" ca="1" si="2">RANDBETWEEN(100,400)</f>
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="K67">
         <f t="shared" ca="1" si="2"/>
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="L67">
         <f t="shared" ca="1" si="2"/>
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -3348,15 +3373,15 @@
       </c>
       <c r="J68">
         <f t="shared" ca="1" si="2"/>
-        <v>374</v>
+        <v>224</v>
       </c>
       <c r="K68">
         <f t="shared" ca="1" si="2"/>
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="L68">
         <f t="shared" ca="1" si="2"/>
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -3389,15 +3414,15 @@
       </c>
       <c r="J69">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>218</v>
       </c>
       <c r="K69">
         <f t="shared" ca="1" si="2"/>
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="L69">
         <f t="shared" ca="1" si="2"/>
-        <v>359</v>
+        <v>276</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -3430,15 +3455,15 @@
       </c>
       <c r="J70">
         <f t="shared" ca="1" si="2"/>
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="K70">
         <f t="shared" ca="1" si="2"/>
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="L70">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -3471,15 +3496,15 @@
       </c>
       <c r="J71">
         <f t="shared" ca="1" si="2"/>
-        <v>230</v>
+        <v>108</v>
       </c>
       <c r="K71">
         <f t="shared" ca="1" si="2"/>
-        <v>392</v>
+        <v>142</v>
       </c>
       <c r="L71">
         <f t="shared" ca="1" si="2"/>
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -3512,15 +3537,15 @@
       </c>
       <c r="J72">
         <f t="shared" ca="1" si="2"/>
-        <v>210</v>
+        <v>329</v>
       </c>
       <c r="K72">
         <f t="shared" ca="1" si="2"/>
-        <v>396</v>
+        <v>358</v>
       </c>
       <c r="L72">
         <f t="shared" ca="1" si="2"/>
-        <v>329</v>
+        <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -3553,15 +3578,15 @@
       </c>
       <c r="J73">
         <f t="shared" ca="1" si="2"/>
-        <v>130</v>
+        <v>393</v>
       </c>
       <c r="K73">
         <f t="shared" ca="1" si="2"/>
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="L73">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>306</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -3594,15 +3619,15 @@
       </c>
       <c r="J74">
         <f t="shared" ca="1" si="2"/>
-        <v>339</v>
+        <v>293</v>
       </c>
       <c r="K74">
         <f t="shared" ca="1" si="2"/>
-        <v>179</v>
+        <v>341</v>
       </c>
       <c r="L74">
         <f t="shared" ca="1" si="2"/>
-        <v>101</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -3635,15 +3660,15 @@
       </c>
       <c r="J75">
         <f t="shared" ca="1" si="2"/>
-        <v>345</v>
+        <v>132</v>
       </c>
       <c r="K75">
         <f t="shared" ca="1" si="2"/>
-        <v>294</v>
+        <v>355</v>
       </c>
       <c r="L75">
         <f t="shared" ca="1" si="2"/>
-        <v>179</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -3676,15 +3701,15 @@
       </c>
       <c r="J76">
         <f t="shared" ca="1" si="2"/>
-        <v>236</v>
+        <v>128</v>
       </c>
       <c r="K76">
         <f t="shared" ca="1" si="2"/>
-        <v>363</v>
+        <v>148</v>
       </c>
       <c r="L76">
         <f t="shared" ca="1" si="2"/>
-        <v>123</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -3717,15 +3742,15 @@
       </c>
       <c r="J77">
         <f t="shared" ca="1" si="2"/>
-        <v>397</v>
+        <v>209</v>
       </c>
       <c r="K77">
         <f t="shared" ca="1" si="2"/>
-        <v>371</v>
+        <v>276</v>
       </c>
       <c r="L77">
         <f t="shared" ca="1" si="2"/>
-        <v>119</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
@@ -3758,15 +3783,15 @@
       </c>
       <c r="J78">
         <f t="shared" ca="1" si="2"/>
-        <v>141</v>
+        <v>277</v>
       </c>
       <c r="K78">
         <f t="shared" ca="1" si="2"/>
-        <v>299</v>
+        <v>134</v>
       </c>
       <c r="L78">
         <f t="shared" ca="1" si="2"/>
-        <v>118</v>
+        <v>394</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
@@ -3799,15 +3824,15 @@
       </c>
       <c r="J79">
         <f t="shared" ca="1" si="2"/>
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="K79">
         <f t="shared" ca="1" si="2"/>
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="L79">
         <f t="shared" ca="1" si="2"/>
-        <v>186</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
@@ -3840,15 +3865,15 @@
       </c>
       <c r="J80">
         <f t="shared" ca="1" si="2"/>
-        <v>136</v>
+        <v>324</v>
       </c>
       <c r="K80">
         <f t="shared" ca="1" si="2"/>
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="L80">
         <f t="shared" ca="1" si="2"/>
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
@@ -3881,15 +3906,15 @@
       </c>
       <c r="J81">
         <f t="shared" ca="1" si="2"/>
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K81">
         <f t="shared" ca="1" si="2"/>
-        <v>293</v>
+        <v>216</v>
       </c>
       <c r="L81">
         <f t="shared" ca="1" si="2"/>
-        <v>234</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -3922,15 +3947,15 @@
       </c>
       <c r="J82">
         <f t="shared" ca="1" si="2"/>
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="K82">
         <f t="shared" ca="1" si="2"/>
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="L82">
         <f t="shared" ca="1" si="2"/>
-        <v>307</v>
+        <v>367</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
@@ -3963,15 +3988,15 @@
       </c>
       <c r="J83">
         <f t="shared" ca="1" si="2"/>
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="K83">
         <f t="shared" ca="1" si="2"/>
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L83">
         <f t="shared" ca="1" si="2"/>
-        <v>303</v>
+        <v>162</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
@@ -4004,15 +4029,15 @@
       </c>
       <c r="J84">
         <f t="shared" ca="1" si="2"/>
-        <v>288</v>
+        <v>132</v>
       </c>
       <c r="K84">
         <f t="shared" ca="1" si="2"/>
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="L84">
         <f t="shared" ca="1" si="2"/>
-        <v>144</v>
+        <v>320</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
@@ -4045,15 +4070,15 @@
       </c>
       <c r="J85">
         <f t="shared" ca="1" si="2"/>
-        <v>125</v>
+        <v>356</v>
       </c>
       <c r="K85">
         <f t="shared" ca="1" si="2"/>
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="L85">
         <f t="shared" ca="1" si="2"/>
-        <v>158</v>
+        <v>366</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
@@ -4086,15 +4111,15 @@
       </c>
       <c r="J86">
         <f t="shared" ca="1" si="2"/>
-        <v>326</v>
+        <v>234</v>
       </c>
       <c r="K86">
         <f t="shared" ca="1" si="2"/>
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="L86">
         <f t="shared" ca="1" si="2"/>
-        <v>137</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
@@ -4127,15 +4152,15 @@
       </c>
       <c r="J87">
         <f t="shared" ca="1" si="2"/>
-        <v>289</v>
+        <v>164</v>
       </c>
       <c r="K87">
         <f t="shared" ca="1" si="2"/>
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="L87">
         <f t="shared" ca="1" si="2"/>
-        <v>113</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
@@ -4168,15 +4193,15 @@
       </c>
       <c r="J88">
         <f t="shared" ca="1" si="2"/>
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="K88">
         <f t="shared" ca="1" si="2"/>
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="L88">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>310</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
@@ -4209,15 +4234,15 @@
       </c>
       <c r="J89">
         <f t="shared" ca="1" si="2"/>
-        <v>387</v>
+        <v>275</v>
       </c>
       <c r="K89">
         <f t="shared" ca="1" si="2"/>
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="L89">
         <f t="shared" ca="1" si="2"/>
-        <v>246</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
@@ -4250,15 +4275,15 @@
       </c>
       <c r="J90">
         <f t="shared" ca="1" si="2"/>
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="K90">
         <f t="shared" ca="1" si="2"/>
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="L90">
         <f t="shared" ca="1" si="2"/>
-        <v>378</v>
+        <v>329</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
@@ -4291,15 +4316,15 @@
       </c>
       <c r="J91">
         <f t="shared" ca="1" si="2"/>
-        <v>296</v>
+        <v>379</v>
       </c>
       <c r="K91">
         <f t="shared" ca="1" si="2"/>
-        <v>110</v>
+        <v>393</v>
       </c>
       <c r="L91">
         <f t="shared" ca="1" si="2"/>
-        <v>368</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
@@ -4332,15 +4357,15 @@
       </c>
       <c r="J92">
         <f t="shared" ca="1" si="2"/>
-        <v>225</v>
+        <v>327</v>
       </c>
       <c r="K92">
         <f t="shared" ca="1" si="2"/>
-        <v>313</v>
+        <v>168</v>
       </c>
       <c r="L92">
         <f t="shared" ca="1" si="2"/>
-        <v>277</v>
+        <v>162</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -4373,15 +4398,15 @@
       </c>
       <c r="J93">
         <f t="shared" ca="1" si="2"/>
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="K93">
         <f t="shared" ca="1" si="2"/>
-        <v>100</v>
+        <v>295</v>
       </c>
       <c r="L93">
         <f t="shared" ca="1" si="2"/>
-        <v>375</v>
+        <v>361</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
@@ -4414,15 +4439,15 @@
       </c>
       <c r="J94">
         <f t="shared" ca="1" si="2"/>
-        <v>125</v>
+        <v>216</v>
       </c>
       <c r="K94">
         <f t="shared" ca="1" si="2"/>
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="L94">
         <f t="shared" ca="1" si="2"/>
-        <v>374</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
@@ -4455,15 +4480,15 @@
       </c>
       <c r="J95">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="K95">
         <f t="shared" ca="1" si="2"/>
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="L95">
         <f t="shared" ca="1" si="2"/>
-        <v>150</v>
+        <v>166</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
@@ -4496,15 +4521,15 @@
       </c>
       <c r="J96">
         <f t="shared" ca="1" si="2"/>
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="K96">
         <f t="shared" ca="1" si="2"/>
-        <v>183</v>
+        <v>373</v>
       </c>
       <c r="L96">
         <f t="shared" ca="1" si="2"/>
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
@@ -4537,15 +4562,15 @@
       </c>
       <c r="J97">
         <f t="shared" ca="1" si="2"/>
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="K97">
         <f t="shared" ca="1" si="2"/>
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="L97">
         <f t="shared" ca="1" si="2"/>
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -4578,15 +4603,15 @@
       </c>
       <c r="J98">
         <f t="shared" ca="1" si="2"/>
-        <v>204</v>
+        <v>119</v>
       </c>
       <c r="K98">
         <f t="shared" ca="1" si="2"/>
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="L98">
         <f t="shared" ca="1" si="2"/>
-        <v>358</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -4619,15 +4644,15 @@
       </c>
       <c r="J99">
         <f t="shared" ca="1" si="2"/>
-        <v>229</v>
+        <v>332</v>
       </c>
       <c r="K99">
         <f t="shared" ca="1" si="2"/>
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="L99">
         <f t="shared" ca="1" si="2"/>
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -4660,15 +4685,15 @@
       </c>
       <c r="J100">
         <f t="shared" ca="1" si="2"/>
-        <v>121</v>
+        <v>326</v>
       </c>
       <c r="K100">
         <f t="shared" ca="1" si="2"/>
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="L100">
         <f t="shared" ca="1" si="2"/>
-        <v>211</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -4701,15 +4726,15 @@
       </c>
       <c r="J101">
         <f t="shared" ca="1" si="2"/>
-        <v>336</v>
+        <v>162</v>
       </c>
       <c r="K101">
         <f t="shared" ca="1" si="2"/>
-        <v>389</v>
+        <v>120</v>
       </c>
       <c r="L101">
         <f t="shared" ca="1" si="2"/>
-        <v>289</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -4742,15 +4767,15 @@
       </c>
       <c r="J102">
         <f t="shared" ca="1" si="2"/>
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="K102">
         <f t="shared" ca="1" si="2"/>
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="L102">
         <f t="shared" ca="1" si="2"/>
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
@@ -4783,15 +4808,15 @@
       </c>
       <c r="J103">
         <f t="shared" ca="1" si="2"/>
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="K103">
         <f t="shared" ca="1" si="2"/>
-        <v>253</v>
+        <v>326</v>
       </c>
       <c r="L103">
         <f t="shared" ca="1" si="2"/>
-        <v>388</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
@@ -4824,15 +4849,15 @@
       </c>
       <c r="J104">
         <f t="shared" ca="1" si="2"/>
-        <v>240</v>
+        <v>365</v>
       </c>
       <c r="K104">
         <f t="shared" ca="1" si="2"/>
-        <v>270</v>
+        <v>161</v>
       </c>
       <c r="L104">
         <f t="shared" ca="1" si="2"/>
-        <v>369</v>
+        <v>383</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
@@ -4865,15 +4890,15 @@
       </c>
       <c r="J105">
         <f t="shared" ca="1" si="2"/>
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="K105">
         <f t="shared" ca="1" si="2"/>
-        <v>166</v>
+        <v>275</v>
       </c>
       <c r="L105">
         <f t="shared" ca="1" si="2"/>
-        <v>142</v>
+        <v>391</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
@@ -4906,15 +4931,15 @@
       </c>
       <c r="J106">
         <f t="shared" ca="1" si="2"/>
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="K106">
         <f t="shared" ca="1" si="2"/>
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="L106">
         <f t="shared" ca="1" si="2"/>
-        <v>121</v>
+        <v>220</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
@@ -4947,15 +4972,15 @@
       </c>
       <c r="J107">
         <f t="shared" ca="1" si="2"/>
-        <v>103</v>
+        <v>296</v>
       </c>
       <c r="K107">
         <f t="shared" ca="1" si="2"/>
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="L107">
         <f t="shared" ca="1" si="2"/>
-        <v>192</v>
+        <v>382</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
@@ -4988,15 +5013,15 @@
       </c>
       <c r="J108">
         <f t="shared" ca="1" si="2"/>
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="K108">
         <f t="shared" ca="1" si="2"/>
-        <v>310</v>
+        <v>217</v>
       </c>
       <c r="L108">
         <f t="shared" ca="1" si="2"/>
-        <v>307</v>
+        <v>254</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -5029,15 +5054,15 @@
       </c>
       <c r="J109">
         <f t="shared" ca="1" si="2"/>
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="K109">
         <f t="shared" ca="1" si="2"/>
-        <v>326</v>
+        <v>204</v>
       </c>
       <c r="L109">
         <f t="shared" ca="1" si="2"/>
-        <v>196</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -5070,15 +5095,15 @@
       </c>
       <c r="J110">
         <f t="shared" ca="1" si="2"/>
-        <v>152</v>
+        <v>364</v>
       </c>
       <c r="K110">
         <f t="shared" ca="1" si="2"/>
-        <v>334</v>
+        <v>145</v>
       </c>
       <c r="L110">
         <f t="shared" ca="1" si="2"/>
-        <v>391</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -5111,15 +5136,15 @@
       </c>
       <c r="J111">
         <f t="shared" ca="1" si="2"/>
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="K111">
         <f t="shared" ca="1" si="2"/>
-        <v>178</v>
+        <v>229</v>
       </c>
       <c r="L111">
         <f t="shared" ca="1" si="2"/>
-        <v>364</v>
+        <v>218</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -5152,15 +5177,15 @@
       </c>
       <c r="J112">
         <f t="shared" ca="1" si="2"/>
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="K112">
         <f t="shared" ca="1" si="2"/>
-        <v>396</v>
+        <v>215</v>
       </c>
       <c r="L112">
         <f t="shared" ca="1" si="2"/>
-        <v>351</v>
+        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
@@ -5193,15 +5218,15 @@
       </c>
       <c r="J113">
         <f t="shared" ca="1" si="2"/>
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="K113">
         <f t="shared" ca="1" si="2"/>
-        <v>358</v>
+        <v>125</v>
       </c>
       <c r="L113">
         <f t="shared" ca="1" si="2"/>
-        <v>214</v>
+        <v>113</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
@@ -5234,15 +5259,15 @@
       </c>
       <c r="J114">
         <f t="shared" ca="1" si="2"/>
-        <v>246</v>
+        <v>197</v>
       </c>
       <c r="K114">
         <f t="shared" ca="1" si="2"/>
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="L114">
         <f t="shared" ca="1" si="2"/>
-        <v>380</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
@@ -5275,15 +5300,15 @@
       </c>
       <c r="J115">
         <f t="shared" ca="1" si="2"/>
-        <v>132</v>
+        <v>336</v>
       </c>
       <c r="K115">
         <f t="shared" ca="1" si="2"/>
-        <v>195</v>
+        <v>337</v>
       </c>
       <c r="L115">
         <f t="shared" ca="1" si="2"/>
-        <v>237</v>
+        <v>344</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
@@ -5316,15 +5341,15 @@
       </c>
       <c r="J116">
         <f t="shared" ca="1" si="2"/>
-        <v>225</v>
+        <v>360</v>
       </c>
       <c r="K116">
         <f t="shared" ca="1" si="2"/>
-        <v>102</v>
+        <v>258</v>
       </c>
       <c r="L116">
         <f t="shared" ca="1" si="2"/>
-        <v>170</v>
+        <v>357</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
@@ -5357,15 +5382,15 @@
       </c>
       <c r="J117">
         <f t="shared" ca="1" si="2"/>
-        <v>235</v>
+        <v>340</v>
       </c>
       <c r="K117">
         <f t="shared" ca="1" si="2"/>
-        <v>192</v>
+        <v>108</v>
       </c>
       <c r="L117">
         <f t="shared" ca="1" si="2"/>
-        <v>334</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
@@ -5398,15 +5423,15 @@
       </c>
       <c r="J118">
         <f t="shared" ca="1" si="2"/>
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="K118">
         <f t="shared" ca="1" si="2"/>
-        <v>294</v>
+        <v>124</v>
       </c>
       <c r="L118">
         <f t="shared" ca="1" si="2"/>
-        <v>386</v>
+        <v>171</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
@@ -5439,15 +5464,15 @@
       </c>
       <c r="J119">
         <f t="shared" ca="1" si="2"/>
-        <v>310</v>
+        <v>389</v>
       </c>
       <c r="K119">
         <f t="shared" ca="1" si="2"/>
-        <v>236</v>
+        <v>310</v>
       </c>
       <c r="L119">
         <f t="shared" ca="1" si="2"/>
-        <v>227</v>
+        <v>145</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
@@ -5480,15 +5505,15 @@
       </c>
       <c r="J120">
         <f t="shared" ca="1" si="2"/>
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="K120">
         <f t="shared" ca="1" si="2"/>
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="L120">
         <f t="shared" ca="1" si="2"/>
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
@@ -5521,15 +5546,15 @@
       </c>
       <c r="J121">
         <f t="shared" ca="1" si="2"/>
-        <v>107</v>
+        <v>246</v>
       </c>
       <c r="K121">
         <f t="shared" ca="1" si="2"/>
-        <v>337</v>
+        <v>193</v>
       </c>
       <c r="L121">
         <f t="shared" ca="1" si="2"/>
-        <v>221</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
@@ -5562,15 +5587,15 @@
       </c>
       <c r="J122">
         <f t="shared" ca="1" si="2"/>
-        <v>392</v>
+        <v>345</v>
       </c>
       <c r="K122">
         <f t="shared" ca="1" si="2"/>
-        <v>371</v>
+        <v>161</v>
       </c>
       <c r="L122">
         <f t="shared" ca="1" si="2"/>
-        <v>192</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
@@ -5603,15 +5628,15 @@
       </c>
       <c r="J123">
         <f t="shared" ca="1" si="2"/>
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="K123">
         <f t="shared" ca="1" si="2"/>
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="L123">
         <f t="shared" ca="1" si="2"/>
-        <v>135</v>
+        <v>183</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
@@ -5644,15 +5669,15 @@
       </c>
       <c r="J124">
         <f t="shared" ca="1" si="2"/>
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="K124">
         <f t="shared" ca="1" si="2"/>
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="L124">
         <f t="shared" ca="1" si="2"/>
-        <v>135</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -5685,15 +5710,15 @@
       </c>
       <c r="J125">
         <f t="shared" ca="1" si="2"/>
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="K125">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="L125">
         <f t="shared" ca="1" si="2"/>
-        <v>238</v>
+        <v>151</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
@@ -5726,15 +5751,15 @@
       </c>
       <c r="J126">
         <f t="shared" ca="1" si="2"/>
-        <v>399</v>
+        <v>287</v>
       </c>
       <c r="K126">
         <f t="shared" ca="1" si="2"/>
-        <v>149</v>
+        <v>268</v>
       </c>
       <c r="L126">
         <f t="shared" ca="1" si="2"/>
-        <v>137</v>
+        <v>295</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
@@ -5767,15 +5792,15 @@
       </c>
       <c r="J127">
         <f t="shared" ca="1" si="2"/>
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="K127">
         <f t="shared" ca="1" si="2"/>
-        <v>271</v>
+        <v>380</v>
       </c>
       <c r="L127">
         <f t="shared" ca="1" si="2"/>
-        <v>309</v>
+        <v>343</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
@@ -5808,15 +5833,15 @@
       </c>
       <c r="J128">
         <f t="shared" ca="1" si="2"/>
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="K128">
         <f t="shared" ca="1" si="2"/>
-        <v>265</v>
+        <v>371</v>
       </c>
       <c r="L128">
         <f t="shared" ca="1" si="2"/>
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
@@ -5849,15 +5874,15 @@
       </c>
       <c r="J129">
         <f t="shared" ca="1" si="2"/>
-        <v>105</v>
+        <v>337</v>
       </c>
       <c r="K129">
         <f t="shared" ca="1" si="2"/>
-        <v>381</v>
+        <v>314</v>
       </c>
       <c r="L129">
         <f t="shared" ca="1" si="2"/>
-        <v>352</v>
+        <v>232</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
@@ -5890,15 +5915,15 @@
       </c>
       <c r="J130">
         <f t="shared" ca="1" si="2"/>
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="K130">
         <f t="shared" ca="1" si="2"/>
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="L130">
         <f t="shared" ca="1" si="2"/>
-        <v>377</v>
+        <v>188</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
@@ -5931,15 +5956,15 @@
       </c>
       <c r="J131">
         <f t="shared" ref="J131:L194" ca="1" si="3">RANDBETWEEN(100,400)</f>
-        <v>347</v>
+        <v>146</v>
       </c>
       <c r="K131">
         <f t="shared" ca="1" si="3"/>
-        <v>155</v>
+        <v>329</v>
       </c>
       <c r="L131">
         <f t="shared" ca="1" si="3"/>
-        <v>210</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
@@ -5972,15 +5997,15 @@
       </c>
       <c r="J132">
         <f t="shared" ca="1" si="3"/>
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="K132">
         <f t="shared" ca="1" si="3"/>
-        <v>167</v>
+        <v>302</v>
       </c>
       <c r="L132">
         <f t="shared" ca="1" si="3"/>
-        <v>386</v>
+        <v>240</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
@@ -6013,7 +6038,7 @@
       </c>
       <c r="J133">
         <f t="shared" ca="1" si="3"/>
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K133">
         <f t="shared" ca="1" si="3"/>
@@ -6021,7 +6046,7 @@
       </c>
       <c r="L133">
         <f t="shared" ca="1" si="3"/>
-        <v>251</v>
+        <v>197</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
@@ -6054,15 +6079,15 @@
       </c>
       <c r="J134">
         <f t="shared" ca="1" si="3"/>
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="K134">
         <f t="shared" ca="1" si="3"/>
-        <v>202</v>
+        <v>396</v>
       </c>
       <c r="L134">
         <f t="shared" ca="1" si="3"/>
-        <v>144</v>
+        <v>282</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
@@ -6095,15 +6120,15 @@
       </c>
       <c r="J135">
         <f t="shared" ca="1" si="3"/>
-        <v>331</v>
+        <v>152</v>
       </c>
       <c r="K135">
         <f t="shared" ca="1" si="3"/>
-        <v>380</v>
+        <v>127</v>
       </c>
       <c r="L135">
         <f t="shared" ca="1" si="3"/>
-        <v>330</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
@@ -6136,15 +6161,15 @@
       </c>
       <c r="J136">
         <f t="shared" ca="1" si="3"/>
-        <v>394</v>
+        <v>250</v>
       </c>
       <c r="K136">
         <f t="shared" ca="1" si="3"/>
-        <v>246</v>
+        <v>328</v>
       </c>
       <c r="L136">
         <f t="shared" ca="1" si="3"/>
-        <v>178</v>
+        <v>279</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
@@ -6177,15 +6202,15 @@
       </c>
       <c r="J137">
         <f t="shared" ca="1" si="3"/>
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="K137">
         <f t="shared" ca="1" si="3"/>
-        <v>288</v>
+        <v>123</v>
       </c>
       <c r="L137">
         <f t="shared" ca="1" si="3"/>
-        <v>314</v>
+        <v>334</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
@@ -6218,15 +6243,15 @@
       </c>
       <c r="J138">
         <f t="shared" ca="1" si="3"/>
-        <v>158</v>
+        <v>381</v>
       </c>
       <c r="K138">
         <f t="shared" ca="1" si="3"/>
-        <v>236</v>
+        <v>279</v>
       </c>
       <c r="L138">
         <f t="shared" ca="1" si="3"/>
-        <v>128</v>
+        <v>215</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
@@ -6259,15 +6284,15 @@
       </c>
       <c r="J139">
         <f t="shared" ca="1" si="3"/>
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="K139">
         <f t="shared" ca="1" si="3"/>
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="L139">
         <f t="shared" ca="1" si="3"/>
-        <v>211</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
@@ -6300,15 +6325,15 @@
       </c>
       <c r="J140">
         <f t="shared" ca="1" si="3"/>
-        <v>167</v>
+        <v>339</v>
       </c>
       <c r="K140">
         <f t="shared" ca="1" si="3"/>
-        <v>125</v>
+        <v>285</v>
       </c>
       <c r="L140">
         <f t="shared" ca="1" si="3"/>
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
@@ -6341,15 +6366,15 @@
       </c>
       <c r="J141">
         <f t="shared" ca="1" si="3"/>
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="K141">
         <f t="shared" ca="1" si="3"/>
-        <v>307</v>
+        <v>148</v>
       </c>
       <c r="L141">
         <f t="shared" ca="1" si="3"/>
-        <v>240</v>
+        <v>287</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
@@ -6382,15 +6407,15 @@
       </c>
       <c r="J142">
         <f t="shared" ca="1" si="3"/>
-        <v>124</v>
+        <v>343</v>
       </c>
       <c r="K142">
         <f t="shared" ca="1" si="3"/>
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="L142">
         <f t="shared" ca="1" si="3"/>
-        <v>165</v>
+        <v>231</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -6423,15 +6448,15 @@
       </c>
       <c r="J143">
         <f t="shared" ca="1" si="3"/>
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="K143">
         <f t="shared" ca="1" si="3"/>
-        <v>239</v>
+        <v>156</v>
       </c>
       <c r="L143">
         <f t="shared" ca="1" si="3"/>
-        <v>323</v>
+        <v>256</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
@@ -6464,15 +6489,15 @@
       </c>
       <c r="J144">
         <f t="shared" ca="1" si="3"/>
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="K144">
         <f t="shared" ca="1" si="3"/>
-        <v>357</v>
+        <v>257</v>
       </c>
       <c r="L144">
         <f t="shared" ca="1" si="3"/>
-        <v>374</v>
+        <v>286</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
@@ -6505,15 +6530,15 @@
       </c>
       <c r="J145">
         <f t="shared" ca="1" si="3"/>
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="K145">
         <f t="shared" ca="1" si="3"/>
-        <v>162</v>
+        <v>302</v>
       </c>
       <c r="L145">
         <f t="shared" ca="1" si="3"/>
-        <v>306</v>
+        <v>391</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
@@ -6546,15 +6571,15 @@
       </c>
       <c r="J146">
         <f t="shared" ca="1" si="3"/>
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K146">
         <f t="shared" ca="1" si="3"/>
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="L146">
         <f t="shared" ca="1" si="3"/>
-        <v>185</v>
+        <v>345</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
@@ -6587,15 +6612,15 @@
       </c>
       <c r="J147">
         <f t="shared" ca="1" si="3"/>
-        <v>314</v>
+        <v>170</v>
       </c>
       <c r="K147">
         <f t="shared" ca="1" si="3"/>
-        <v>395</v>
+        <v>323</v>
       </c>
       <c r="L147">
         <f t="shared" ca="1" si="3"/>
-        <v>229</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
@@ -6628,15 +6653,15 @@
       </c>
       <c r="J148">
         <f t="shared" ca="1" si="3"/>
-        <v>261</v>
+        <v>323</v>
       </c>
       <c r="K148">
         <f t="shared" ca="1" si="3"/>
-        <v>279</v>
+        <v>368</v>
       </c>
       <c r="L148">
         <f t="shared" ca="1" si="3"/>
-        <v>357</v>
+        <v>133</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
@@ -6669,15 +6694,15 @@
       </c>
       <c r="J149">
         <f t="shared" ca="1" si="3"/>
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="K149">
         <f t="shared" ca="1" si="3"/>
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="L149">
         <f t="shared" ca="1" si="3"/>
-        <v>123</v>
+        <v>326</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
@@ -6710,15 +6735,15 @@
       </c>
       <c r="J150">
         <f t="shared" ca="1" si="3"/>
-        <v>381</v>
+        <v>128</v>
       </c>
       <c r="K150">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="L150">
         <f t="shared" ca="1" si="3"/>
-        <v>112</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
@@ -6751,15 +6776,15 @@
       </c>
       <c r="J151">
         <f t="shared" ca="1" si="3"/>
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="K151">
         <f t="shared" ca="1" si="3"/>
-        <v>357</v>
+        <v>299</v>
       </c>
       <c r="L151">
         <f t="shared" ca="1" si="3"/>
-        <v>388</v>
+        <v>139</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -6792,15 +6817,15 @@
       </c>
       <c r="J152">
         <f t="shared" ca="1" si="3"/>
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="K152">
         <f t="shared" ca="1" si="3"/>
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="L152">
         <f t="shared" ca="1" si="3"/>
-        <v>337</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
@@ -6833,15 +6858,15 @@
       </c>
       <c r="J153">
         <f t="shared" ca="1" si="3"/>
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="K153">
         <f t="shared" ca="1" si="3"/>
-        <v>262</v>
+        <v>100</v>
       </c>
       <c r="L153">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
@@ -6874,15 +6899,15 @@
       </c>
       <c r="J154">
         <f t="shared" ca="1" si="3"/>
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="K154">
         <f t="shared" ca="1" si="3"/>
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="L154">
         <f t="shared" ca="1" si="3"/>
-        <v>375</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
@@ -6915,15 +6940,15 @@
       </c>
       <c r="J155">
         <f t="shared" ca="1" si="3"/>
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="K155">
         <f t="shared" ca="1" si="3"/>
-        <v>279</v>
+        <v>396</v>
       </c>
       <c r="L155">
         <f t="shared" ca="1" si="3"/>
-        <v>361</v>
+        <v>261</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
@@ -6956,15 +6981,15 @@
       </c>
       <c r="J156">
         <f t="shared" ca="1" si="3"/>
-        <v>322</v>
+        <v>396</v>
       </c>
       <c r="K156">
         <f t="shared" ca="1" si="3"/>
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="L156">
         <f t="shared" ca="1" si="3"/>
-        <v>347</v>
+        <v>308</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
@@ -6997,15 +7022,15 @@
       </c>
       <c r="J157">
         <f t="shared" ca="1" si="3"/>
-        <v>330</v>
+        <v>225</v>
       </c>
       <c r="K157">
         <f t="shared" ca="1" si="3"/>
-        <v>277</v>
+        <v>375</v>
       </c>
       <c r="L157">
         <f t="shared" ca="1" si="3"/>
-        <v>226</v>
+        <v>258</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
@@ -7038,15 +7063,15 @@
       </c>
       <c r="J158">
         <f t="shared" ca="1" si="3"/>
-        <v>328</v>
+        <v>236</v>
       </c>
       <c r="K158">
         <f t="shared" ca="1" si="3"/>
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="L158">
         <f t="shared" ca="1" si="3"/>
-        <v>378</v>
+        <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
@@ -7079,15 +7104,15 @@
       </c>
       <c r="J159">
         <f t="shared" ca="1" si="3"/>
-        <v>195</v>
+        <v>276</v>
       </c>
       <c r="K159">
         <f t="shared" ca="1" si="3"/>
-        <v>111</v>
+        <v>230</v>
       </c>
       <c r="L159">
         <f t="shared" ca="1" si="3"/>
-        <v>364</v>
+        <v>274</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
@@ -7120,15 +7145,15 @@
       </c>
       <c r="J160">
         <f t="shared" ca="1" si="3"/>
-        <v>314</v>
+        <v>173</v>
       </c>
       <c r="K160">
         <f t="shared" ca="1" si="3"/>
-        <v>327</v>
+        <v>243</v>
       </c>
       <c r="L160">
         <f t="shared" ca="1" si="3"/>
-        <v>382</v>
+        <v>235</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
@@ -7161,15 +7186,15 @@
       </c>
       <c r="J161">
         <f t="shared" ca="1" si="3"/>
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="K161">
         <f t="shared" ca="1" si="3"/>
-        <v>397</v>
+        <v>282</v>
       </c>
       <c r="L161">
         <f t="shared" ca="1" si="3"/>
-        <v>191</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
@@ -7202,15 +7227,15 @@
       </c>
       <c r="J162">
         <f t="shared" ca="1" si="3"/>
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="K162">
         <f t="shared" ca="1" si="3"/>
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="L162">
         <f t="shared" ca="1" si="3"/>
-        <v>248</v>
+        <v>384</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
@@ -7243,15 +7268,15 @@
       </c>
       <c r="J163">
         <f t="shared" ca="1" si="3"/>
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K163">
         <f t="shared" ca="1" si="3"/>
-        <v>334</v>
+        <v>190</v>
       </c>
       <c r="L163">
         <f t="shared" ca="1" si="3"/>
-        <v>146</v>
+        <v>130</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
@@ -7284,15 +7309,15 @@
       </c>
       <c r="J164">
         <f t="shared" ca="1" si="3"/>
-        <v>168</v>
+        <v>262</v>
       </c>
       <c r="K164">
         <f t="shared" ca="1" si="3"/>
-        <v>252</v>
+        <v>144</v>
       </c>
       <c r="L164">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>211</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
@@ -7325,15 +7350,15 @@
       </c>
       <c r="J165">
         <f t="shared" ca="1" si="3"/>
-        <v>308</v>
+        <v>167</v>
       </c>
       <c r="K165">
         <f t="shared" ca="1" si="3"/>
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="L165">
         <f t="shared" ca="1" si="3"/>
-        <v>165</v>
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
@@ -7366,15 +7391,15 @@
       </c>
       <c r="J166">
         <f t="shared" ca="1" si="3"/>
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="K166">
         <f t="shared" ca="1" si="3"/>
-        <v>373</v>
+        <v>145</v>
       </c>
       <c r="L166">
         <f t="shared" ca="1" si="3"/>
-        <v>180</v>
+        <v>381</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
@@ -7407,15 +7432,15 @@
       </c>
       <c r="J167">
         <f t="shared" ca="1" si="3"/>
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="K167">
         <f t="shared" ca="1" si="3"/>
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="L167">
         <f t="shared" ca="1" si="3"/>
-        <v>160</v>
+        <v>232</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
@@ -7448,15 +7473,15 @@
       </c>
       <c r="J168">
         <f t="shared" ca="1" si="3"/>
-        <v>344</v>
+        <v>157</v>
       </c>
       <c r="K168">
         <f t="shared" ca="1" si="3"/>
-        <v>166</v>
+        <v>307</v>
       </c>
       <c r="L168">
         <f t="shared" ca="1" si="3"/>
-        <v>176</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
@@ -7489,15 +7514,15 @@
       </c>
       <c r="J169">
         <f t="shared" ca="1" si="3"/>
-        <v>389</v>
+        <v>232</v>
       </c>
       <c r="K169">
         <f t="shared" ca="1" si="3"/>
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="L169">
         <f t="shared" ca="1" si="3"/>
-        <v>118</v>
+        <v>233</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
@@ -7530,15 +7555,15 @@
       </c>
       <c r="J170">
         <f t="shared" ca="1" si="3"/>
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="K170">
         <f t="shared" ca="1" si="3"/>
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="L170">
         <f t="shared" ca="1" si="3"/>
-        <v>299</v>
+        <v>275</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -7571,15 +7596,15 @@
       </c>
       <c r="J171">
         <f t="shared" ca="1" si="3"/>
-        <v>293</v>
+        <v>236</v>
       </c>
       <c r="K171">
         <f t="shared" ca="1" si="3"/>
-        <v>335</v>
+        <v>296</v>
       </c>
       <c r="L171">
         <f t="shared" ca="1" si="3"/>
-        <v>325</v>
+        <v>249</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
@@ -7612,15 +7637,15 @@
       </c>
       <c r="J172">
         <f t="shared" ca="1" si="3"/>
-        <v>290</v>
+        <v>358</v>
       </c>
       <c r="K172">
         <f t="shared" ca="1" si="3"/>
-        <v>148</v>
+        <v>369</v>
       </c>
       <c r="L172">
         <f t="shared" ca="1" si="3"/>
-        <v>177</v>
+        <v>361</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
@@ -7653,15 +7678,15 @@
       </c>
       <c r="J173">
         <f t="shared" ca="1" si="3"/>
-        <v>165</v>
+        <v>297</v>
       </c>
       <c r="K173">
         <f t="shared" ca="1" si="3"/>
-        <v>143</v>
+        <v>302</v>
       </c>
       <c r="L173">
         <f t="shared" ca="1" si="3"/>
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
@@ -7694,15 +7719,15 @@
       </c>
       <c r="J174">
         <f t="shared" ca="1" si="3"/>
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="K174">
         <f t="shared" ca="1" si="3"/>
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="L174">
         <f t="shared" ca="1" si="3"/>
-        <v>158</v>
+        <v>325</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
@@ -7735,15 +7760,15 @@
       </c>
       <c r="J175">
         <f t="shared" ca="1" si="3"/>
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="K175">
         <f t="shared" ca="1" si="3"/>
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="L175">
         <f t="shared" ca="1" si="3"/>
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
@@ -7776,15 +7801,15 @@
       </c>
       <c r="J176">
         <f t="shared" ca="1" si="3"/>
-        <v>125</v>
+        <v>298</v>
       </c>
       <c r="K176">
         <f t="shared" ca="1" si="3"/>
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="L176">
         <f t="shared" ca="1" si="3"/>
-        <v>160</v>
+        <v>135</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
@@ -7817,15 +7842,15 @@
       </c>
       <c r="J177">
         <f t="shared" ca="1" si="3"/>
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="K177">
         <f t="shared" ca="1" si="3"/>
-        <v>182</v>
+        <v>297</v>
       </c>
       <c r="L177">
         <f t="shared" ca="1" si="3"/>
-        <v>352</v>
+        <v>334</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
@@ -7858,15 +7883,15 @@
       </c>
       <c r="J178">
         <f t="shared" ca="1" si="3"/>
-        <v>391</v>
+        <v>102</v>
       </c>
       <c r="K178">
         <f t="shared" ca="1" si="3"/>
-        <v>146</v>
+        <v>398</v>
       </c>
       <c r="L178">
         <f t="shared" ca="1" si="3"/>
-        <v>213</v>
+        <v>109</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
@@ -7899,15 +7924,15 @@
       </c>
       <c r="J179">
         <f t="shared" ca="1" si="3"/>
-        <v>279</v>
+        <v>382</v>
       </c>
       <c r="K179">
         <f t="shared" ca="1" si="3"/>
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="L179">
         <f t="shared" ca="1" si="3"/>
-        <v>288</v>
+        <v>333</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
@@ -7940,15 +7965,15 @@
       </c>
       <c r="J180">
         <f t="shared" ca="1" si="3"/>
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="K180">
         <f t="shared" ca="1" si="3"/>
-        <v>326</v>
+        <v>207</v>
       </c>
       <c r="L180">
         <f t="shared" ca="1" si="3"/>
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -7981,15 +8006,15 @@
       </c>
       <c r="J181">
         <f t="shared" ca="1" si="3"/>
-        <v>158</v>
+        <v>351</v>
       </c>
       <c r="K181">
         <f t="shared" ca="1" si="3"/>
-        <v>355</v>
+        <v>124</v>
       </c>
       <c r="L181">
         <f t="shared" ca="1" si="3"/>
-        <v>329</v>
+        <v>347</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -8022,15 +8047,15 @@
       </c>
       <c r="J182">
         <f t="shared" ca="1" si="3"/>
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="K182">
         <f t="shared" ca="1" si="3"/>
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="L182">
         <f t="shared" ca="1" si="3"/>
-        <v>317</v>
+        <v>303</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
@@ -8063,15 +8088,15 @@
       </c>
       <c r="J183">
         <f t="shared" ca="1" si="3"/>
-        <v>389</v>
+        <v>282</v>
       </c>
       <c r="K183">
         <f t="shared" ca="1" si="3"/>
-        <v>131</v>
+        <v>275</v>
       </c>
       <c r="L183">
         <f t="shared" ca="1" si="3"/>
-        <v>148</v>
+        <v>340</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
@@ -8104,15 +8129,15 @@
       </c>
       <c r="J184">
         <f t="shared" ca="1" si="3"/>
-        <v>243</v>
+        <v>304</v>
       </c>
       <c r="K184">
         <f t="shared" ca="1" si="3"/>
-        <v>240</v>
+        <v>309</v>
       </c>
       <c r="L184">
         <f t="shared" ca="1" si="3"/>
-        <v>226</v>
+        <v>240</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
@@ -8145,15 +8170,15 @@
       </c>
       <c r="J185">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
+        <v>380</v>
       </c>
       <c r="K185">
         <f t="shared" ca="1" si="3"/>
-        <v>333</v>
+        <v>272</v>
       </c>
       <c r="L185">
         <f t="shared" ca="1" si="3"/>
-        <v>305</v>
+        <v>243</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
@@ -8186,15 +8211,15 @@
       </c>
       <c r="J186">
         <f t="shared" ca="1" si="3"/>
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="K186">
         <f t="shared" ca="1" si="3"/>
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="L186">
         <f t="shared" ca="1" si="3"/>
-        <v>214</v>
+        <v>114</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
@@ -8227,15 +8252,15 @@
       </c>
       <c r="J187">
         <f t="shared" ca="1" si="3"/>
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="K187">
         <f t="shared" ca="1" si="3"/>
-        <v>371</v>
+        <v>150</v>
       </c>
       <c r="L187">
         <f t="shared" ca="1" si="3"/>
-        <v>374</v>
+        <v>335</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
@@ -8268,15 +8293,15 @@
       </c>
       <c r="J188">
         <f t="shared" ca="1" si="3"/>
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="K188">
         <f t="shared" ca="1" si="3"/>
-        <v>389</v>
+        <v>338</v>
       </c>
       <c r="L188">
         <f t="shared" ca="1" si="3"/>
-        <v>314</v>
+        <v>387</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
@@ -8309,15 +8334,15 @@
       </c>
       <c r="J189">
         <f t="shared" ca="1" si="3"/>
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="K189">
         <f t="shared" ca="1" si="3"/>
-        <v>369</v>
+        <v>259</v>
       </c>
       <c r="L189">
         <f t="shared" ca="1" si="3"/>
-        <v>137</v>
+        <v>349</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
@@ -8350,15 +8375,15 @@
       </c>
       <c r="J190">
         <f t="shared" ca="1" si="3"/>
-        <v>265</v>
+        <v>214</v>
       </c>
       <c r="K190">
         <f t="shared" ca="1" si="3"/>
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="L190">
         <f t="shared" ca="1" si="3"/>
-        <v>260</v>
+        <v>113</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
@@ -8391,15 +8416,15 @@
       </c>
       <c r="J191">
         <f t="shared" ca="1" si="3"/>
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="K191">
         <f t="shared" ca="1" si="3"/>
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="L191">
         <f t="shared" ca="1" si="3"/>
-        <v>151</v>
+        <v>100</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
@@ -8432,15 +8457,15 @@
       </c>
       <c r="J192">
         <f t="shared" ca="1" si="3"/>
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="K192">
         <f t="shared" ca="1" si="3"/>
-        <v>382</v>
+        <v>271</v>
       </c>
       <c r="L192">
         <f t="shared" ca="1" si="3"/>
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
@@ -8473,15 +8498,15 @@
       </c>
       <c r="J193">
         <f t="shared" ca="1" si="3"/>
-        <v>194</v>
+        <v>311</v>
       </c>
       <c r="K193">
         <f t="shared" ca="1" si="3"/>
-        <v>130</v>
+        <v>367</v>
       </c>
       <c r="L193">
         <f t="shared" ca="1" si="3"/>
-        <v>381</v>
+        <v>133</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
@@ -8514,15 +8539,15 @@
       </c>
       <c r="J194">
         <f t="shared" ca="1" si="3"/>
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="K194">
         <f t="shared" ca="1" si="3"/>
-        <v>225</v>
+        <v>342</v>
       </c>
       <c r="L194">
         <f t="shared" ca="1" si="3"/>
-        <v>332</v>
+        <v>347</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
@@ -8555,15 +8580,15 @@
       </c>
       <c r="J195">
         <f t="shared" ref="J195:L258" ca="1" si="4">RANDBETWEEN(100,400)</f>
-        <v>293</v>
+        <v>343</v>
       </c>
       <c r="K195">
         <f t="shared" ca="1" si="4"/>
-        <v>116</v>
+        <v>273</v>
       </c>
       <c r="L195">
         <f t="shared" ca="1" si="4"/>
-        <v>257</v>
+        <v>141</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
@@ -8596,15 +8621,15 @@
       </c>
       <c r="J196">
         <f t="shared" ca="1" si="4"/>
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="K196">
         <f t="shared" ca="1" si="4"/>
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="L196">
         <f t="shared" ca="1" si="4"/>
-        <v>267</v>
+        <v>168</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
@@ -8637,15 +8662,15 @@
       </c>
       <c r="J197">
         <f t="shared" ca="1" si="4"/>
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="K197">
         <f t="shared" ca="1" si="4"/>
-        <v>357</v>
+        <v>247</v>
       </c>
       <c r="L197">
         <f t="shared" ca="1" si="4"/>
-        <v>216</v>
+        <v>273</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
@@ -8678,15 +8703,15 @@
       </c>
       <c r="J198">
         <f t="shared" ca="1" si="4"/>
-        <v>297</v>
+        <v>148</v>
       </c>
       <c r="K198">
         <f t="shared" ca="1" si="4"/>
-        <v>246</v>
+        <v>358</v>
       </c>
       <c r="L198">
         <f t="shared" ca="1" si="4"/>
-        <v>191</v>
+        <v>347</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -8719,15 +8744,15 @@
       </c>
       <c r="J199">
         <f t="shared" ca="1" si="4"/>
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="K199">
         <f t="shared" ca="1" si="4"/>
-        <v>300</v>
+        <v>377</v>
       </c>
       <c r="L199">
         <f t="shared" ca="1" si="4"/>
-        <v>128</v>
+        <v>263</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
@@ -8760,15 +8785,15 @@
       </c>
       <c r="J200">
         <f t="shared" ca="1" si="4"/>
-        <v>372</v>
+        <v>294</v>
       </c>
       <c r="K200">
         <f t="shared" ca="1" si="4"/>
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="L200">
         <f t="shared" ca="1" si="4"/>
-        <v>393</v>
+        <v>137</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
@@ -8801,15 +8826,15 @@
       </c>
       <c r="J201">
         <f t="shared" ca="1" si="4"/>
-        <v>342</v>
+        <v>111</v>
       </c>
       <c r="K201">
         <f t="shared" ca="1" si="4"/>
-        <v>149</v>
+        <v>284</v>
       </c>
       <c r="L201">
         <f t="shared" ca="1" si="4"/>
-        <v>294</v>
+        <v>208</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
@@ -8842,15 +8867,15 @@
       </c>
       <c r="J202">
         <f t="shared" ca="1" si="4"/>
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="K202">
         <f t="shared" ca="1" si="4"/>
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="L202">
         <f t="shared" ca="1" si="4"/>
-        <v>311</v>
+        <v>345</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
@@ -8883,15 +8908,15 @@
       </c>
       <c r="J203">
         <f t="shared" ca="1" si="4"/>
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="K203">
         <f t="shared" ca="1" si="4"/>
-        <v>327</v>
+        <v>135</v>
       </c>
       <c r="L203">
         <f t="shared" ca="1" si="4"/>
-        <v>258</v>
+        <v>295</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
@@ -8924,15 +8949,15 @@
       </c>
       <c r="J204">
         <f t="shared" ca="1" si="4"/>
-        <v>110</v>
+        <v>349</v>
       </c>
       <c r="K204">
         <f t="shared" ca="1" si="4"/>
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L204">
         <f t="shared" ca="1" si="4"/>
-        <v>269</v>
+        <v>135</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
@@ -8965,15 +8990,15 @@
       </c>
       <c r="J205">
         <f t="shared" ca="1" si="4"/>
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="K205">
         <f t="shared" ca="1" si="4"/>
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="L205">
         <f t="shared" ca="1" si="4"/>
-        <v>375</v>
+        <v>339</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
@@ -9006,15 +9031,15 @@
       </c>
       <c r="J206">
         <f t="shared" ca="1" si="4"/>
-        <v>232</v>
+        <v>185</v>
       </c>
       <c r="K206">
         <f t="shared" ca="1" si="4"/>
-        <v>341</v>
+        <v>225</v>
       </c>
       <c r="L206">
         <f t="shared" ca="1" si="4"/>
-        <v>266</v>
+        <v>152</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
@@ -9047,15 +9072,15 @@
       </c>
       <c r="J207">
         <f t="shared" ca="1" si="4"/>
-        <v>323</v>
+        <v>198</v>
       </c>
       <c r="K207">
         <f t="shared" ca="1" si="4"/>
-        <v>123</v>
+        <v>330</v>
       </c>
       <c r="L207">
         <f t="shared" ca="1" si="4"/>
-        <v>180</v>
+        <v>289</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
@@ -9088,15 +9113,15 @@
       </c>
       <c r="J208">
         <f t="shared" ca="1" si="4"/>
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="K208">
         <f t="shared" ca="1" si="4"/>
-        <v>149</v>
+        <v>363</v>
       </c>
       <c r="L208">
         <f t="shared" ca="1" si="4"/>
-        <v>296</v>
+        <v>253</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
@@ -9129,15 +9154,15 @@
       </c>
       <c r="J209">
         <f t="shared" ca="1" si="4"/>
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="K209">
         <f t="shared" ca="1" si="4"/>
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="L209">
         <f t="shared" ca="1" si="4"/>
-        <v>313</v>
+        <v>163</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
@@ -9170,15 +9195,15 @@
       </c>
       <c r="J210">
         <f t="shared" ca="1" si="4"/>
-        <v>352</v>
+        <v>272</v>
       </c>
       <c r="K210">
         <f t="shared" ca="1" si="4"/>
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="L210">
         <f t="shared" ca="1" si="4"/>
-        <v>108</v>
+        <v>164</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
@@ -9211,15 +9236,15 @@
       </c>
       <c r="J211">
         <f t="shared" ca="1" si="4"/>
-        <v>124</v>
+        <v>365</v>
       </c>
       <c r="K211">
         <f t="shared" ca="1" si="4"/>
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="L211">
         <f t="shared" ca="1" si="4"/>
-        <v>396</v>
+        <v>139</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
@@ -9252,15 +9277,15 @@
       </c>
       <c r="J212">
         <f t="shared" ca="1" si="4"/>
-        <v>177</v>
+        <v>379</v>
       </c>
       <c r="K212">
         <f t="shared" ca="1" si="4"/>
-        <v>231</v>
+        <v>287</v>
       </c>
       <c r="L212">
         <f t="shared" ca="1" si="4"/>
-        <v>231</v>
+        <v>303</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
@@ -9293,15 +9318,15 @@
       </c>
       <c r="J213">
         <f t="shared" ca="1" si="4"/>
-        <v>128</v>
+        <v>382</v>
       </c>
       <c r="K213">
         <f t="shared" ca="1" si="4"/>
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="L213">
         <f t="shared" ca="1" si="4"/>
-        <v>307</v>
+        <v>137</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
@@ -9334,15 +9359,15 @@
       </c>
       <c r="J214">
         <f t="shared" ca="1" si="4"/>
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="K214">
         <f t="shared" ca="1" si="4"/>
-        <v>159</v>
+        <v>301</v>
       </c>
       <c r="L214">
         <f t="shared" ca="1" si="4"/>
-        <v>365</v>
+        <v>238</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
@@ -9375,15 +9400,15 @@
       </c>
       <c r="J215">
         <f t="shared" ca="1" si="4"/>
-        <v>353</v>
+        <v>163</v>
       </c>
       <c r="K215">
         <f t="shared" ca="1" si="4"/>
-        <v>384</v>
+        <v>221</v>
       </c>
       <c r="L215">
         <f t="shared" ca="1" si="4"/>
-        <v>357</v>
+        <v>172</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
@@ -9416,15 +9441,15 @@
       </c>
       <c r="J216">
         <f t="shared" ca="1" si="4"/>
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="K216">
         <f t="shared" ca="1" si="4"/>
-        <v>303</v>
+        <v>104</v>
       </c>
       <c r="L216">
         <f t="shared" ca="1" si="4"/>
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
@@ -9457,15 +9482,15 @@
       </c>
       <c r="J217">
         <f t="shared" ca="1" si="4"/>
-        <v>392</v>
+        <v>206</v>
       </c>
       <c r="K217">
         <f t="shared" ca="1" si="4"/>
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="L217">
         <f t="shared" ca="1" si="4"/>
-        <v>305</v>
+        <v>108</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
@@ -9498,15 +9523,15 @@
       </c>
       <c r="J218">
         <f t="shared" ca="1" si="4"/>
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="K218">
         <f t="shared" ca="1" si="4"/>
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L218">
         <f t="shared" ca="1" si="4"/>
-        <v>259</v>
+        <v>324</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
@@ -9539,15 +9564,15 @@
       </c>
       <c r="J219">
         <f t="shared" ca="1" si="4"/>
-        <v>357</v>
+        <v>224</v>
       </c>
       <c r="K219">
         <f t="shared" ca="1" si="4"/>
-        <v>267</v>
+        <v>101</v>
       </c>
       <c r="L219">
         <f t="shared" ca="1" si="4"/>
-        <v>202</v>
+        <v>247</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
@@ -9580,15 +9605,15 @@
       </c>
       <c r="J220">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="K220">
         <f t="shared" ca="1" si="4"/>
-        <v>245</v>
+        <v>320</v>
       </c>
       <c r="L220">
         <f t="shared" ca="1" si="4"/>
-        <v>318</v>
+        <v>393</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
@@ -9621,15 +9646,15 @@
       </c>
       <c r="J221">
         <f t="shared" ca="1" si="4"/>
-        <v>311</v>
+        <v>142</v>
       </c>
       <c r="K221">
         <f t="shared" ca="1" si="4"/>
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="L221">
         <f t="shared" ca="1" si="4"/>
-        <v>348</v>
+        <v>111</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
@@ -9662,15 +9687,15 @@
       </c>
       <c r="J222">
         <f t="shared" ca="1" si="4"/>
-        <v>385</v>
+        <v>180</v>
       </c>
       <c r="K222">
         <f t="shared" ca="1" si="4"/>
-        <v>136</v>
+        <v>308</v>
       </c>
       <c r="L222">
         <f t="shared" ca="1" si="4"/>
-        <v>229</v>
+        <v>149</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
@@ -9703,15 +9728,15 @@
       </c>
       <c r="J223">
         <f t="shared" ca="1" si="4"/>
-        <v>139</v>
+        <v>320</v>
       </c>
       <c r="K223">
         <f t="shared" ca="1" si="4"/>
-        <v>193</v>
+        <v>306</v>
       </c>
       <c r="L223">
         <f t="shared" ca="1" si="4"/>
-        <v>214</v>
+        <v>334</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
@@ -9744,15 +9769,15 @@
       </c>
       <c r="J224">
         <f t="shared" ca="1" si="4"/>
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K224">
         <f t="shared" ca="1" si="4"/>
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="L224">
         <f t="shared" ca="1" si="4"/>
-        <v>274</v>
+        <v>137</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
@@ -9785,15 +9810,15 @@
       </c>
       <c r="J225">
         <f t="shared" ca="1" si="4"/>
-        <v>353</v>
+        <v>196</v>
       </c>
       <c r="K225">
         <f t="shared" ca="1" si="4"/>
-        <v>246</v>
+        <v>364</v>
       </c>
       <c r="L225">
         <f t="shared" ca="1" si="4"/>
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
@@ -9826,15 +9851,15 @@
       </c>
       <c r="J226">
         <f t="shared" ca="1" si="4"/>
-        <v>347</v>
+        <v>286</v>
       </c>
       <c r="K226">
         <f t="shared" ca="1" si="4"/>
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L226">
         <f t="shared" ca="1" si="4"/>
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
@@ -9867,15 +9892,15 @@
       </c>
       <c r="J227">
         <f t="shared" ca="1" si="4"/>
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="K227">
         <f t="shared" ca="1" si="4"/>
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="L227">
         <f t="shared" ca="1" si="4"/>
-        <v>138</v>
+        <v>196</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
@@ -9908,15 +9933,15 @@
       </c>
       <c r="J228">
         <f t="shared" ca="1" si="4"/>
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K228">
         <f t="shared" ca="1" si="4"/>
-        <v>278</v>
+        <v>145</v>
       </c>
       <c r="L228">
         <f t="shared" ca="1" si="4"/>
-        <v>223</v>
+        <v>319</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
@@ -9949,15 +9974,15 @@
       </c>
       <c r="J229">
         <f t="shared" ca="1" si="4"/>
-        <v>179</v>
+        <v>340</v>
       </c>
       <c r="K229">
         <f t="shared" ca="1" si="4"/>
-        <v>287</v>
+        <v>348</v>
       </c>
       <c r="L229">
         <f t="shared" ca="1" si="4"/>
-        <v>193</v>
+        <v>228</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
@@ -9990,15 +10015,15 @@
       </c>
       <c r="J230">
         <f t="shared" ca="1" si="4"/>
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="K230">
         <f t="shared" ca="1" si="4"/>
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="L230">
         <f t="shared" ca="1" si="4"/>
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
@@ -10031,15 +10056,15 @@
       </c>
       <c r="J231">
         <f t="shared" ca="1" si="4"/>
-        <v>391</v>
+        <v>150</v>
       </c>
       <c r="K231">
         <f t="shared" ca="1" si="4"/>
-        <v>315</v>
+        <v>256</v>
       </c>
       <c r="L231">
         <f t="shared" ca="1" si="4"/>
-        <v>249</v>
+        <v>231</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
@@ -10072,15 +10097,15 @@
       </c>
       <c r="J232">
         <f t="shared" ca="1" si="4"/>
-        <v>361</v>
+        <v>317</v>
       </c>
       <c r="K232">
         <f t="shared" ca="1" si="4"/>
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="L232">
         <f t="shared" ca="1" si="4"/>
-        <v>241</v>
+        <v>174</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
@@ -10113,15 +10138,15 @@
       </c>
       <c r="J233">
         <f t="shared" ca="1" si="4"/>
-        <v>283</v>
+        <v>165</v>
       </c>
       <c r="K233">
         <f t="shared" ca="1" si="4"/>
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="L233">
         <f t="shared" ca="1" si="4"/>
-        <v>318</v>
+        <v>177</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
@@ -10154,15 +10179,15 @@
       </c>
       <c r="J234">
         <f t="shared" ca="1" si="4"/>
-        <v>329</v>
+        <v>120</v>
       </c>
       <c r="K234">
         <f t="shared" ca="1" si="4"/>
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="L234">
         <f t="shared" ca="1" si="4"/>
-        <v>245</v>
+        <v>135</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
@@ -10195,15 +10220,15 @@
       </c>
       <c r="J235">
         <f t="shared" ca="1" si="4"/>
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="K235">
         <f t="shared" ca="1" si="4"/>
-        <v>343</v>
+        <v>285</v>
       </c>
       <c r="L235">
         <f t="shared" ca="1" si="4"/>
-        <v>236</v>
+        <v>397</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
@@ -10236,15 +10261,15 @@
       </c>
       <c r="J236">
         <f t="shared" ca="1" si="4"/>
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K236">
         <f t="shared" ca="1" si="4"/>
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L236">
         <f t="shared" ca="1" si="4"/>
-        <v>389</v>
+        <v>184</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
@@ -10277,15 +10302,15 @@
       </c>
       <c r="J237">
         <f t="shared" ca="1" si="4"/>
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="K237">
         <f t="shared" ca="1" si="4"/>
-        <v>340</v>
+        <v>397</v>
       </c>
       <c r="L237">
         <f t="shared" ca="1" si="4"/>
-        <v>205</v>
+        <v>239</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
@@ -10318,15 +10343,15 @@
       </c>
       <c r="J238">
         <f t="shared" ca="1" si="4"/>
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="K238">
         <f t="shared" ca="1" si="4"/>
-        <v>201</v>
+        <v>350</v>
       </c>
       <c r="L238">
         <f t="shared" ca="1" si="4"/>
-        <v>231</v>
+        <v>395</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
@@ -10359,15 +10384,15 @@
       </c>
       <c r="J239">
         <f t="shared" ca="1" si="4"/>
-        <v>105</v>
+        <v>361</v>
       </c>
       <c r="K239">
         <f t="shared" ca="1" si="4"/>
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="L239">
         <f t="shared" ca="1" si="4"/>
-        <v>115</v>
+        <v>247</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
@@ -10400,15 +10425,15 @@
       </c>
       <c r="J240">
         <f t="shared" ca="1" si="4"/>
-        <v>102</v>
+        <v>309</v>
       </c>
       <c r="K240">
         <f t="shared" ca="1" si="4"/>
-        <v>376</v>
+        <v>133</v>
       </c>
       <c r="L240">
         <f t="shared" ca="1" si="4"/>
-        <v>387</v>
+        <v>265</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
@@ -10441,15 +10466,15 @@
       </c>
       <c r="J241">
         <f t="shared" ca="1" si="4"/>
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="K241">
         <f t="shared" ca="1" si="4"/>
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="L241">
         <f t="shared" ca="1" si="4"/>
-        <v>400</v>
+        <v>248</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.3">
@@ -10482,15 +10507,15 @@
       </c>
       <c r="J242">
         <f t="shared" ca="1" si="4"/>
-        <v>371</v>
+        <v>297</v>
       </c>
       <c r="K242">
         <f t="shared" ca="1" si="4"/>
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="L242">
         <f t="shared" ca="1" si="4"/>
-        <v>181</v>
+        <v>358</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
@@ -10523,15 +10548,15 @@
       </c>
       <c r="J243">
         <f t="shared" ca="1" si="4"/>
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="K243">
         <f t="shared" ca="1" si="4"/>
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="L243">
         <f t="shared" ca="1" si="4"/>
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
@@ -10564,15 +10589,15 @@
       </c>
       <c r="J244">
         <f t="shared" ca="1" si="4"/>
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="K244">
         <f t="shared" ca="1" si="4"/>
-        <v>108</v>
+        <v>343</v>
       </c>
       <c r="L244">
         <f t="shared" ca="1" si="4"/>
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
@@ -10605,15 +10630,15 @@
       </c>
       <c r="J245">
         <f t="shared" ca="1" si="4"/>
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="K245">
         <f t="shared" ca="1" si="4"/>
-        <v>382</v>
+        <v>235</v>
       </c>
       <c r="L245">
         <f t="shared" ca="1" si="4"/>
-        <v>209</v>
+        <v>243</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
@@ -10646,15 +10671,15 @@
       </c>
       <c r="J246">
         <f t="shared" ca="1" si="4"/>
-        <v>126</v>
+        <v>307</v>
       </c>
       <c r="K246">
         <f t="shared" ca="1" si="4"/>
-        <v>313</v>
+        <v>355</v>
       </c>
       <c r="L246">
         <f t="shared" ca="1" si="4"/>
-        <v>274</v>
+        <v>335</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
@@ -10687,15 +10712,15 @@
       </c>
       <c r="J247">
         <f t="shared" ca="1" si="4"/>
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="K247">
         <f t="shared" ca="1" si="4"/>
-        <v>302</v>
+        <v>373</v>
       </c>
       <c r="L247">
         <f t="shared" ca="1" si="4"/>
-        <v>108</v>
+        <v>268</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
@@ -10728,15 +10753,15 @@
       </c>
       <c r="J248">
         <f t="shared" ca="1" si="4"/>
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K248">
         <f t="shared" ca="1" si="4"/>
-        <v>376</v>
+        <v>303</v>
       </c>
       <c r="L248">
         <f t="shared" ca="1" si="4"/>
-        <v>321</v>
+        <v>129</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
@@ -10769,15 +10794,15 @@
       </c>
       <c r="J249">
         <f t="shared" ca="1" si="4"/>
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="K249">
         <f t="shared" ca="1" si="4"/>
-        <v>248</v>
+        <v>349</v>
       </c>
       <c r="L249">
         <f t="shared" ca="1" si="4"/>
-        <v>147</v>
+        <v>232</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
@@ -10810,15 +10835,15 @@
       </c>
       <c r="J250">
         <f t="shared" ca="1" si="4"/>
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="K250">
         <f t="shared" ca="1" si="4"/>
-        <v>194</v>
+        <v>357</v>
       </c>
       <c r="L250">
         <f t="shared" ca="1" si="4"/>
-        <v>174</v>
+        <v>313</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
@@ -10851,15 +10876,15 @@
       </c>
       <c r="J251">
         <f t="shared" ca="1" si="4"/>
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="K251">
         <f t="shared" ca="1" si="4"/>
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="L251">
         <f t="shared" ca="1" si="4"/>
-        <v>366</v>
+        <v>207</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
@@ -10892,15 +10917,15 @@
       </c>
       <c r="J252">
         <f t="shared" ca="1" si="4"/>
-        <v>334</v>
+        <v>264</v>
       </c>
       <c r="K252">
         <f t="shared" ca="1" si="4"/>
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="L252">
         <f t="shared" ca="1" si="4"/>
-        <v>338</v>
+        <v>247</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
@@ -10933,15 +10958,15 @@
       </c>
       <c r="J253">
         <f t="shared" ca="1" si="4"/>
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="K253">
         <f t="shared" ca="1" si="4"/>
-        <v>151</v>
+        <v>351</v>
       </c>
       <c r="L253">
         <f t="shared" ca="1" si="4"/>
-        <v>246</v>
+        <v>346</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
@@ -10974,15 +10999,15 @@
       </c>
       <c r="J254">
         <f t="shared" ca="1" si="4"/>
-        <v>121</v>
+        <v>249</v>
       </c>
       <c r="K254">
         <f t="shared" ca="1" si="4"/>
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="L254">
         <f t="shared" ca="1" si="4"/>
-        <v>236</v>
+        <v>202</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
@@ -11015,15 +11040,15 @@
       </c>
       <c r="J255">
         <f t="shared" ca="1" si="4"/>
-        <v>182</v>
+        <v>238</v>
       </c>
       <c r="K255">
         <f t="shared" ca="1" si="4"/>
-        <v>174</v>
+        <v>317</v>
       </c>
       <c r="L255">
         <f t="shared" ca="1" si="4"/>
-        <v>210</v>
+        <v>245</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
@@ -11056,15 +11081,15 @@
       </c>
       <c r="J256">
         <f t="shared" ca="1" si="4"/>
-        <v>271</v>
+        <v>367</v>
       </c>
       <c r="K256">
         <f t="shared" ca="1" si="4"/>
-        <v>358</v>
+        <v>141</v>
       </c>
       <c r="L256">
         <f t="shared" ca="1" si="4"/>
-        <v>306</v>
+        <v>238</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
@@ -11101,11 +11126,11 @@
       </c>
       <c r="K257">
         <f t="shared" ca="1" si="4"/>
-        <v>222</v>
+        <v>368</v>
       </c>
       <c r="L257">
         <f t="shared" ca="1" si="4"/>
-        <v>318</v>
+        <v>288</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
@@ -11138,15 +11163,15 @@
       </c>
       <c r="J258">
         <f t="shared" ca="1" si="4"/>
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="K258">
         <f t="shared" ca="1" si="4"/>
-        <v>136</v>
+        <v>363</v>
       </c>
       <c r="L258">
         <f t="shared" ca="1" si="4"/>
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
@@ -11179,15 +11204,15 @@
       </c>
       <c r="J259">
         <f t="shared" ref="J259:L322" ca="1" si="5">RANDBETWEEN(100,400)</f>
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="K259">
         <f t="shared" ca="1" si="5"/>
-        <v>382</v>
+        <v>232</v>
       </c>
       <c r="L259">
         <f t="shared" ca="1" si="5"/>
-        <v>125</v>
+        <v>300</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
@@ -11220,15 +11245,15 @@
       </c>
       <c r="J260">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>378</v>
       </c>
       <c r="K260">
         <f t="shared" ca="1" si="5"/>
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="L260">
         <f t="shared" ca="1" si="5"/>
-        <v>296</v>
+        <v>312</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
@@ -11261,15 +11286,15 @@
       </c>
       <c r="J261">
         <f t="shared" ca="1" si="5"/>
-        <v>206</v>
+        <v>295</v>
       </c>
       <c r="K261">
         <f t="shared" ca="1" si="5"/>
-        <v>349</v>
+        <v>214</v>
       </c>
       <c r="L261">
         <f t="shared" ca="1" si="5"/>
-        <v>359</v>
+        <v>247</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
@@ -11302,15 +11327,15 @@
       </c>
       <c r="J262">
         <f t="shared" ca="1" si="5"/>
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="K262">
         <f t="shared" ca="1" si="5"/>
-        <v>375</v>
+        <v>336</v>
       </c>
       <c r="L262">
         <f t="shared" ca="1" si="5"/>
-        <v>203</v>
+        <v>321</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
@@ -11343,15 +11368,15 @@
       </c>
       <c r="J263">
         <f t="shared" ca="1" si="5"/>
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="K263">
         <f t="shared" ca="1" si="5"/>
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="L263">
         <f t="shared" ca="1" si="5"/>
-        <v>329</v>
+        <v>155</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
@@ -11384,15 +11409,15 @@
       </c>
       <c r="J264">
         <f t="shared" ca="1" si="5"/>
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="K264">
         <f t="shared" ca="1" si="5"/>
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="L264">
         <f t="shared" ca="1" si="5"/>
-        <v>178</v>
+        <v>337</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
@@ -11425,15 +11450,15 @@
       </c>
       <c r="J265">
         <f t="shared" ca="1" si="5"/>
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="K265">
         <f t="shared" ca="1" si="5"/>
-        <v>386</v>
+        <v>230</v>
       </c>
       <c r="L265">
         <f t="shared" ca="1" si="5"/>
-        <v>308</v>
+        <v>333</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.3">
@@ -11466,15 +11491,15 @@
       </c>
       <c r="J266">
         <f t="shared" ca="1" si="5"/>
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="K266">
         <f t="shared" ca="1" si="5"/>
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="L266">
         <f t="shared" ca="1" si="5"/>
-        <v>269</v>
+        <v>120</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
@@ -11507,15 +11532,15 @@
       </c>
       <c r="J267">
         <f t="shared" ca="1" si="5"/>
-        <v>381</v>
+        <v>212</v>
       </c>
       <c r="K267">
         <f t="shared" ca="1" si="5"/>
-        <v>106</v>
+        <v>375</v>
       </c>
       <c r="L267">
         <f t="shared" ca="1" si="5"/>
-        <v>326</v>
+        <v>191</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
@@ -11548,15 +11573,15 @@
       </c>
       <c r="J268">
         <f t="shared" ca="1" si="5"/>
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="K268">
         <f t="shared" ca="1" si="5"/>
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="L268">
         <f t="shared" ca="1" si="5"/>
-        <v>173</v>
+        <v>310</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
@@ -11589,15 +11614,15 @@
       </c>
       <c r="J269">
         <f t="shared" ca="1" si="5"/>
-        <v>120</v>
+        <v>237</v>
       </c>
       <c r="K269">
         <f t="shared" ca="1" si="5"/>
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="L269">
         <f t="shared" ca="1" si="5"/>
-        <v>387</v>
+        <v>263</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
@@ -11630,15 +11655,15 @@
       </c>
       <c r="J270">
         <f t="shared" ca="1" si="5"/>
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="K270">
         <f t="shared" ca="1" si="5"/>
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="L270">
         <f t="shared" ca="1" si="5"/>
-        <v>354</v>
+        <v>261</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
@@ -11671,15 +11696,15 @@
       </c>
       <c r="J271">
         <f t="shared" ca="1" si="5"/>
-        <v>107</v>
+        <v>377</v>
       </c>
       <c r="K271">
         <f t="shared" ca="1" si="5"/>
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="L271">
         <f t="shared" ca="1" si="5"/>
-        <v>190</v>
+        <v>227</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
@@ -11712,15 +11737,15 @@
       </c>
       <c r="J272">
         <f t="shared" ca="1" si="5"/>
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="K272">
         <f t="shared" ca="1" si="5"/>
-        <v>368</v>
+        <v>100</v>
       </c>
       <c r="L272">
         <f t="shared" ca="1" si="5"/>
-        <v>287</v>
+        <v>262</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
@@ -11753,15 +11778,15 @@
       </c>
       <c r="J273">
         <f t="shared" ca="1" si="5"/>
-        <v>293</v>
+        <v>110</v>
       </c>
       <c r="K273">
         <f t="shared" ca="1" si="5"/>
-        <v>187</v>
+        <v>397</v>
       </c>
       <c r="L273">
         <f t="shared" ca="1" si="5"/>
-        <v>173</v>
+        <v>248</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
@@ -11794,15 +11819,15 @@
       </c>
       <c r="J274">
         <f t="shared" ca="1" si="5"/>
-        <v>165</v>
+        <v>260</v>
       </c>
       <c r="K274">
         <f t="shared" ca="1" si="5"/>
-        <v>247</v>
+        <v>385</v>
       </c>
       <c r="L274">
         <f t="shared" ca="1" si="5"/>
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
@@ -11835,15 +11860,15 @@
       </c>
       <c r="J275">
         <f t="shared" ca="1" si="5"/>
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K275">
         <f t="shared" ca="1" si="5"/>
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="L275">
         <f t="shared" ca="1" si="5"/>
-        <v>241</v>
+        <v>284</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
@@ -11876,15 +11901,15 @@
       </c>
       <c r="J276">
         <f t="shared" ca="1" si="5"/>
-        <v>136</v>
+        <v>387</v>
       </c>
       <c r="K276">
         <f t="shared" ca="1" si="5"/>
-        <v>126</v>
+        <v>299</v>
       </c>
       <c r="L276">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>137</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
@@ -11917,15 +11942,15 @@
       </c>
       <c r="J277">
         <f t="shared" ca="1" si="5"/>
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="K277">
         <f t="shared" ca="1" si="5"/>
-        <v>361</v>
+        <v>392</v>
       </c>
       <c r="L277">
         <f t="shared" ca="1" si="5"/>
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
@@ -11958,15 +11983,15 @@
       </c>
       <c r="J278">
         <f t="shared" ca="1" si="5"/>
-        <v>109</v>
+        <v>329</v>
       </c>
       <c r="K278">
         <f t="shared" ca="1" si="5"/>
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="L278">
         <f t="shared" ca="1" si="5"/>
-        <v>196</v>
+        <v>267</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
@@ -11999,15 +12024,15 @@
       </c>
       <c r="J279">
         <f t="shared" ca="1" si="5"/>
-        <v>107</v>
+        <v>265</v>
       </c>
       <c r="K279">
         <f t="shared" ca="1" si="5"/>
-        <v>228</v>
+        <v>142</v>
       </c>
       <c r="L279">
         <f t="shared" ca="1" si="5"/>
-        <v>379</v>
+        <v>275</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
@@ -12040,15 +12065,15 @@
       </c>
       <c r="J280">
         <f t="shared" ca="1" si="5"/>
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="K280">
         <f t="shared" ca="1" si="5"/>
-        <v>308</v>
+        <v>388</v>
       </c>
       <c r="L280">
         <f t="shared" ca="1" si="5"/>
-        <v>272</v>
+        <v>355</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
@@ -12081,15 +12106,15 @@
       </c>
       <c r="J281">
         <f t="shared" ca="1" si="5"/>
-        <v>244</v>
+        <v>326</v>
       </c>
       <c r="K281">
         <f t="shared" ca="1" si="5"/>
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="L281">
         <f t="shared" ca="1" si="5"/>
-        <v>373</v>
+        <v>316</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
@@ -12122,15 +12147,15 @@
       </c>
       <c r="J282">
         <f t="shared" ca="1" si="5"/>
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K282">
         <f t="shared" ca="1" si="5"/>
-        <v>396</v>
+        <v>134</v>
       </c>
       <c r="L282">
         <f t="shared" ca="1" si="5"/>
-        <v>329</v>
+        <v>221</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
@@ -12163,15 +12188,15 @@
       </c>
       <c r="J283">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="K283">
         <f t="shared" ca="1" si="5"/>
-        <v>374</v>
+        <v>103</v>
       </c>
       <c r="L283">
         <f t="shared" ca="1" si="5"/>
-        <v>119</v>
+        <v>184</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
@@ -12204,15 +12229,15 @@
       </c>
       <c r="J284">
         <f t="shared" ca="1" si="5"/>
-        <v>366</v>
+        <v>128</v>
       </c>
       <c r="K284">
         <f t="shared" ca="1" si="5"/>
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="L284">
         <f t="shared" ca="1" si="5"/>
-        <v>235</v>
+        <v>172</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
@@ -12245,15 +12270,15 @@
       </c>
       <c r="J285">
         <f t="shared" ca="1" si="5"/>
-        <v>160</v>
+        <v>217</v>
       </c>
       <c r="K285">
         <f t="shared" ca="1" si="5"/>
-        <v>187</v>
+        <v>284</v>
       </c>
       <c r="L285">
         <f t="shared" ca="1" si="5"/>
-        <v>350</v>
+        <v>187</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
@@ -12286,15 +12311,15 @@
       </c>
       <c r="J286">
         <f t="shared" ca="1" si="5"/>
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="K286">
         <f t="shared" ca="1" si="5"/>
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="L286">
         <f t="shared" ca="1" si="5"/>
-        <v>134</v>
+        <v>193</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
@@ -12327,15 +12352,15 @@
       </c>
       <c r="J287">
         <f t="shared" ca="1" si="5"/>
-        <v>311</v>
+        <v>106</v>
       </c>
       <c r="K287">
         <f t="shared" ca="1" si="5"/>
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="L287">
         <f t="shared" ca="1" si="5"/>
-        <v>259</v>
+        <v>400</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
@@ -12368,15 +12393,15 @@
       </c>
       <c r="J288">
         <f t="shared" ca="1" si="5"/>
-        <v>238</v>
+        <v>171</v>
       </c>
       <c r="K288">
         <f t="shared" ca="1" si="5"/>
-        <v>214</v>
+        <v>143</v>
       </c>
       <c r="L288">
         <f t="shared" ca="1" si="5"/>
-        <v>326</v>
+        <v>382</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
@@ -12409,15 +12434,15 @@
       </c>
       <c r="J289">
         <f t="shared" ca="1" si="5"/>
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="K289">
         <f t="shared" ca="1" si="5"/>
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="L289">
         <f t="shared" ca="1" si="5"/>
-        <v>361</v>
+        <v>240</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.3">
@@ -12450,15 +12475,15 @@
       </c>
       <c r="J290">
         <f t="shared" ca="1" si="5"/>
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="K290">
         <f t="shared" ca="1" si="5"/>
-        <v>353</v>
+        <v>145</v>
       </c>
       <c r="L290">
         <f t="shared" ca="1" si="5"/>
-        <v>275</v>
+        <v>134</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
@@ -12491,15 +12516,15 @@
       </c>
       <c r="J291">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="K291">
         <f t="shared" ca="1" si="5"/>
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="L291">
         <f t="shared" ca="1" si="5"/>
-        <v>297</v>
+        <v>165</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
@@ -12532,15 +12557,15 @@
       </c>
       <c r="J292">
         <f t="shared" ca="1" si="5"/>
-        <v>345</v>
+        <v>100</v>
       </c>
       <c r="K292">
         <f t="shared" ca="1" si="5"/>
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="L292">
         <f t="shared" ca="1" si="5"/>
-        <v>336</v>
+        <v>257</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
@@ -12573,15 +12598,15 @@
       </c>
       <c r="J293">
         <f t="shared" ca="1" si="5"/>
-        <v>269</v>
+        <v>119</v>
       </c>
       <c r="K293">
         <f t="shared" ca="1" si="5"/>
-        <v>269</v>
+        <v>182</v>
       </c>
       <c r="L293">
         <f t="shared" ca="1" si="5"/>
-        <v>181</v>
+        <v>234</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
@@ -12614,15 +12639,15 @@
       </c>
       <c r="J294">
         <f t="shared" ca="1" si="5"/>
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="K294">
         <f t="shared" ca="1" si="5"/>
-        <v>366</v>
+        <v>115</v>
       </c>
       <c r="L294">
         <f t="shared" ca="1" si="5"/>
-        <v>354</v>
+        <v>296</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
@@ -12655,15 +12680,15 @@
       </c>
       <c r="J295">
         <f t="shared" ca="1" si="5"/>
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="K295">
         <f t="shared" ca="1" si="5"/>
-        <v>281</v>
+        <v>160</v>
       </c>
       <c r="L295">
         <f t="shared" ca="1" si="5"/>
-        <v>238</v>
+        <v>329</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
@@ -12696,15 +12721,15 @@
       </c>
       <c r="J296">
         <f t="shared" ca="1" si="5"/>
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K296">
         <f t="shared" ca="1" si="5"/>
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="L296">
         <f t="shared" ca="1" si="5"/>
-        <v>376</v>
+        <v>250</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
@@ -12737,15 +12762,15 @@
       </c>
       <c r="J297">
         <f t="shared" ca="1" si="5"/>
-        <v>336</v>
+        <v>154</v>
       </c>
       <c r="K297">
         <f t="shared" ca="1" si="5"/>
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="L297">
         <f t="shared" ca="1" si="5"/>
-        <v>308</v>
+        <v>155</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
@@ -12778,15 +12803,15 @@
       </c>
       <c r="J298">
         <f t="shared" ca="1" si="5"/>
-        <v>378</v>
+        <v>172</v>
       </c>
       <c r="K298">
         <f t="shared" ca="1" si="5"/>
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="L298">
         <f t="shared" ca="1" si="5"/>
-        <v>400</v>
+        <v>369</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
@@ -12819,15 +12844,15 @@
       </c>
       <c r="J299">
         <f t="shared" ca="1" si="5"/>
-        <v>384</v>
+        <v>159</v>
       </c>
       <c r="K299">
         <f t="shared" ca="1" si="5"/>
-        <v>345</v>
+        <v>274</v>
       </c>
       <c r="L299">
         <f t="shared" ca="1" si="5"/>
-        <v>157</v>
+        <v>374</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
@@ -12860,15 +12885,15 @@
       </c>
       <c r="J300">
         <f t="shared" ca="1" si="5"/>
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="K300">
         <f t="shared" ca="1" si="5"/>
-        <v>398</v>
+        <v>295</v>
       </c>
       <c r="L300">
         <f t="shared" ca="1" si="5"/>
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
@@ -12901,15 +12926,15 @@
       </c>
       <c r="J301">
         <f t="shared" ca="1" si="5"/>
-        <v>214</v>
+        <v>292</v>
       </c>
       <c r="K301">
         <f t="shared" ca="1" si="5"/>
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="L301">
         <f t="shared" ca="1" si="5"/>
-        <v>109</v>
+        <v>272</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
@@ -12942,15 +12967,15 @@
       </c>
       <c r="J302">
         <f t="shared" ca="1" si="5"/>
-        <v>382</v>
+        <v>268</v>
       </c>
       <c r="K302">
         <f t="shared" ca="1" si="5"/>
-        <v>354</v>
+        <v>108</v>
       </c>
       <c r="L302">
         <f t="shared" ca="1" si="5"/>
-        <v>256</v>
+        <v>203</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
@@ -12983,15 +13008,15 @@
       </c>
       <c r="J303">
         <f t="shared" ca="1" si="5"/>
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="K303">
         <f t="shared" ca="1" si="5"/>
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="L303">
         <f t="shared" ca="1" si="5"/>
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
@@ -13024,15 +13049,15 @@
       </c>
       <c r="J304">
         <f t="shared" ca="1" si="5"/>
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="K304">
         <f t="shared" ca="1" si="5"/>
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L304">
         <f t="shared" ca="1" si="5"/>
-        <v>365</v>
+        <v>244</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
@@ -13065,15 +13090,15 @@
       </c>
       <c r="J305">
         <f t="shared" ca="1" si="5"/>
-        <v>198</v>
+        <v>324</v>
       </c>
       <c r="K305">
         <f t="shared" ca="1" si="5"/>
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="L305">
         <f t="shared" ca="1" si="5"/>
-        <v>124</v>
+        <v>216</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
@@ -13106,15 +13131,15 @@
       </c>
       <c r="J306">
         <f t="shared" ca="1" si="5"/>
-        <v>354</v>
+        <v>250</v>
       </c>
       <c r="K306">
         <f t="shared" ca="1" si="5"/>
-        <v>203</v>
+        <v>323</v>
       </c>
       <c r="L306">
         <f t="shared" ca="1" si="5"/>
-        <v>281</v>
+        <v>155</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
@@ -13147,15 +13172,15 @@
       </c>
       <c r="J307">
         <f t="shared" ca="1" si="5"/>
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="K307">
         <f t="shared" ca="1" si="5"/>
-        <v>395</v>
+        <v>184</v>
       </c>
       <c r="L307">
         <f t="shared" ca="1" si="5"/>
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
@@ -13188,15 +13213,15 @@
       </c>
       <c r="J308">
         <f t="shared" ca="1" si="5"/>
-        <v>385</v>
+        <v>324</v>
       </c>
       <c r="K308">
         <f t="shared" ca="1" si="5"/>
-        <v>303</v>
+        <v>267</v>
       </c>
       <c r="L308">
         <f t="shared" ca="1" si="5"/>
-        <v>193</v>
+        <v>112</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
@@ -13229,15 +13254,15 @@
       </c>
       <c r="J309">
         <f t="shared" ca="1" si="5"/>
-        <v>257</v>
+        <v>101</v>
       </c>
       <c r="K309">
         <f t="shared" ca="1" si="5"/>
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L309">
         <f t="shared" ca="1" si="5"/>
-        <v>282</v>
+        <v>188</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
@@ -13270,15 +13295,15 @@
       </c>
       <c r="J310">
         <f t="shared" ca="1" si="5"/>
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="K310">
         <f t="shared" ca="1" si="5"/>
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="L310">
         <f t="shared" ca="1" si="5"/>
-        <v>389</v>
+        <v>267</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
@@ -13311,15 +13336,15 @@
       </c>
       <c r="J311">
         <f t="shared" ca="1" si="5"/>
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="K311">
         <f t="shared" ca="1" si="5"/>
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="L311">
         <f t="shared" ca="1" si="5"/>
-        <v>204</v>
+        <v>273</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
@@ -13352,15 +13377,15 @@
       </c>
       <c r="J312">
         <f t="shared" ca="1" si="5"/>
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="K312">
         <f t="shared" ca="1" si="5"/>
-        <v>239</v>
+        <v>141</v>
       </c>
       <c r="L312">
         <f t="shared" ca="1" si="5"/>
-        <v>272</v>
+        <v>242</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
@@ -13393,15 +13418,15 @@
       </c>
       <c r="J313">
         <f t="shared" ca="1" si="5"/>
-        <v>371</v>
+        <v>134</v>
       </c>
       <c r="K313">
         <f t="shared" ca="1" si="5"/>
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="L313">
         <f t="shared" ca="1" si="5"/>
-        <v>382</v>
+        <v>263</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.3">
@@ -13434,15 +13459,15 @@
       </c>
       <c r="J314">
         <f t="shared" ca="1" si="5"/>
-        <v>384</v>
+        <v>142</v>
       </c>
       <c r="K314">
         <f t="shared" ca="1" si="5"/>
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L314">
         <f t="shared" ca="1" si="5"/>
-        <v>231</v>
+        <v>261</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
@@ -13475,15 +13500,15 @@
       </c>
       <c r="J315">
         <f t="shared" ca="1" si="5"/>
-        <v>268</v>
+        <v>362</v>
       </c>
       <c r="K315">
         <f t="shared" ca="1" si="5"/>
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="L315">
         <f t="shared" ca="1" si="5"/>
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
@@ -13516,15 +13541,15 @@
       </c>
       <c r="J316">
         <f t="shared" ca="1" si="5"/>
-        <v>142</v>
+        <v>256</v>
       </c>
       <c r="K316">
         <f t="shared" ca="1" si="5"/>
-        <v>311</v>
+        <v>227</v>
       </c>
       <c r="L316">
         <f t="shared" ca="1" si="5"/>
-        <v>296</v>
+        <v>105</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
@@ -13557,15 +13582,15 @@
       </c>
       <c r="J317">
         <f t="shared" ca="1" si="5"/>
-        <v>237</v>
+        <v>160</v>
       </c>
       <c r="K317">
         <f t="shared" ca="1" si="5"/>
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="L317">
         <f t="shared" ca="1" si="5"/>
-        <v>329</v>
+        <v>182</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
@@ -13598,15 +13623,15 @@
       </c>
       <c r="J318">
         <f t="shared" ca="1" si="5"/>
-        <v>345</v>
+        <v>245</v>
       </c>
       <c r="K318">
         <f t="shared" ca="1" si="5"/>
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="L318">
         <f t="shared" ca="1" si="5"/>
-        <v>399</v>
+        <v>372</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.3">
@@ -13639,15 +13664,15 @@
       </c>
       <c r="J319">
         <f t="shared" ca="1" si="5"/>
-        <v>173</v>
+        <v>263</v>
       </c>
       <c r="K319">
         <f t="shared" ca="1" si="5"/>
-        <v>331</v>
+        <v>206</v>
       </c>
       <c r="L319">
         <f t="shared" ca="1" si="5"/>
-        <v>196</v>
+        <v>165</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.3">
@@ -13680,15 +13705,15 @@
       </c>
       <c r="J320">
         <f t="shared" ca="1" si="5"/>
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="K320">
         <f t="shared" ca="1" si="5"/>
-        <v>386</v>
+        <v>188</v>
       </c>
       <c r="L320">
         <f t="shared" ca="1" si="5"/>
-        <v>385</v>
+        <v>101</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.3">
@@ -13721,15 +13746,15 @@
       </c>
       <c r="J321">
         <f t="shared" ca="1" si="5"/>
-        <v>146</v>
+        <v>309</v>
       </c>
       <c r="K321">
         <f t="shared" ca="1" si="5"/>
-        <v>156</v>
+        <v>256</v>
       </c>
       <c r="L321">
         <f t="shared" ca="1" si="5"/>
-        <v>117</v>
+        <v>145</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.3">
@@ -13762,15 +13787,15 @@
       </c>
       <c r="J322">
         <f t="shared" ca="1" si="5"/>
-        <v>369</v>
+        <v>143</v>
       </c>
       <c r="K322">
         <f t="shared" ca="1" si="5"/>
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="L322">
         <f t="shared" ca="1" si="5"/>
-        <v>357</v>
+        <v>229</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
@@ -13803,15 +13828,15 @@
       </c>
       <c r="J323">
         <f t="shared" ref="J323:L354" ca="1" si="6">RANDBETWEEN(100,400)</f>
-        <v>371</v>
+        <v>207</v>
       </c>
       <c r="K323">
         <f t="shared" ca="1" si="6"/>
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L323">
         <f t="shared" ca="1" si="6"/>
-        <v>131</v>
+        <v>358</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.3">
@@ -13844,15 +13869,15 @@
       </c>
       <c r="J324">
         <f t="shared" ca="1" si="6"/>
-        <v>371</v>
+        <v>285</v>
       </c>
       <c r="K324">
         <f t="shared" ca="1" si="6"/>
-        <v>325</v>
+        <v>265</v>
       </c>
       <c r="L324">
         <f t="shared" ca="1" si="6"/>
-        <v>139</v>
+        <v>364</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.3">
@@ -13885,15 +13910,15 @@
       </c>
       <c r="J325">
         <f t="shared" ca="1" si="6"/>
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="K325">
         <f t="shared" ca="1" si="6"/>
-        <v>339</v>
+        <v>200</v>
       </c>
       <c r="L325">
         <f t="shared" ca="1" si="6"/>
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.3">
@@ -13926,15 +13951,15 @@
       </c>
       <c r="J326">
         <f t="shared" ca="1" si="6"/>
-        <v>154</v>
+        <v>342</v>
       </c>
       <c r="K326">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>188</v>
       </c>
       <c r="L326">
         <f t="shared" ca="1" si="6"/>
-        <v>324</v>
+        <v>250</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.3">
@@ -13967,15 +13992,15 @@
       </c>
       <c r="J327">
         <f t="shared" ca="1" si="6"/>
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="K327">
         <f t="shared" ca="1" si="6"/>
-        <v>212</v>
+        <v>389</v>
       </c>
       <c r="L327">
         <f t="shared" ca="1" si="6"/>
-        <v>127</v>
+        <v>312</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.3">
@@ -14008,11 +14033,11 @@
       </c>
       <c r="J328">
         <f t="shared" ca="1" si="6"/>
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="K328">
         <f t="shared" ca="1" si="6"/>
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="L328">
         <f t="shared" ca="1" si="6"/>
@@ -14049,15 +14074,15 @@
       </c>
       <c r="J329">
         <f t="shared" ca="1" si="6"/>
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="K329">
         <f t="shared" ca="1" si="6"/>
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="L329">
         <f t="shared" ca="1" si="6"/>
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.3">
@@ -14090,15 +14115,15 @@
       </c>
       <c r="J330">
         <f t="shared" ca="1" si="6"/>
-        <v>185</v>
+        <v>286</v>
       </c>
       <c r="K330">
         <f t="shared" ca="1" si="6"/>
-        <v>356</v>
+        <v>127</v>
       </c>
       <c r="L330">
         <f t="shared" ca="1" si="6"/>
-        <v>260</v>
+        <v>323</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.3">
@@ -14131,15 +14156,15 @@
       </c>
       <c r="J331">
         <f t="shared" ca="1" si="6"/>
-        <v>246</v>
+        <v>116</v>
       </c>
       <c r="K331">
         <f t="shared" ca="1" si="6"/>
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="L331">
         <f t="shared" ca="1" si="6"/>
-        <v>122</v>
+        <v>360</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.3">
@@ -14172,15 +14197,15 @@
       </c>
       <c r="J332">
         <f t="shared" ca="1" si="6"/>
-        <v>309</v>
+        <v>143</v>
       </c>
       <c r="K332">
         <f t="shared" ca="1" si="6"/>
-        <v>337</v>
+        <v>213</v>
       </c>
       <c r="L332">
         <f t="shared" ca="1" si="6"/>
-        <v>234</v>
+        <v>300</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.3">
@@ -14213,15 +14238,15 @@
       </c>
       <c r="J333">
         <f t="shared" ca="1" si="6"/>
-        <v>108</v>
+        <v>391</v>
       </c>
       <c r="K333">
         <f t="shared" ca="1" si="6"/>
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="L333">
         <f t="shared" ca="1" si="6"/>
-        <v>257</v>
+        <v>233</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.3">
@@ -14254,15 +14279,15 @@
       </c>
       <c r="J334">
         <f t="shared" ca="1" si="6"/>
-        <v>287</v>
+        <v>378</v>
       </c>
       <c r="K334">
         <f t="shared" ca="1" si="6"/>
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="L334">
         <f t="shared" ca="1" si="6"/>
-        <v>392</v>
+        <v>280</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.3">
@@ -14295,15 +14320,15 @@
       </c>
       <c r="J335">
         <f t="shared" ca="1" si="6"/>
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="K335">
         <f t="shared" ca="1" si="6"/>
-        <v>260</v>
+        <v>381</v>
       </c>
       <c r="L335">
         <f t="shared" ca="1" si="6"/>
-        <v>121</v>
+        <v>337</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.3">
@@ -14336,15 +14361,15 @@
       </c>
       <c r="J336">
         <f t="shared" ca="1" si="6"/>
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="K336">
         <f t="shared" ca="1" si="6"/>
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="L336">
         <f t="shared" ca="1" si="6"/>
-        <v>179</v>
+        <v>339</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.3">
@@ -14377,15 +14402,15 @@
       </c>
       <c r="J337">
         <f t="shared" ca="1" si="6"/>
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="K337">
         <f t="shared" ca="1" si="6"/>
-        <v>367</v>
+        <v>191</v>
       </c>
       <c r="L337">
         <f t="shared" ca="1" si="6"/>
-        <v>369</v>
+        <v>293</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.3">
@@ -14418,15 +14443,15 @@
       </c>
       <c r="J338">
         <f t="shared" ca="1" si="6"/>
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="K338">
         <f t="shared" ca="1" si="6"/>
-        <v>400</v>
+        <v>252</v>
       </c>
       <c r="L338">
         <f t="shared" ca="1" si="6"/>
-        <v>317</v>
+        <v>217</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.3">
@@ -14459,15 +14484,15 @@
       </c>
       <c r="J339">
         <f t="shared" ca="1" si="6"/>
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="K339">
         <f t="shared" ca="1" si="6"/>
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="L339">
         <f t="shared" ca="1" si="6"/>
-        <v>215</v>
+        <v>287</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.3">
@@ -14500,15 +14525,15 @@
       </c>
       <c r="J340">
         <f t="shared" ca="1" si="6"/>
-        <v>162</v>
+        <v>329</v>
       </c>
       <c r="K340">
         <f t="shared" ca="1" si="6"/>
-        <v>376</v>
+        <v>292</v>
       </c>
       <c r="L340">
         <f t="shared" ca="1" si="6"/>
-        <v>201</v>
+        <v>291</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.3">
@@ -14541,15 +14566,15 @@
       </c>
       <c r="J341">
         <f t="shared" ca="1" si="6"/>
-        <v>125</v>
+        <v>297</v>
       </c>
       <c r="K341">
         <f t="shared" ca="1" si="6"/>
-        <v>220</v>
+        <v>124</v>
       </c>
       <c r="L341">
         <f t="shared" ca="1" si="6"/>
-        <v>309</v>
+        <v>126</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.3">
@@ -14582,15 +14607,15 @@
       </c>
       <c r="J342">
         <f t="shared" ca="1" si="6"/>
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="K342">
         <f t="shared" ca="1" si="6"/>
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="L342">
         <f t="shared" ca="1" si="6"/>
-        <v>116</v>
+        <v>321</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.3">
@@ -14623,15 +14648,15 @@
       </c>
       <c r="J343">
         <f t="shared" ca="1" si="6"/>
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="K343">
         <f t="shared" ca="1" si="6"/>
-        <v>213</v>
+        <v>298</v>
       </c>
       <c r="L343">
         <f t="shared" ca="1" si="6"/>
-        <v>242</v>
+        <v>192</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.3">
@@ -14664,15 +14689,15 @@
       </c>
       <c r="J344">
         <f t="shared" ca="1" si="6"/>
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="K344">
         <f t="shared" ca="1" si="6"/>
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="L344">
         <f t="shared" ca="1" si="6"/>
-        <v>100</v>
+        <v>211</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.3">
@@ -14705,15 +14730,15 @@
       </c>
       <c r="J345">
         <f t="shared" ca="1" si="6"/>
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="K345">
         <f t="shared" ca="1" si="6"/>
-        <v>366</v>
+        <v>177</v>
       </c>
       <c r="L345">
         <f t="shared" ca="1" si="6"/>
-        <v>143</v>
+        <v>254</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.3">
@@ -14746,15 +14771,15 @@
       </c>
       <c r="J346">
         <f t="shared" ca="1" si="6"/>
-        <v>224</v>
+        <v>105</v>
       </c>
       <c r="K346">
         <f t="shared" ca="1" si="6"/>
-        <v>391</v>
+        <v>185</v>
       </c>
       <c r="L346">
         <f t="shared" ca="1" si="6"/>
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.3">
@@ -14787,15 +14812,15 @@
       </c>
       <c r="J347">
         <f t="shared" ca="1" si="6"/>
-        <v>369</v>
+        <v>193</v>
       </c>
       <c r="K347">
         <f t="shared" ca="1" si="6"/>
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="L347">
         <f t="shared" ca="1" si="6"/>
-        <v>323</v>
+        <v>199</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.3">
@@ -14828,15 +14853,15 @@
       </c>
       <c r="J348">
         <f t="shared" ca="1" si="6"/>
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="K348">
         <f t="shared" ca="1" si="6"/>
-        <v>321</v>
+        <v>266</v>
       </c>
       <c r="L348">
         <f t="shared" ca="1" si="6"/>
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.3">
@@ -14869,15 +14894,15 @@
       </c>
       <c r="J349">
         <f t="shared" ca="1" si="6"/>
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="K349">
         <f t="shared" ca="1" si="6"/>
-        <v>352</v>
+        <v>211</v>
       </c>
       <c r="L349">
         <f t="shared" ca="1" si="6"/>
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.3">
@@ -14910,15 +14935,15 @@
       </c>
       <c r="J350">
         <f t="shared" ca="1" si="6"/>
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="K350">
         <f t="shared" ca="1" si="6"/>
-        <v>193</v>
+        <v>355</v>
       </c>
       <c r="L350">
         <f t="shared" ca="1" si="6"/>
-        <v>236</v>
+        <v>381</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.3">
@@ -14951,15 +14976,15 @@
       </c>
       <c r="J351">
         <f t="shared" ca="1" si="6"/>
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="K351">
         <f t="shared" ca="1" si="6"/>
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="L351">
         <f t="shared" ca="1" si="6"/>
-        <v>246</v>
+        <v>228</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.3">
@@ -14992,15 +15017,15 @@
       </c>
       <c r="J352">
         <f t="shared" ca="1" si="6"/>
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K352">
         <f t="shared" ca="1" si="6"/>
-        <v>372</v>
+        <v>208</v>
       </c>
       <c r="L352">
         <f t="shared" ca="1" si="6"/>
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.3">
@@ -15033,15 +15058,15 @@
       </c>
       <c r="J353">
         <f t="shared" ca="1" si="6"/>
-        <v>210</v>
+        <v>367</v>
       </c>
       <c r="K353">
         <f t="shared" ca="1" si="6"/>
-        <v>389</v>
+        <v>153</v>
       </c>
       <c r="L353">
         <f t="shared" ca="1" si="6"/>
-        <v>201</v>
+        <v>235</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.3">
@@ -15074,15 +15099,15 @@
       </c>
       <c r="J354">
         <f t="shared" ca="1" si="6"/>
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="K354">
         <f t="shared" ca="1" si="6"/>
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="L354">
         <f t="shared" ca="1" si="6"/>
-        <v>164</v>
+        <v>321</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.3">
@@ -15115,15 +15140,15 @@
       </c>
       <c r="J355">
         <f t="shared" ref="J355:L386" ca="1" si="7">RANDBETWEEN(100,400)</f>
-        <v>292</v>
+        <v>244</v>
       </c>
       <c r="K355">
         <f t="shared" ca="1" si="7"/>
-        <v>130</v>
+        <v>395</v>
       </c>
       <c r="L355">
         <f t="shared" ca="1" si="7"/>
-        <v>365</v>
+        <v>126</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.3">
@@ -15156,15 +15181,15 @@
       </c>
       <c r="J356">
         <f t="shared" ca="1" si="7"/>
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="K356">
         <f t="shared" ca="1" si="7"/>
-        <v>384</v>
+        <v>142</v>
       </c>
       <c r="L356">
         <f t="shared" ca="1" si="7"/>
-        <v>385</v>
+        <v>137</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.3">
@@ -15197,15 +15222,15 @@
       </c>
       <c r="J357">
         <f t="shared" ca="1" si="7"/>
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="K357">
         <f t="shared" ca="1" si="7"/>
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="L357">
         <f t="shared" ca="1" si="7"/>
-        <v>190</v>
+        <v>124</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.3">
@@ -15238,15 +15263,15 @@
       </c>
       <c r="J358">
         <f t="shared" ca="1" si="7"/>
-        <v>254</v>
+        <v>139</v>
       </c>
       <c r="K358">
         <f t="shared" ca="1" si="7"/>
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="L358">
         <f t="shared" ca="1" si="7"/>
-        <v>179</v>
+        <v>198</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.3">
@@ -15279,15 +15304,15 @@
       </c>
       <c r="J359">
         <f t="shared" ca="1" si="7"/>
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="K359">
         <f t="shared" ca="1" si="7"/>
-        <v>390</v>
+        <v>155</v>
       </c>
       <c r="L359">
         <f t="shared" ca="1" si="7"/>
-        <v>142</v>
+        <v>267</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.3">
@@ -15320,15 +15345,15 @@
       </c>
       <c r="J360">
         <f t="shared" ca="1" si="7"/>
-        <v>164</v>
+        <v>297</v>
       </c>
       <c r="K360">
         <f t="shared" ca="1" si="7"/>
-        <v>231</v>
+        <v>398</v>
       </c>
       <c r="L360">
         <f t="shared" ca="1" si="7"/>
-        <v>202</v>
+        <v>294</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.3">
@@ -15361,15 +15386,15 @@
       </c>
       <c r="J361">
         <f t="shared" ca="1" si="7"/>
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="K361">
         <f t="shared" ca="1" si="7"/>
-        <v>355</v>
+        <v>118</v>
       </c>
       <c r="L361">
         <f t="shared" ca="1" si="7"/>
-        <v>170</v>
+        <v>216</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.3">
@@ -15402,15 +15427,15 @@
       </c>
       <c r="J362">
         <f t="shared" ca="1" si="7"/>
-        <v>357</v>
+        <v>245</v>
       </c>
       <c r="K362">
         <f t="shared" ca="1" si="7"/>
-        <v>343</v>
+        <v>145</v>
       </c>
       <c r="L362">
         <f t="shared" ca="1" si="7"/>
-        <v>158</v>
+        <v>276</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.3">
@@ -15443,15 +15468,15 @@
       </c>
       <c r="J363">
         <f t="shared" ca="1" si="7"/>
-        <v>369</v>
+        <v>266</v>
       </c>
       <c r="K363">
         <f t="shared" ca="1" si="7"/>
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="L363">
         <f t="shared" ca="1" si="7"/>
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
@@ -15484,15 +15509,15 @@
       </c>
       <c r="J364">
         <f t="shared" ca="1" si="7"/>
-        <v>334</v>
+        <v>224</v>
       </c>
       <c r="K364">
         <f t="shared" ca="1" si="7"/>
-        <v>176</v>
+        <v>388</v>
       </c>
       <c r="L364">
         <f t="shared" ca="1" si="7"/>
-        <v>178</v>
+        <v>112</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.3">
@@ -15525,15 +15550,15 @@
       </c>
       <c r="J365">
         <f t="shared" ca="1" si="7"/>
-        <v>251</v>
+        <v>174</v>
       </c>
       <c r="K365">
         <f t="shared" ca="1" si="7"/>
-        <v>231</v>
+        <v>280</v>
       </c>
       <c r="L365">
         <f t="shared" ca="1" si="7"/>
-        <v>365</v>
+        <v>193</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.3">
@@ -15566,15 +15591,15 @@
       </c>
       <c r="J366">
         <f t="shared" ca="1" si="7"/>
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="K366">
         <f t="shared" ca="1" si="7"/>
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="L366">
         <f t="shared" ca="1" si="7"/>
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.3">
@@ -15607,15 +15632,15 @@
       </c>
       <c r="J367">
         <f t="shared" ca="1" si="7"/>
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="K367">
         <f t="shared" ca="1" si="7"/>
-        <v>265</v>
+        <v>195</v>
       </c>
       <c r="L367">
         <f t="shared" ca="1" si="7"/>
-        <v>119</v>
+        <v>169</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.3">
@@ -15648,15 +15673,15 @@
       </c>
       <c r="J368">
         <f t="shared" ca="1" si="7"/>
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="K368">
         <f t="shared" ca="1" si="7"/>
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="L368">
         <f t="shared" ca="1" si="7"/>
-        <v>164</v>
+        <v>130</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.3">
@@ -15689,15 +15714,15 @@
       </c>
       <c r="J369">
         <f t="shared" ca="1" si="7"/>
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="K369">
         <f t="shared" ca="1" si="7"/>
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="L369">
         <f t="shared" ca="1" si="7"/>
-        <v>207</v>
+        <v>140</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.3">
@@ -15730,15 +15755,15 @@
       </c>
       <c r="J370">
         <f t="shared" ca="1" si="7"/>
-        <v>277</v>
+        <v>225</v>
       </c>
       <c r="K370">
         <f t="shared" ca="1" si="7"/>
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="L370">
         <f t="shared" ca="1" si="7"/>
-        <v>251</v>
+        <v>116</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.3">
@@ -15771,15 +15796,15 @@
       </c>
       <c r="J371">
         <f t="shared" ca="1" si="7"/>
-        <v>218</v>
+        <v>174</v>
       </c>
       <c r="K371">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="L371">
         <f t="shared" ca="1" si="7"/>
-        <v>215</v>
+        <v>170</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.3">
@@ -15812,15 +15837,15 @@
       </c>
       <c r="J372">
         <f t="shared" ca="1" si="7"/>
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="K372">
         <f t="shared" ca="1" si="7"/>
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="L372">
         <f t="shared" ca="1" si="7"/>
-        <v>389</v>
+        <v>120</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.3">
@@ -15853,15 +15878,15 @@
       </c>
       <c r="J373">
         <f t="shared" ca="1" si="7"/>
-        <v>275</v>
+        <v>339</v>
       </c>
       <c r="K373">
         <f t="shared" ca="1" si="7"/>
-        <v>175</v>
+        <v>388</v>
       </c>
       <c r="L373">
         <f t="shared" ca="1" si="7"/>
-        <v>382</v>
+        <v>244</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.3">
@@ -15894,15 +15919,15 @@
       </c>
       <c r="J374">
         <f t="shared" ca="1" si="7"/>
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="K374">
         <f t="shared" ca="1" si="7"/>
-        <v>389</v>
+        <v>267</v>
       </c>
       <c r="L374">
         <f t="shared" ca="1" si="7"/>
-        <v>374</v>
+        <v>202</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.3">
@@ -15935,15 +15960,15 @@
       </c>
       <c r="J375">
         <f t="shared" ca="1" si="7"/>
-        <v>248</v>
+        <v>385</v>
       </c>
       <c r="K375">
         <f t="shared" ca="1" si="7"/>
-        <v>347</v>
+        <v>216</v>
       </c>
       <c r="L375">
         <f t="shared" ca="1" si="7"/>
-        <v>327</v>
+        <v>129</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.3">
@@ -15976,15 +16001,15 @@
       </c>
       <c r="J376">
         <f t="shared" ca="1" si="7"/>
-        <v>236</v>
+        <v>316</v>
       </c>
       <c r="K376">
         <f t="shared" ca="1" si="7"/>
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="L376">
         <f t="shared" ca="1" si="7"/>
-        <v>355</v>
+        <v>243</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.3">
@@ -16017,15 +16042,15 @@
       </c>
       <c r="J377">
         <f t="shared" ca="1" si="7"/>
-        <v>327</v>
+        <v>280</v>
       </c>
       <c r="K377">
         <f t="shared" ca="1" si="7"/>
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="L377">
         <f t="shared" ca="1" si="7"/>
-        <v>305</v>
+        <v>363</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.3">
@@ -16058,15 +16083,15 @@
       </c>
       <c r="J378">
         <f t="shared" ca="1" si="7"/>
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="K378">
         <f t="shared" ca="1" si="7"/>
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="L378">
         <f t="shared" ca="1" si="7"/>
-        <v>212</v>
+        <v>329</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.3">
@@ -16099,15 +16124,15 @@
       </c>
       <c r="J379">
         <f t="shared" ca="1" si="7"/>
-        <v>392</v>
+        <v>235</v>
       </c>
       <c r="K379">
         <f t="shared" ca="1" si="7"/>
-        <v>310</v>
+        <v>214</v>
       </c>
       <c r="L379">
         <f t="shared" ca="1" si="7"/>
-        <v>105</v>
+        <v>328</v>
       </c>
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.3">
@@ -16140,15 +16165,15 @@
       </c>
       <c r="J380">
         <f t="shared" ca="1" si="7"/>
-        <v>388</v>
+        <v>177</v>
       </c>
       <c r="K380">
         <f t="shared" ca="1" si="7"/>
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="L380">
         <f t="shared" ca="1" si="7"/>
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.3">
@@ -16181,15 +16206,15 @@
       </c>
       <c r="J381">
         <f t="shared" ca="1" si="7"/>
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="K381">
         <f t="shared" ca="1" si="7"/>
-        <v>156</v>
+        <v>277</v>
       </c>
       <c r="L381">
         <f t="shared" ca="1" si="7"/>
-        <v>390</v>
+        <v>243</v>
       </c>
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.3">
@@ -16222,15 +16247,15 @@
       </c>
       <c r="J382">
         <f t="shared" ca="1" si="7"/>
-        <v>326</v>
+        <v>227</v>
       </c>
       <c r="K382">
         <f t="shared" ca="1" si="7"/>
-        <v>283</v>
+        <v>381</v>
       </c>
       <c r="L382">
         <f t="shared" ca="1" si="7"/>
-        <v>213</v>
+        <v>111</v>
       </c>
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.3">
@@ -16263,15 +16288,15 @@
       </c>
       <c r="J383">
         <f t="shared" ca="1" si="7"/>
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="K383">
         <f t="shared" ca="1" si="7"/>
-        <v>311</v>
+        <v>388</v>
       </c>
       <c r="L383">
         <f t="shared" ca="1" si="7"/>
-        <v>214</v>
+        <v>305</v>
       </c>
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.3">
@@ -16304,15 +16329,15 @@
       </c>
       <c r="J384">
         <f t="shared" ca="1" si="7"/>
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="K384">
         <f t="shared" ca="1" si="7"/>
-        <v>277</v>
+        <v>318</v>
       </c>
       <c r="L384">
         <f t="shared" ca="1" si="7"/>
-        <v>185</v>
+        <v>250</v>
       </c>
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.3">
@@ -16345,15 +16370,15 @@
       </c>
       <c r="J385">
         <f t="shared" ca="1" si="7"/>
-        <v>375</v>
+        <v>249</v>
       </c>
       <c r="K385">
         <f t="shared" ca="1" si="7"/>
-        <v>363</v>
+        <v>185</v>
       </c>
       <c r="L385">
         <f t="shared" ca="1" si="7"/>
-        <v>363</v>
+        <v>215</v>
       </c>
     </row>
     <row r="386" spans="1:12" x14ac:dyDescent="0.3">
@@ -16386,15 +16411,15 @@
       </c>
       <c r="J386">
         <f t="shared" ca="1" si="7"/>
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="K386">
         <f t="shared" ca="1" si="7"/>
-        <v>387</v>
+        <v>123</v>
       </c>
       <c r="L386">
         <f t="shared" ca="1" si="7"/>
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.3">
@@ -16427,15 +16452,15 @@
       </c>
       <c r="J387">
         <f t="shared" ref="J387:L418" ca="1" si="8">RANDBETWEEN(100,400)</f>
-        <v>170</v>
+        <v>254</v>
       </c>
       <c r="K387">
         <f t="shared" ca="1" si="8"/>
-        <v>216</v>
+        <v>305</v>
       </c>
       <c r="L387">
         <f t="shared" ca="1" si="8"/>
-        <v>280</v>
+        <v>258</v>
       </c>
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.3">
@@ -16468,15 +16493,15 @@
       </c>
       <c r="J388">
         <f t="shared" ca="1" si="8"/>
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="K388">
         <f t="shared" ca="1" si="8"/>
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L388">
         <f t="shared" ca="1" si="8"/>
-        <v>264</v>
+        <v>288</v>
       </c>
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.3">
@@ -16509,15 +16534,15 @@
       </c>
       <c r="J389">
         <f t="shared" ca="1" si="8"/>
-        <v>126</v>
+        <v>373</v>
       </c>
       <c r="K389">
         <f t="shared" ca="1" si="8"/>
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="L389">
         <f t="shared" ca="1" si="8"/>
-        <v>353</v>
+        <v>242</v>
       </c>
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.3">
@@ -16550,15 +16575,15 @@
       </c>
       <c r="J390">
         <f t="shared" ca="1" si="8"/>
-        <v>357</v>
+        <v>146</v>
       </c>
       <c r="K390">
         <f t="shared" ca="1" si="8"/>
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="L390">
         <f t="shared" ca="1" si="8"/>
-        <v>271</v>
+        <v>360</v>
       </c>
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.3">
@@ -16591,15 +16616,15 @@
       </c>
       <c r="J391">
         <f t="shared" ca="1" si="8"/>
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="K391">
         <f t="shared" ca="1" si="8"/>
-        <v>253</v>
+        <v>343</v>
       </c>
       <c r="L391">
         <f t="shared" ca="1" si="8"/>
-        <v>319</v>
+        <v>371</v>
       </c>
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.3">
@@ -16632,15 +16657,15 @@
       </c>
       <c r="J392">
         <f t="shared" ca="1" si="8"/>
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="K392">
         <f t="shared" ca="1" si="8"/>
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="L392">
         <f t="shared" ca="1" si="8"/>
-        <v>170</v>
+        <v>251</v>
       </c>
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.3">
@@ -16673,15 +16698,15 @@
       </c>
       <c r="J393">
         <f t="shared" ca="1" si="8"/>
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="K393">
         <f t="shared" ca="1" si="8"/>
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="L393">
         <f t="shared" ca="1" si="8"/>
-        <v>210</v>
+        <v>123</v>
       </c>
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.3">
@@ -16714,15 +16739,15 @@
       </c>
       <c r="J394">
         <f t="shared" ca="1" si="8"/>
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="K394">
         <f t="shared" ca="1" si="8"/>
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="L394">
         <f t="shared" ca="1" si="8"/>
-        <v>221</v>
+        <v>354</v>
       </c>
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.3">
@@ -16755,15 +16780,15 @@
       </c>
       <c r="J395">
         <f t="shared" ca="1" si="8"/>
-        <v>235</v>
+        <v>112</v>
       </c>
       <c r="K395">
         <f t="shared" ca="1" si="8"/>
-        <v>311</v>
+        <v>393</v>
       </c>
       <c r="L395">
         <f t="shared" ca="1" si="8"/>
-        <v>396</v>
+        <v>103</v>
       </c>
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.3">
@@ -16796,15 +16821,15 @@
       </c>
       <c r="J396">
         <f t="shared" ca="1" si="8"/>
-        <v>271</v>
+        <v>124</v>
       </c>
       <c r="K396">
         <f t="shared" ca="1" si="8"/>
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="L396">
         <f t="shared" ca="1" si="8"/>
-        <v>176</v>
+        <v>267</v>
       </c>
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.3">
@@ -16837,15 +16862,15 @@
       </c>
       <c r="J397">
         <f t="shared" ca="1" si="8"/>
-        <v>230</v>
+        <v>301</v>
       </c>
       <c r="K397">
         <f t="shared" ca="1" si="8"/>
-        <v>372</v>
+        <v>261</v>
       </c>
       <c r="L397">
         <f t="shared" ca="1" si="8"/>
-        <v>132</v>
+        <v>192</v>
       </c>
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.3">
@@ -16878,15 +16903,15 @@
       </c>
       <c r="J398">
         <f t="shared" ca="1" si="8"/>
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="K398">
         <f t="shared" ca="1" si="8"/>
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="L398">
         <f t="shared" ca="1" si="8"/>
-        <v>380</v>
+        <v>180</v>
       </c>
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.3">
@@ -16919,15 +16944,15 @@
       </c>
       <c r="J399">
         <f t="shared" ca="1" si="8"/>
-        <v>210</v>
+        <v>145</v>
       </c>
       <c r="K399">
         <f t="shared" ca="1" si="8"/>
-        <v>389</v>
+        <v>284</v>
       </c>
       <c r="L399">
         <f t="shared" ca="1" si="8"/>
-        <v>126</v>
+        <v>269</v>
       </c>
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.3">
@@ -16960,15 +16985,15 @@
       </c>
       <c r="J400">
         <f t="shared" ca="1" si="8"/>
-        <v>123</v>
+        <v>245</v>
       </c>
       <c r="K400">
         <f t="shared" ca="1" si="8"/>
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="L400">
         <f t="shared" ca="1" si="8"/>
-        <v>300</v>
+        <v>352</v>
       </c>
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.3">
@@ -17001,15 +17026,15 @@
       </c>
       <c r="J401">
         <f t="shared" ca="1" si="8"/>
-        <v>116</v>
+        <v>393</v>
       </c>
       <c r="K401">
         <f t="shared" ca="1" si="8"/>
-        <v>393</v>
+        <v>316</v>
       </c>
       <c r="L401">
         <f t="shared" ca="1" si="8"/>
-        <v>179</v>
+        <v>275</v>
       </c>
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.3">
@@ -17042,15 +17067,15 @@
       </c>
       <c r="J402">
         <f t="shared" ca="1" si="8"/>
-        <v>397</v>
+        <v>353</v>
       </c>
       <c r="K402">
         <f t="shared" ca="1" si="8"/>
-        <v>115</v>
+        <v>396</v>
       </c>
       <c r="L402">
         <f t="shared" ca="1" si="8"/>
-        <v>123</v>
+        <v>362</v>
       </c>
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.3">
@@ -17083,15 +17108,15 @@
       </c>
       <c r="J403">
         <f t="shared" ca="1" si="8"/>
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="K403">
         <f t="shared" ca="1" si="8"/>
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="L403">
         <f t="shared" ca="1" si="8"/>
-        <v>233</v>
+        <v>171</v>
       </c>
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.3">
@@ -17124,15 +17149,15 @@
       </c>
       <c r="J404">
         <f t="shared" ca="1" si="8"/>
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="K404">
         <f t="shared" ca="1" si="8"/>
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="L404">
         <f t="shared" ca="1" si="8"/>
-        <v>228</v>
+        <v>106</v>
       </c>
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.3">
@@ -17165,15 +17190,15 @@
       </c>
       <c r="J405">
         <f t="shared" ca="1" si="8"/>
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="K405">
         <f t="shared" ca="1" si="8"/>
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="L405">
         <f t="shared" ca="1" si="8"/>
-        <v>287</v>
+        <v>117</v>
       </c>
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.3">
@@ -17206,15 +17231,15 @@
       </c>
       <c r="J406">
         <f t="shared" ca="1" si="8"/>
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="K406">
         <f t="shared" ca="1" si="8"/>
-        <v>294</v>
+        <v>127</v>
       </c>
       <c r="L406">
         <f t="shared" ca="1" si="8"/>
-        <v>257</v>
+        <v>120</v>
       </c>
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.3">
@@ -17247,15 +17272,15 @@
       </c>
       <c r="J407">
         <f t="shared" ca="1" si="8"/>
-        <v>307</v>
+        <v>222</v>
       </c>
       <c r="K407">
         <f t="shared" ca="1" si="8"/>
-        <v>351</v>
+        <v>114</v>
       </c>
       <c r="L407">
         <f t="shared" ca="1" si="8"/>
-        <v>307</v>
+        <v>344</v>
       </c>
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.3">
@@ -17288,15 +17313,15 @@
       </c>
       <c r="J408">
         <f t="shared" ca="1" si="8"/>
-        <v>220</v>
+        <v>362</v>
       </c>
       <c r="K408">
         <f t="shared" ca="1" si="8"/>
-        <v>108</v>
+        <v>315</v>
       </c>
       <c r="L408">
         <f t="shared" ca="1" si="8"/>
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.3">
@@ -17329,15 +17354,15 @@
       </c>
       <c r="J409">
         <f t="shared" ca="1" si="8"/>
-        <v>337</v>
+        <v>262</v>
       </c>
       <c r="K409">
         <f t="shared" ca="1" si="8"/>
-        <v>288</v>
+        <v>184</v>
       </c>
       <c r="L409">
         <f t="shared" ca="1" si="8"/>
-        <v>262</v>
+        <v>141</v>
       </c>
     </row>
     <row r="410" spans="1:12" x14ac:dyDescent="0.3">
@@ -17370,15 +17395,15 @@
       </c>
       <c r="J410">
         <f t="shared" ca="1" si="8"/>
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="K410">
         <f t="shared" ca="1" si="8"/>
-        <v>379</v>
+        <v>200</v>
       </c>
       <c r="L410">
         <f t="shared" ca="1" si="8"/>
-        <v>399</v>
+        <v>361</v>
       </c>
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.3">
@@ -17411,15 +17436,15 @@
       </c>
       <c r="J411">
         <f t="shared" ca="1" si="8"/>
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="K411">
         <f t="shared" ca="1" si="8"/>
-        <v>106</v>
+        <v>393</v>
       </c>
       <c r="L411">
         <f t="shared" ca="1" si="8"/>
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.3">
@@ -17452,15 +17477,15 @@
       </c>
       <c r="J412">
         <f t="shared" ca="1" si="8"/>
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="K412">
         <f t="shared" ca="1" si="8"/>
-        <v>154</v>
+        <v>337</v>
       </c>
       <c r="L412">
         <f t="shared" ca="1" si="8"/>
-        <v>270</v>
+        <v>385</v>
       </c>
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.3">
@@ -17493,15 +17518,15 @@
       </c>
       <c r="J413">
         <f t="shared" ca="1" si="8"/>
-        <v>389</v>
+        <v>224</v>
       </c>
       <c r="K413">
         <f t="shared" ca="1" si="8"/>
-        <v>133</v>
+        <v>187</v>
       </c>
       <c r="L413">
         <f t="shared" ca="1" si="8"/>
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.3">
@@ -17534,15 +17559,15 @@
       </c>
       <c r="J414">
         <f t="shared" ca="1" si="8"/>
-        <v>367</v>
+        <v>102</v>
       </c>
       <c r="K414">
         <f t="shared" ca="1" si="8"/>
-        <v>210</v>
+        <v>138</v>
       </c>
       <c r="L414">
         <f t="shared" ca="1" si="8"/>
-        <v>368</v>
+        <v>244</v>
       </c>
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.3">
@@ -17575,15 +17600,15 @@
       </c>
       <c r="J415">
         <f t="shared" ca="1" si="8"/>
-        <v>371</v>
+        <v>148</v>
       </c>
       <c r="K415">
         <f t="shared" ca="1" si="8"/>
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="L415">
         <f t="shared" ca="1" si="8"/>
-        <v>181</v>
+        <v>332</v>
       </c>
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.3">
@@ -17616,15 +17641,15 @@
       </c>
       <c r="J416">
         <f t="shared" ca="1" si="8"/>
-        <v>160</v>
+        <v>386</v>
       </c>
       <c r="K416">
         <f t="shared" ca="1" si="8"/>
-        <v>320</v>
+        <v>365</v>
       </c>
       <c r="L416">
         <f t="shared" ca="1" si="8"/>
-        <v>329</v>
+        <v>151</v>
       </c>
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.3">
@@ -17657,15 +17682,15 @@
       </c>
       <c r="J417">
         <f t="shared" ca="1" si="8"/>
-        <v>300</v>
+        <v>129</v>
       </c>
       <c r="K417">
         <f t="shared" ca="1" si="8"/>
-        <v>339</v>
+        <v>298</v>
       </c>
       <c r="L417">
         <f t="shared" ca="1" si="8"/>
-        <v>362</v>
+        <v>130</v>
       </c>
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.3">
@@ -17698,15 +17723,15 @@
       </c>
       <c r="J418">
         <f t="shared" ca="1" si="8"/>
-        <v>148</v>
+        <v>329</v>
       </c>
       <c r="K418">
         <f t="shared" ca="1" si="8"/>
-        <v>190</v>
+        <v>356</v>
       </c>
       <c r="L418">
         <f t="shared" ca="1" si="8"/>
-        <v>198</v>
+        <v>128</v>
       </c>
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.3">
@@ -17739,15 +17764,15 @@
       </c>
       <c r="J419">
         <f t="shared" ref="J419:L450" ca="1" si="9">RANDBETWEEN(100,400)</f>
-        <v>184</v>
+        <v>384</v>
       </c>
       <c r="K419">
         <f t="shared" ca="1" si="9"/>
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="L419">
         <f t="shared" ca="1" si="9"/>
-        <v>373</v>
+        <v>255</v>
       </c>
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.3">
@@ -17780,15 +17805,15 @@
       </c>
       <c r="J420">
         <f t="shared" ca="1" si="9"/>
-        <v>358</v>
+        <v>305</v>
       </c>
       <c r="K420">
         <f t="shared" ca="1" si="9"/>
-        <v>212</v>
+        <v>316</v>
       </c>
       <c r="L420">
         <f t="shared" ca="1" si="9"/>
-        <v>264</v>
+        <v>324</v>
       </c>
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.3">
@@ -17821,15 +17846,15 @@
       </c>
       <c r="J421">
         <f t="shared" ca="1" si="9"/>
-        <v>334</v>
+        <v>241</v>
       </c>
       <c r="K421">
         <f t="shared" ca="1" si="9"/>
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="L421">
         <f t="shared" ca="1" si="9"/>
-        <v>354</v>
+        <v>263</v>
       </c>
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.3">
@@ -17862,15 +17887,15 @@
       </c>
       <c r="J422">
         <f t="shared" ca="1" si="9"/>
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K422">
         <f t="shared" ca="1" si="9"/>
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="L422">
         <f t="shared" ca="1" si="9"/>
-        <v>176</v>
+        <v>302</v>
       </c>
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.3">
@@ -17903,15 +17928,15 @@
       </c>
       <c r="J423">
         <f t="shared" ca="1" si="9"/>
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="K423">
         <f t="shared" ca="1" si="9"/>
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L423">
         <f t="shared" ca="1" si="9"/>
-        <v>369</v>
+        <v>194</v>
       </c>
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.3">
@@ -17944,15 +17969,15 @@
       </c>
       <c r="J424">
         <f t="shared" ca="1" si="9"/>
-        <v>127</v>
+        <v>335</v>
       </c>
       <c r="K424">
         <f t="shared" ca="1" si="9"/>
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="L424">
         <f t="shared" ca="1" si="9"/>
-        <v>382</v>
+        <v>328</v>
       </c>
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.3">
@@ -17985,15 +18010,15 @@
       </c>
       <c r="J425">
         <f t="shared" ca="1" si="9"/>
-        <v>252</v>
+        <v>341</v>
       </c>
       <c r="K425">
         <f t="shared" ca="1" si="9"/>
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="L425">
         <f t="shared" ca="1" si="9"/>
-        <v>162</v>
+        <v>334</v>
       </c>
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.3">
@@ -18026,15 +18051,15 @@
       </c>
       <c r="J426">
         <f t="shared" ca="1" si="9"/>
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="K426">
         <f t="shared" ca="1" si="9"/>
-        <v>103</v>
+        <v>233</v>
       </c>
       <c r="L426">
         <f t="shared" ca="1" si="9"/>
-        <v>327</v>
+        <v>282</v>
       </c>
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.3">
@@ -18067,15 +18092,15 @@
       </c>
       <c r="J427">
         <f t="shared" ca="1" si="9"/>
-        <v>396</v>
+        <v>357</v>
       </c>
       <c r="K427">
         <f t="shared" ca="1" si="9"/>
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="L427">
         <f t="shared" ca="1" si="9"/>
-        <v>347</v>
+        <v>131</v>
       </c>
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.3">
@@ -18108,15 +18133,15 @@
       </c>
       <c r="J428">
         <f t="shared" ca="1" si="9"/>
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="K428">
         <f t="shared" ca="1" si="9"/>
-        <v>267</v>
+        <v>151</v>
       </c>
       <c r="L428">
         <f t="shared" ca="1" si="9"/>
-        <v>254</v>
+        <v>374</v>
       </c>
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.3">
@@ -18149,15 +18174,15 @@
       </c>
       <c r="J429">
         <f t="shared" ca="1" si="9"/>
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="K429">
         <f t="shared" ca="1" si="9"/>
-        <v>257</v>
+        <v>378</v>
       </c>
       <c r="L429">
         <f t="shared" ca="1" si="9"/>
-        <v>278</v>
+        <v>327</v>
       </c>
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.3">
@@ -18190,15 +18215,15 @@
       </c>
       <c r="J430">
         <f t="shared" ca="1" si="9"/>
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="K430">
         <f t="shared" ca="1" si="9"/>
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="L430">
         <f t="shared" ca="1" si="9"/>
-        <v>369</v>
+        <v>191</v>
       </c>
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.3">
@@ -18231,15 +18256,15 @@
       </c>
       <c r="J431">
         <f t="shared" ca="1" si="9"/>
-        <v>365</v>
+        <v>206</v>
       </c>
       <c r="K431">
         <f t="shared" ca="1" si="9"/>
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="L431">
         <f t="shared" ca="1" si="9"/>
-        <v>285</v>
+        <v>393</v>
       </c>
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.3">
@@ -18272,15 +18297,15 @@
       </c>
       <c r="J432">
         <f t="shared" ca="1" si="9"/>
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K432">
         <f t="shared" ca="1" si="9"/>
-        <v>127</v>
+        <v>294</v>
       </c>
       <c r="L432">
         <f t="shared" ca="1" si="9"/>
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.3">
@@ -18313,15 +18338,15 @@
       </c>
       <c r="J433">
         <f t="shared" ca="1" si="9"/>
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="K433">
         <f t="shared" ca="1" si="9"/>
-        <v>365</v>
+        <v>176</v>
       </c>
       <c r="L433">
         <f t="shared" ca="1" si="9"/>
-        <v>127</v>
+        <v>398</v>
       </c>
     </row>
     <row r="434" spans="1:12" x14ac:dyDescent="0.3">
@@ -18354,15 +18379,15 @@
       </c>
       <c r="J434">
         <f t="shared" ca="1" si="9"/>
-        <v>295</v>
+        <v>124</v>
       </c>
       <c r="K434">
         <f t="shared" ca="1" si="9"/>
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="L434">
         <f t="shared" ca="1" si="9"/>
-        <v>319</v>
+        <v>199</v>
       </c>
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.3">
@@ -18395,15 +18420,15 @@
       </c>
       <c r="J435">
         <f t="shared" ca="1" si="9"/>
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="K435">
         <f t="shared" ca="1" si="9"/>
-        <v>102</v>
+        <v>381</v>
       </c>
       <c r="L435">
         <f t="shared" ca="1" si="9"/>
-        <v>129</v>
+        <v>305</v>
       </c>
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.3">
@@ -18436,15 +18461,15 @@
       </c>
       <c r="J436">
         <f t="shared" ca="1" si="9"/>
-        <v>373</v>
+        <v>312</v>
       </c>
       <c r="K436">
         <f t="shared" ca="1" si="9"/>
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L436">
         <f t="shared" ca="1" si="9"/>
-        <v>340</v>
+        <v>286</v>
       </c>
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.3">
@@ -18477,7 +18502,7 @@
       </c>
       <c r="J437">
         <f t="shared" ca="1" si="9"/>
-        <v>239</v>
+        <v>346</v>
       </c>
       <c r="K437">
         <f t="shared" ca="1" si="9"/>
@@ -18485,7 +18510,7 @@
       </c>
       <c r="L437">
         <f t="shared" ca="1" si="9"/>
-        <v>289</v>
+        <v>218</v>
       </c>
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.3">
@@ -18518,15 +18543,15 @@
       </c>
       <c r="J438">
         <f t="shared" ca="1" si="9"/>
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="K438">
         <f t="shared" ca="1" si="9"/>
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="L438">
         <f t="shared" ca="1" si="9"/>
-        <v>262</v>
+        <v>143</v>
       </c>
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.3">
@@ -18559,15 +18584,15 @@
       </c>
       <c r="J439">
         <f t="shared" ca="1" si="9"/>
-        <v>398</v>
+        <v>167</v>
       </c>
       <c r="K439">
         <f t="shared" ca="1" si="9"/>
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="L439">
         <f t="shared" ca="1" si="9"/>
-        <v>387</v>
+        <v>281</v>
       </c>
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.3">
@@ -18600,15 +18625,15 @@
       </c>
       <c r="J440">
         <f t="shared" ca="1" si="9"/>
-        <v>276</v>
+        <v>145</v>
       </c>
       <c r="K440">
         <f t="shared" ca="1" si="9"/>
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="L440">
         <f t="shared" ca="1" si="9"/>
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.3">
@@ -18641,15 +18666,15 @@
       </c>
       <c r="J441">
         <f t="shared" ca="1" si="9"/>
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="K441">
         <f t="shared" ca="1" si="9"/>
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="L441">
         <f t="shared" ca="1" si="9"/>
-        <v>340</v>
+        <v>138</v>
       </c>
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.3">
@@ -18682,15 +18707,15 @@
       </c>
       <c r="J442">
         <f t="shared" ca="1" si="9"/>
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="K442">
         <f t="shared" ca="1" si="9"/>
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="L442">
         <f t="shared" ca="1" si="9"/>
-        <v>366</v>
+        <v>302</v>
       </c>
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.3">
@@ -18723,15 +18748,15 @@
       </c>
       <c r="J443">
         <f t="shared" ca="1" si="9"/>
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="K443">
         <f t="shared" ca="1" si="9"/>
-        <v>192</v>
+        <v>121</v>
       </c>
       <c r="L443">
         <f t="shared" ca="1" si="9"/>
-        <v>372</v>
+        <v>206</v>
       </c>
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.3">
@@ -18764,15 +18789,15 @@
       </c>
       <c r="J444">
         <f t="shared" ca="1" si="9"/>
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="K444">
         <f t="shared" ca="1" si="9"/>
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="L444">
         <f t="shared" ca="1" si="9"/>
-        <v>358</v>
+        <v>187</v>
       </c>
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.3">
@@ -18805,15 +18830,15 @@
       </c>
       <c r="J445">
         <f t="shared" ca="1" si="9"/>
-        <v>138</v>
+        <v>279</v>
       </c>
       <c r="K445">
         <f t="shared" ca="1" si="9"/>
-        <v>117</v>
+        <v>309</v>
       </c>
       <c r="L445">
         <f t="shared" ca="1" si="9"/>
-        <v>390</v>
+        <v>316</v>
       </c>
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.3">
@@ -18846,15 +18871,15 @@
       </c>
       <c r="J446">
         <f t="shared" ca="1" si="9"/>
-        <v>283</v>
+        <v>392</v>
       </c>
       <c r="K446">
         <f t="shared" ca="1" si="9"/>
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="L446">
         <f t="shared" ca="1" si="9"/>
-        <v>311</v>
+        <v>263</v>
       </c>
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.3">
@@ -18887,15 +18912,15 @@
       </c>
       <c r="J447">
         <f t="shared" ca="1" si="9"/>
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="K447">
         <f t="shared" ca="1" si="9"/>
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="L447">
         <f t="shared" ca="1" si="9"/>
-        <v>295</v>
+        <v>273</v>
       </c>
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.3">
@@ -18928,15 +18953,15 @@
       </c>
       <c r="J448">
         <f t="shared" ca="1" si="9"/>
-        <v>250</v>
+        <v>341</v>
       </c>
       <c r="K448">
         <f t="shared" ca="1" si="9"/>
-        <v>361</v>
+        <v>318</v>
       </c>
       <c r="L448">
         <f t="shared" ca="1" si="9"/>
-        <v>153</v>
+        <v>313</v>
       </c>
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.3">
@@ -18969,15 +18994,15 @@
       </c>
       <c r="J449">
         <f t="shared" ca="1" si="9"/>
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="K449">
         <f t="shared" ca="1" si="9"/>
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="L449">
         <f t="shared" ca="1" si="9"/>
-        <v>188</v>
+        <v>107</v>
       </c>
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.3">
@@ -19010,15 +19035,15 @@
       </c>
       <c r="J450">
         <f t="shared" ca="1" si="9"/>
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="K450">
         <f t="shared" ca="1" si="9"/>
-        <v>109</v>
+        <v>354</v>
       </c>
       <c r="L450">
         <f t="shared" ca="1" si="9"/>
-        <v>171</v>
+        <v>232</v>
       </c>
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.3">
@@ -19051,15 +19076,15 @@
       </c>
       <c r="J451">
         <f t="shared" ref="J451:L481" ca="1" si="10">RANDBETWEEN(100,400)</f>
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="K451">
         <f t="shared" ca="1" si="10"/>
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="L451">
         <f t="shared" ca="1" si="10"/>
-        <v>222</v>
+        <v>147</v>
       </c>
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.3">
@@ -19092,15 +19117,15 @@
       </c>
       <c r="J452">
         <f t="shared" ca="1" si="10"/>
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="K452">
         <f t="shared" ca="1" si="10"/>
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="L452">
         <f t="shared" ca="1" si="10"/>
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.3">
@@ -19133,15 +19158,15 @@
       </c>
       <c r="J453">
         <f t="shared" ca="1" si="10"/>
-        <v>166</v>
+        <v>361</v>
       </c>
       <c r="K453">
         <f t="shared" ca="1" si="10"/>
-        <v>382</v>
+        <v>303</v>
       </c>
       <c r="L453">
         <f t="shared" ca="1" si="10"/>
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.3">
@@ -19174,15 +19199,15 @@
       </c>
       <c r="J454">
         <f t="shared" ca="1" si="10"/>
-        <v>337</v>
+        <v>143</v>
       </c>
       <c r="K454">
         <f t="shared" ca="1" si="10"/>
-        <v>321</v>
+        <v>184</v>
       </c>
       <c r="L454">
         <f t="shared" ca="1" si="10"/>
-        <v>257</v>
+        <v>223</v>
       </c>
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.3">
@@ -19215,15 +19240,15 @@
       </c>
       <c r="J455">
         <f t="shared" ca="1" si="10"/>
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="K455">
         <f t="shared" ca="1" si="10"/>
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="L455">
         <f t="shared" ca="1" si="10"/>
-        <v>191</v>
+        <v>295</v>
       </c>
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.3">
@@ -19256,15 +19281,15 @@
       </c>
       <c r="J456">
         <f t="shared" ca="1" si="10"/>
-        <v>110</v>
+        <v>323</v>
       </c>
       <c r="K456">
         <f t="shared" ca="1" si="10"/>
-        <v>268</v>
+        <v>202</v>
       </c>
       <c r="L456">
         <f t="shared" ca="1" si="10"/>
-        <v>117</v>
+        <v>224</v>
       </c>
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.3">
@@ -19297,15 +19322,15 @@
       </c>
       <c r="J457">
         <f t="shared" ca="1" si="10"/>
-        <v>363</v>
+        <v>219</v>
       </c>
       <c r="K457">
         <f t="shared" ca="1" si="10"/>
-        <v>395</v>
+        <v>218</v>
       </c>
       <c r="L457">
         <f t="shared" ca="1" si="10"/>
-        <v>185</v>
+        <v>388</v>
       </c>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.3">
@@ -19338,15 +19363,15 @@
       </c>
       <c r="J458">
         <f t="shared" ca="1" si="10"/>
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="K458">
         <f t="shared" ca="1" si="10"/>
-        <v>389</v>
+        <v>113</v>
       </c>
       <c r="L458">
         <f t="shared" ca="1" si="10"/>
-        <v>294</v>
+        <v>207</v>
       </c>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.3">
@@ -19379,15 +19404,15 @@
       </c>
       <c r="J459">
         <f t="shared" ca="1" si="10"/>
-        <v>133</v>
+        <v>300</v>
       </c>
       <c r="K459">
         <f t="shared" ca="1" si="10"/>
-        <v>270</v>
+        <v>400</v>
       </c>
       <c r="L459">
         <f t="shared" ca="1" si="10"/>
-        <v>237</v>
+        <v>291</v>
       </c>
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.3">
@@ -19420,15 +19445,15 @@
       </c>
       <c r="J460">
         <f t="shared" ca="1" si="10"/>
-        <v>233</v>
+        <v>102</v>
       </c>
       <c r="K460">
         <f t="shared" ca="1" si="10"/>
-        <v>290</v>
+        <v>162</v>
       </c>
       <c r="L460">
         <f t="shared" ca="1" si="10"/>
-        <v>360</v>
+        <v>123</v>
       </c>
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.3">
@@ -19461,15 +19486,15 @@
       </c>
       <c r="J461">
         <f t="shared" ca="1" si="10"/>
-        <v>359</v>
+        <v>312</v>
       </c>
       <c r="K461">
         <f t="shared" ca="1" si="10"/>
-        <v>216</v>
+        <v>303</v>
       </c>
       <c r="L461">
         <f t="shared" ca="1" si="10"/>
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.3">
@@ -19502,15 +19527,15 @@
       </c>
       <c r="J462">
         <f t="shared" ca="1" si="10"/>
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="K462">
         <f t="shared" ca="1" si="10"/>
-        <v>342</v>
+        <v>115</v>
       </c>
       <c r="L462">
         <f t="shared" ca="1" si="10"/>
-        <v>297</v>
+        <v>127</v>
       </c>
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.3">
@@ -19543,15 +19568,15 @@
       </c>
       <c r="J463">
         <f t="shared" ca="1" si="10"/>
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="K463">
         <f t="shared" ca="1" si="10"/>
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="L463">
         <f t="shared" ca="1" si="10"/>
-        <v>175</v>
+        <v>381</v>
       </c>
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.3">
@@ -19584,15 +19609,15 @@
       </c>
       <c r="J464">
         <f t="shared" ca="1" si="10"/>
-        <v>288</v>
+        <v>110</v>
       </c>
       <c r="K464">
         <f t="shared" ca="1" si="10"/>
-        <v>256</v>
+        <v>130</v>
       </c>
       <c r="L464">
         <f t="shared" ca="1" si="10"/>
-        <v>194</v>
+        <v>340</v>
       </c>
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.3">
@@ -19625,15 +19650,15 @@
       </c>
       <c r="J465">
         <f t="shared" ca="1" si="10"/>
-        <v>259</v>
+        <v>393</v>
       </c>
       <c r="K465">
         <f t="shared" ca="1" si="10"/>
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="L465">
         <f t="shared" ca="1" si="10"/>
-        <v>338</v>
+        <v>202</v>
       </c>
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.3">
@@ -19666,15 +19691,15 @@
       </c>
       <c r="J466">
         <f t="shared" ca="1" si="10"/>
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="K466">
         <f t="shared" ca="1" si="10"/>
-        <v>344</v>
+        <v>221</v>
       </c>
       <c r="L466">
         <f t="shared" ca="1" si="10"/>
-        <v>365</v>
+        <v>172</v>
       </c>
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.3">
@@ -19707,15 +19732,15 @@
       </c>
       <c r="J467">
         <f t="shared" ca="1" si="10"/>
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="K467">
         <f t="shared" ca="1" si="10"/>
-        <v>351</v>
+        <v>233</v>
       </c>
       <c r="L467">
         <f t="shared" ca="1" si="10"/>
-        <v>167</v>
+        <v>351</v>
       </c>
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.3">
@@ -19748,15 +19773,15 @@
       </c>
       <c r="J468">
         <f t="shared" ca="1" si="10"/>
-        <v>253</v>
+        <v>341</v>
       </c>
       <c r="K468">
         <f t="shared" ca="1" si="10"/>
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="L468">
         <f t="shared" ca="1" si="10"/>
-        <v>373</v>
+        <v>289</v>
       </c>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.3">
@@ -19789,15 +19814,15 @@
       </c>
       <c r="J469">
         <f t="shared" ca="1" si="10"/>
-        <v>386</v>
+        <v>196</v>
       </c>
       <c r="K469">
         <f t="shared" ca="1" si="10"/>
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="L469">
         <f t="shared" ca="1" si="10"/>
-        <v>173</v>
+        <v>322</v>
       </c>
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.3">
@@ -19830,15 +19855,15 @@
       </c>
       <c r="J470">
         <f t="shared" ca="1" si="10"/>
-        <v>359</v>
+        <v>183</v>
       </c>
       <c r="K470">
         <f t="shared" ca="1" si="10"/>
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="L470">
         <f t="shared" ca="1" si="10"/>
-        <v>293</v>
+        <v>153</v>
       </c>
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.3">
@@ -19871,15 +19896,15 @@
       </c>
       <c r="J471">
         <f t="shared" ca="1" si="10"/>
-        <v>258</v>
+        <v>169</v>
       </c>
       <c r="K471">
         <f t="shared" ca="1" si="10"/>
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="L471">
         <f t="shared" ca="1" si="10"/>
-        <v>142</v>
+        <v>114</v>
       </c>
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.3">
@@ -19912,15 +19937,15 @@
       </c>
       <c r="J472">
         <f t="shared" ca="1" si="10"/>
-        <v>309</v>
+        <v>204</v>
       </c>
       <c r="K472">
         <f t="shared" ca="1" si="10"/>
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="L472">
         <f t="shared" ca="1" si="10"/>
-        <v>303</v>
+        <v>374</v>
       </c>
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.3">
@@ -19953,15 +19978,15 @@
       </c>
       <c r="J473">
         <f t="shared" ca="1" si="10"/>
-        <v>395</v>
+        <v>101</v>
       </c>
       <c r="K473">
         <f t="shared" ca="1" si="10"/>
-        <v>149</v>
+        <v>356</v>
       </c>
       <c r="L473">
         <f t="shared" ca="1" si="10"/>
-        <v>250</v>
+        <v>131</v>
       </c>
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.3">
@@ -19994,15 +20019,15 @@
       </c>
       <c r="J474">
         <f t="shared" ca="1" si="10"/>
-        <v>287</v>
+        <v>207</v>
       </c>
       <c r="K474">
         <f t="shared" ca="1" si="10"/>
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="L474">
         <f t="shared" ca="1" si="10"/>
-        <v>355</v>
+        <v>392</v>
       </c>
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.3">
@@ -20035,15 +20060,15 @@
       </c>
       <c r="J475">
         <f t="shared" ca="1" si="10"/>
-        <v>147</v>
+        <v>328</v>
       </c>
       <c r="K475">
         <f t="shared" ca="1" si="10"/>
-        <v>400</v>
+        <v>352</v>
       </c>
       <c r="L475">
         <f t="shared" ca="1" si="10"/>
-        <v>204</v>
+        <v>334</v>
       </c>
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.3">
@@ -20076,15 +20101,15 @@
       </c>
       <c r="J476">
         <f t="shared" ca="1" si="10"/>
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="K476">
         <f t="shared" ca="1" si="10"/>
-        <v>284</v>
+        <v>139</v>
       </c>
       <c r="L476">
         <f t="shared" ca="1" si="10"/>
-        <v>366</v>
+        <v>319</v>
       </c>
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.3">
@@ -20117,15 +20142,15 @@
       </c>
       <c r="J477">
         <f t="shared" ca="1" si="10"/>
-        <v>160</v>
+        <v>285</v>
       </c>
       <c r="K477">
         <f t="shared" ca="1" si="10"/>
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L477">
         <f t="shared" ca="1" si="10"/>
-        <v>199</v>
+        <v>111</v>
       </c>
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.3">
@@ -20158,15 +20183,15 @@
       </c>
       <c r="J478">
         <f t="shared" ca="1" si="10"/>
-        <v>205</v>
+        <v>332</v>
       </c>
       <c r="K478">
         <f t="shared" ca="1" si="10"/>
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="L478">
         <f t="shared" ca="1" si="10"/>
-        <v>393</v>
+        <v>201</v>
       </c>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.3">
@@ -20199,15 +20224,15 @@
       </c>
       <c r="J479">
         <f t="shared" ca="1" si="10"/>
-        <v>290</v>
+        <v>227</v>
       </c>
       <c r="K479">
         <f t="shared" ca="1" si="10"/>
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L479">
         <f t="shared" ca="1" si="10"/>
-        <v>377</v>
+        <v>176</v>
       </c>
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.3">
@@ -20240,15 +20265,15 @@
       </c>
       <c r="J480">
         <f t="shared" ca="1" si="10"/>
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="K480">
         <f t="shared" ca="1" si="10"/>
-        <v>390</v>
+        <v>151</v>
       </c>
       <c r="L480">
         <f t="shared" ca="1" si="10"/>
-        <v>351</v>
+        <v>192</v>
       </c>
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.3">
@@ -20281,15 +20306,15 @@
       </c>
       <c r="J481">
         <f t="shared" ca="1" si="10"/>
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="K481">
         <f t="shared" ca="1" si="10"/>
-        <v>148</v>
+        <v>284</v>
       </c>
       <c r="L481">
         <f t="shared" ca="1" si="10"/>
-        <v>144</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
